--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GIT\IMS_REPORTS\web\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GIT\TTBC\IMS_REPORTS\web\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B24E67-5F73-47B8-81C2-E81CB9271F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E19D5C-843E-4C01-9E21-6FE193D72916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{3C09AF49-172C-41AF-8C84-695524C35950}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BIEU 02 -2022" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'BIEU 02 -2022'!$A$1:$H$182</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'BIEU 02 -2022'!$A$1:$H$190</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BIEU 02 -2022'!$7:$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -617,12 +617,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -640,18 +652,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -971,7 +971,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I196"/>
+  <dimension ref="A1:I204"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="2" customWidth="1"/>
@@ -1314,11 +1314,11 @@
         <v>31</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="5"/>
@@ -1327,104 +1327,104 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
     </row>
     <row r="5" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
     </row>
     <row r="6" spans="1:9" ht="23.25" customHeight="1">
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
     </row>
     <row r="7" spans="1:9" ht="21.6" customHeight="1">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="63" t="s">
+      <c r="F7" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:9" ht="26.45" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="54" t="s">
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="57" t="s">
+      <c r="G8" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="58"/>
+      <c r="H8" s="62"/>
     </row>
     <row r="9" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="59" t="s">
+      <c r="A9" s="52"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="59" t="s">
+      <c r="H9" s="63" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="6">
@@ -3601,7 +3601,7 @@
       <c r="D146" s="43"/>
       <c r="E146" s="31"/>
       <c r="F146" s="37">
-        <f t="shared" ref="F146:F176" si="2">E146+G146</f>
+        <f t="shared" ref="F146:F184" si="2">E146+G146</f>
         <v>0</v>
       </c>
       <c r="G146" s="31"/>
@@ -3958,276 +3958,350 @@
       </c>
       <c r="G168" s="33"/>
       <c r="H168" s="38">
-        <f t="shared" ref="H168:H177" si="4">IFERROR(G168/E168,0)</f>
+        <f t="shared" ref="H168:H185" si="4">IFERROR(G168/E168,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="47"/>
       <c r="B169" s="50"/>
-      <c r="C169" s="19"/>
+      <c r="C169" s="23"/>
       <c r="D169" s="43"/>
       <c r="E169" s="31"/>
-      <c r="F169" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G169" s="31"/>
-      <c r="H169" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" s="7" customFormat="1">
+      <c r="F169" s="37"/>
+      <c r="G169" s="33"/>
+      <c r="H169" s="38"/>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" s="47"/>
       <c r="B170" s="50"/>
-      <c r="C170" s="20"/>
+      <c r="C170" s="23"/>
       <c r="D170" s="43"/>
       <c r="E170" s="31"/>
-      <c r="F170" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G170" s="31"/>
-      <c r="H170" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" s="7" customFormat="1">
+      <c r="F170" s="37"/>
+      <c r="G170" s="33"/>
+      <c r="H170" s="38"/>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171" s="47"/>
       <c r="B171" s="50"/>
-      <c r="C171" s="20"/>
+      <c r="C171" s="23"/>
       <c r="D171" s="43"/>
       <c r="E171" s="31"/>
-      <c r="F171" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G171" s="31"/>
-      <c r="H171" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" s="7" customFormat="1">
+      <c r="F171" s="37"/>
+      <c r="G171" s="33"/>
+      <c r="H171" s="38"/>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" s="47"/>
       <c r="B172" s="50"/>
-      <c r="C172" s="29"/>
+      <c r="C172" s="23"/>
       <c r="D172" s="43"/>
       <c r="E172" s="31"/>
-      <c r="F172" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G172" s="31"/>
-      <c r="H172" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" s="7" customFormat="1">
+      <c r="F172" s="37"/>
+      <c r="G172" s="33"/>
+      <c r="H172" s="38"/>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" s="47"/>
       <c r="B173" s="50"/>
-      <c r="C173" s="27"/>
+      <c r="C173" s="23"/>
       <c r="D173" s="43"/>
-      <c r="E173" s="33"/>
-      <c r="F173" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="E173" s="31"/>
+      <c r="F173" s="37"/>
       <c r="G173" s="33"/>
-      <c r="H173" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" s="7" customFormat="1">
+      <c r="H173" s="38"/>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174" s="47"/>
       <c r="B174" s="50"/>
-      <c r="C174" s="27"/>
+      <c r="C174" s="23"/>
       <c r="D174" s="43"/>
-      <c r="E174" s="33"/>
-      <c r="F174" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="E174" s="31"/>
+      <c r="F174" s="37"/>
       <c r="G174" s="33"/>
-      <c r="H174" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" s="7" customFormat="1">
+      <c r="H174" s="38"/>
+    </row>
+    <row r="175" spans="1:8">
       <c r="A175" s="47"/>
       <c r="B175" s="50"/>
-      <c r="C175" s="21"/>
+      <c r="C175" s="23"/>
       <c r="D175" s="43"/>
       <c r="E175" s="31"/>
-      <c r="F175" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G175" s="31"/>
-      <c r="H175" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" s="7" customFormat="1">
+      <c r="F175" s="37"/>
+      <c r="G175" s="33"/>
+      <c r="H175" s="38"/>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" s="47"/>
       <c r="B176" s="50"/>
-      <c r="C176" s="27"/>
+      <c r="C176" s="23"/>
       <c r="D176" s="43"/>
       <c r="E176" s="31"/>
-      <c r="F176" s="37">
+      <c r="F176" s="37"/>
+      <c r="G176" s="33"/>
+      <c r="H176" s="38"/>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="47"/>
+      <c r="B177" s="50"/>
+      <c r="C177" s="23"/>
+      <c r="D177" s="43"/>
+      <c r="E177" s="31"/>
+      <c r="F177" s="37"/>
+      <c r="G177" s="33"/>
+      <c r="H177" s="38"/>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="47"/>
+      <c r="B178" s="50"/>
+      <c r="C178" s="19"/>
+      <c r="D178" s="43"/>
+      <c r="E178" s="31"/>
+      <c r="F178" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G176" s="31"/>
-      <c r="H176" s="38">
+      <c r="G178" s="31"/>
+      <c r="H178" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
-      <c r="A177" s="48"/>
-      <c r="B177" s="51"/>
-      <c r="C177" s="30"/>
-      <c r="D177" s="44"/>
-      <c r="E177" s="36"/>
-      <c r="F177" s="41">
-        <f t="shared" ref="F177" si="5">E177+G177</f>
-        <v>0</v>
-      </c>
-      <c r="G177" s="36"/>
-      <c r="H177" s="39">
+    <row r="179" spans="1:8" s="7" customFormat="1">
+      <c r="A179" s="47"/>
+      <c r="B179" s="50"/>
+      <c r="C179" s="20"/>
+      <c r="D179" s="43"/>
+      <c r="E179" s="31"/>
+      <c r="F179" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G179" s="31"/>
+      <c r="H179" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="12" customHeight="1">
-      <c r="A178" s="10"/>
-      <c r="B178" s="13"/>
-      <c r="C178" s="11"/>
-      <c r="D178" s="11"/>
-      <c r="H178" s="7"/>
-    </row>
-    <row r="179" spans="1:8" ht="12" customHeight="1">
-      <c r="A179" s="10"/>
-      <c r="B179" s="13"/>
-      <c r="C179" s="2" t="s">
+    <row r="180" spans="1:8" s="7" customFormat="1">
+      <c r="A180" s="47"/>
+      <c r="B180" s="50"/>
+      <c r="C180" s="20"/>
+      <c r="D180" s="43"/>
+      <c r="E180" s="31"/>
+      <c r="F180" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G180" s="31"/>
+      <c r="H180" s="38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" s="7" customFormat="1">
+      <c r="A181" s="47"/>
+      <c r="B181" s="50"/>
+      <c r="C181" s="29"/>
+      <c r="D181" s="43"/>
+      <c r="E181" s="31"/>
+      <c r="F181" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G181" s="31"/>
+      <c r="H181" s="38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" s="7" customFormat="1">
+      <c r="A182" s="47"/>
+      <c r="B182" s="50"/>
+      <c r="C182" s="27"/>
+      <c r="D182" s="43"/>
+      <c r="E182" s="33"/>
+      <c r="F182" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G182" s="33"/>
+      <c r="H182" s="38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" s="7" customFormat="1">
+      <c r="A183" s="47"/>
+      <c r="B183" s="50"/>
+      <c r="C183" s="27"/>
+      <c r="D183" s="43"/>
+      <c r="E183" s="33"/>
+      <c r="F183" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G183" s="33"/>
+      <c r="H183" s="38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" s="7" customFormat="1">
+      <c r="A184" s="47"/>
+      <c r="B184" s="50"/>
+      <c r="C184" s="21"/>
+      <c r="D184" s="43"/>
+      <c r="E184" s="31"/>
+      <c r="F184" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G184" s="31"/>
+      <c r="H184" s="38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="48"/>
+      <c r="B185" s="51"/>
+      <c r="C185" s="30"/>
+      <c r="D185" s="44"/>
+      <c r="E185" s="36"/>
+      <c r="F185" s="41">
+        <f t="shared" ref="F185" si="5">E185+G185</f>
+        <v>0</v>
+      </c>
+      <c r="G185" s="36"/>
+      <c r="H185" s="39">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="12" customHeight="1">
+      <c r="A186" s="10"/>
+      <c r="B186" s="13"/>
+      <c r="C186" s="11"/>
+      <c r="D186" s="11"/>
+      <c r="H186" s="7"/>
+    </row>
+    <row r="187" spans="1:8" ht="12" customHeight="1">
+      <c r="A187" s="10"/>
+      <c r="B187" s="13"/>
+      <c r="C187" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H179" s="7"/>
-    </row>
-    <row r="180" spans="1:8">
-      <c r="A180" s="12"/>
-      <c r="B180" s="12"/>
-      <c r="C180" s="12"/>
-      <c r="D180" s="12"/>
-      <c r="E180" s="53" t="s">
+      <c r="H187" s="7"/>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="12"/>
+      <c r="B188" s="12"/>
+      <c r="C188" s="12"/>
+      <c r="D188" s="12"/>
+      <c r="E188" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F180" s="53"/>
-      <c r="G180" s="53"/>
-      <c r="H180" s="53"/>
-    </row>
-    <row r="181" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
-      <c r="C181" s="3" t="s">
+      <c r="F188" s="54"/>
+      <c r="G188" s="54"/>
+      <c r="H188" s="54"/>
+    </row>
+    <row r="189" spans="1:8" ht="19.5" customHeight="1">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D181" s="3"/>
-      <c r="E181" s="52" t="s">
+      <c r="D189" s="3"/>
+      <c r="E189" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F181" s="52"/>
-      <c r="G181" s="52"/>
-      <c r="H181" s="52"/>
-    </row>
-    <row r="182" spans="1:8">
-      <c r="A182" s="11"/>
-      <c r="B182" s="11"/>
-      <c r="C182" s="11" t="s">
+      <c r="F189" s="57"/>
+      <c r="G189" s="57"/>
+      <c r="H189" s="57"/>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="11"/>
+      <c r="B190" s="11"/>
+      <c r="C190" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D182" s="11"/>
-      <c r="E182" s="53" t="s">
+      <c r="D190" s="11"/>
+      <c r="E190" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F182" s="53"/>
-      <c r="G182" s="53"/>
-      <c r="H182" s="53"/>
-    </row>
-    <row r="183" spans="1:8" ht="18" customHeight="1">
-      <c r="A183" s="1"/>
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
-      <c r="E183" s="1"/>
-      <c r="F183" s="1"/>
-      <c r="G183" s="1"/>
-    </row>
-    <row r="186" spans="1:8">
-      <c r="C186" s="3" t="s">
+      <c r="F190" s="54"/>
+      <c r="G190" s="54"/>
+      <c r="H190" s="54"/>
+    </row>
+    <row r="191" spans="1:8" ht="18" customHeight="1">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+    </row>
+    <row r="194" spans="3:3">
+      <c r="C194" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="30.6" customHeight="1">
-      <c r="C187" s="2" t="s">
+    <row r="195" spans="3:3" ht="30.6" customHeight="1">
+      <c r="C195" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
-      <c r="C188" s="2" t="s">
+    <row r="196" spans="3:3">
+      <c r="C196" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
-      <c r="C189" s="2" t="s">
+    <row r="197" spans="3:3">
+      <c r="C197" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
-      <c r="C190" s="2" t="s">
+    <row r="198" spans="3:3">
+      <c r="C198" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
-      <c r="C191" s="2" t="s">
+    <row r="199" spans="3:3">
+      <c r="C199" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
-      <c r="C192" s="2" t="s">
+    <row r="200" spans="3:3">
+      <c r="C200" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="196" spans="3:3">
-      <c r="C196" s="3"/>
+    <row r="204" spans="3:3">
+      <c r="C204" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E189:H189"/>
+    <mergeCell ref="E190:H190"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="E188:H188"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="E7:E10"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="B7:B10"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="E181:H181"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="E180:H180"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="3.937007874015748E-2" footer="3.937007874015748E-2"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\KHNV\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0762B19-C856-4E63-B66C-6C77DEBAFD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="BIEU 02 -2022" sheetId="1" r:id="rId1"/>
@@ -19,7 +13,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'BIEU 02 -2022'!$A$1:$H$190</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BIEU 02 -2022'!$7:$11</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -981,8 +975,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1285,7 +1279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1439,6 +1433,9 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1478,7 +1475,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_1a. Mau bieu Ke hoach hoa  949 ngay 08-6-2004" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal_1a. Mau bieu Ke hoach hoa  949 ngay 08-6-2004" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1782,19 +1779,19 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I204"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" style="2" customWidth="1"/>
@@ -2122,7 +2119,7 @@
     <col min="16137" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="F1" s="3"/>
@@ -2131,124 +2128,124 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>294</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-    </row>
-    <row r="5" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A5" s="55" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+    </row>
+    <row r="5" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-    </row>
-    <row r="6" spans="1:9" ht="23.25" customHeight="1">
-      <c r="F6" s="53" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+    </row>
+    <row r="6" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F6" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-    </row>
-    <row r="7" spans="1:9" ht="21.6" customHeight="1">
-      <c r="A7" s="51" t="s">
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+    </row>
+    <row r="7" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-    </row>
-    <row r="8" spans="1:9" ht="26.45" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="57" t="s">
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+    </row>
+    <row r="8" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="60" t="s">
+      <c r="G8" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="61"/>
-    </row>
-    <row r="9" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="62" t="s">
+      <c r="H8" s="62"/>
+    </row>
+    <row r="9" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="62" t="s">
+      <c r="H9" s="63" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="21" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-    </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1">
+    <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>1</v>
       </c>
@@ -2272,7 +2269,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1">
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
         <v>30</v>
       </c>
@@ -2290,10 +2287,7 @@
         <f>E13+E21</f>
         <v>0</v>
       </c>
-      <c r="F12" s="31">
-        <f>E12+G12</f>
-        <v>0</v>
-      </c>
+      <c r="F12" s="31"/>
       <c r="G12" s="43">
         <f>G13+G21</f>
         <v>0</v>
@@ -2303,7 +2297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1">
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
         <v>33</v>
       </c>
@@ -2321,10 +2315,7 @@
         <f>E14+E15</f>
         <v>0</v>
       </c>
-      <c r="F13" s="28">
-        <f>E13+G13</f>
-        <v>0</v>
-      </c>
+      <c r="F13" s="28"/>
       <c r="G13" s="48">
         <f>G14+G15</f>
         <v>0</v>
@@ -2335,7 +2326,7 @@
       </c>
       <c r="I13" s="46"/>
     </row>
-    <row r="14" spans="1:9" s="7" customFormat="1">
+    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
         <v>36</v>
       </c>
@@ -2353,10 +2344,7 @@
         <f>E24-E21-E15</f>
         <v>0</v>
       </c>
-      <c r="F14" s="28">
-        <f t="shared" ref="F14:F77" si="1">E14+G14</f>
-        <v>0</v>
-      </c>
+      <c r="F14" s="28"/>
       <c r="G14" s="49">
         <f>G24-G21-G15</f>
         <v>0</v>
@@ -2367,7 +2355,7 @@
       </c>
       <c r="I14" s="47"/>
     </row>
-    <row r="15" spans="1:9" s="7" customFormat="1">
+    <row r="15" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>39</v>
       </c>
@@ -2385,10 +2373,7 @@
         <f>E16+E20</f>
         <v>0</v>
       </c>
-      <c r="F15" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F15" s="28"/>
       <c r="G15" s="49">
         <f>G16+G20</f>
         <v>0</v>
@@ -2398,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="8" customFormat="1">
+    <row r="16" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
         <v>42</v>
       </c>
@@ -2410,17 +2395,14 @@
       </c>
       <c r="D16" s="34"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F16" s="28"/>
       <c r="G16" s="49"/>
       <c r="H16" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="8" customFormat="1">
+    <row r="17" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
         <v>45</v>
       </c>
@@ -2432,17 +2414,14 @@
       </c>
       <c r="D17" s="34"/>
       <c r="E17" s="26"/>
-      <c r="F17" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F17" s="28"/>
       <c r="G17" s="50"/>
       <c r="H17" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="8" customFormat="1">
+    <row r="18" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>48</v>
       </c>
@@ -2454,17 +2433,14 @@
       </c>
       <c r="D18" s="34"/>
       <c r="E18" s="26"/>
-      <c r="F18" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F18" s="28"/>
       <c r="G18" s="50"/>
       <c r="H18" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="8" customFormat="1">
+    <row r="19" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
         <v>51</v>
       </c>
@@ -2476,17 +2452,14 @@
       </c>
       <c r="D19" s="34"/>
       <c r="E19" s="26"/>
-      <c r="F19" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F19" s="28"/>
       <c r="G19" s="50"/>
       <c r="H19" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="8" customFormat="1">
+    <row r="20" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
         <v>54</v>
       </c>
@@ -2498,17 +2471,14 @@
       </c>
       <c r="D20" s="34"/>
       <c r="E20" s="24"/>
-      <c r="F20" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F20" s="28"/>
       <c r="G20" s="49"/>
       <c r="H20" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
         <v>57</v>
       </c>
@@ -2526,10 +2496,7 @@
         <f>E22+E23</f>
         <v>0</v>
       </c>
-      <c r="F21" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F21" s="28"/>
       <c r="G21" s="49">
         <f>G22+G23</f>
         <v>0</v>
@@ -2539,7 +2506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="38" t="s">
         <v>60</v>
       </c>
@@ -2551,17 +2518,14 @@
       </c>
       <c r="D22" s="34"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F22" s="28"/>
       <c r="G22" s="49"/>
       <c r="H22" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
         <v>63</v>
       </c>
@@ -2573,17 +2537,14 @@
       </c>
       <c r="D23" s="34"/>
       <c r="E23" s="24"/>
-      <c r="F23" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F23" s="28"/>
       <c r="G23" s="49"/>
       <c r="H23" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="2" customFormat="1">
+    <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
         <v>66</v>
       </c>
@@ -2601,10 +2562,7 @@
         <f>E25+E60+E87</f>
         <v>0</v>
       </c>
-      <c r="F24" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F24" s="28"/>
       <c r="G24" s="49">
         <f>G25+G60+G87</f>
         <v>0</v>
@@ -2614,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="7" customFormat="1">
+    <row r="25" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
         <v>69</v>
       </c>
@@ -2632,10 +2590,7 @@
         <f>SUM(E26:E51)-E32-E47+E59</f>
         <v>0</v>
       </c>
-      <c r="F25" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F25" s="28"/>
       <c r="G25" s="49">
         <f>SUM(G26:G51)-G32-G47+G59</f>
         <v>0</v>
@@ -2645,7 +2600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
         <v>72</v>
       </c>
@@ -2657,17 +2612,14 @@
       </c>
       <c r="D26" s="34"/>
       <c r="E26" s="24"/>
-      <c r="F26" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F26" s="28"/>
       <c r="G26" s="24"/>
       <c r="H26" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="38" t="s">
         <v>75</v>
       </c>
@@ -2679,17 +2631,14 @@
       </c>
       <c r="D27" s="34"/>
       <c r="E27" s="26"/>
-      <c r="F27" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F27" s="28"/>
       <c r="G27" s="26"/>
       <c r="H27" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
         <v>78</v>
       </c>
@@ -2701,17 +2650,14 @@
       </c>
       <c r="D28" s="34"/>
       <c r="E28" s="26"/>
-      <c r="F28" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F28" s="28"/>
       <c r="G28" s="26"/>
       <c r="H28" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
         <v>81</v>
       </c>
@@ -2723,17 +2669,14 @@
       </c>
       <c r="D29" s="34"/>
       <c r="E29" s="24"/>
-      <c r="F29" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F29" s="28"/>
       <c r="G29" s="24"/>
       <c r="H29" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="38" t="s">
         <v>84</v>
       </c>
@@ -2745,17 +2688,14 @@
       </c>
       <c r="D30" s="34"/>
       <c r="E30" s="24"/>
-      <c r="F30" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F30" s="28"/>
       <c r="G30" s="26"/>
       <c r="H30" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="47.25">
+    <row r="31" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
         <v>87</v>
       </c>
@@ -2767,17 +2707,14 @@
       </c>
       <c r="D31" s="34"/>
       <c r="E31" s="24"/>
-      <c r="F31" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F31" s="28"/>
       <c r="G31" s="26"/>
       <c r="H31" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="38" t="s">
         <v>90</v>
       </c>
@@ -2789,17 +2726,14 @@
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="24"/>
-      <c r="F32" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F32" s="28"/>
       <c r="G32" s="26"/>
       <c r="H32" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
         <v>92</v>
       </c>
@@ -2811,17 +2745,14 @@
       </c>
       <c r="D33" s="34"/>
       <c r="E33" s="24"/>
-      <c r="F33" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F33" s="28"/>
       <c r="G33" s="25"/>
       <c r="H33" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
         <v>95</v>
       </c>
@@ -2833,17 +2764,14 @@
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="24"/>
-      <c r="F34" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F34" s="28"/>
       <c r="G34" s="26"/>
       <c r="H34" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="38" t="s">
         <v>98</v>
       </c>
@@ -2855,17 +2783,14 @@
       </c>
       <c r="D35" s="34"/>
       <c r="E35" s="24"/>
-      <c r="F35" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F35" s="28"/>
       <c r="G35" s="26"/>
       <c r="H35" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="38" t="s">
         <v>101</v>
       </c>
@@ -2877,17 +2802,14 @@
       </c>
       <c r="D36" s="34"/>
       <c r="E36" s="24"/>
-      <c r="F36" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F36" s="28"/>
       <c r="G36" s="26"/>
       <c r="H36" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="31.5">
+    <row r="37" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
         <v>104</v>
       </c>
@@ -2899,17 +2821,14 @@
       </c>
       <c r="D37" s="34"/>
       <c r="E37" s="24"/>
-      <c r="F37" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F37" s="28"/>
       <c r="G37" s="26"/>
       <c r="H37" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="31.5">
+    <row r="38" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
         <v>107</v>
       </c>
@@ -2921,17 +2840,14 @@
       </c>
       <c r="D38" s="34"/>
       <c r="E38" s="24"/>
-      <c r="F38" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F38" s="28"/>
       <c r="G38" s="26"/>
       <c r="H38" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="31.5">
+    <row r="39" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
         <v>110</v>
       </c>
@@ -2943,17 +2859,14 @@
       </c>
       <c r="D39" s="34"/>
       <c r="E39" s="24"/>
-      <c r="F39" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F39" s="28"/>
       <c r="G39" s="26"/>
       <c r="H39" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="38" t="s">
         <v>113</v>
       </c>
@@ -2965,17 +2878,14 @@
       </c>
       <c r="D40" s="34"/>
       <c r="E40" s="24"/>
-      <c r="F40" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F40" s="28"/>
       <c r="G40" s="26"/>
       <c r="H40" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
         <v>116</v>
       </c>
@@ -2987,17 +2897,14 @@
       </c>
       <c r="D41" s="34"/>
       <c r="E41" s="24"/>
-      <c r="F41" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F41" s="28"/>
       <c r="G41" s="26"/>
       <c r="H41" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="38" t="s">
         <v>119</v>
       </c>
@@ -3009,17 +2916,14 @@
       </c>
       <c r="D42" s="34"/>
       <c r="E42" s="24"/>
-      <c r="F42" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F42" s="28"/>
       <c r="G42" s="26"/>
       <c r="H42" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="38" t="s">
         <v>122</v>
       </c>
@@ -3031,17 +2935,14 @@
       </c>
       <c r="D43" s="34"/>
       <c r="E43" s="24"/>
-      <c r="F43" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F43" s="28"/>
       <c r="G43" s="26"/>
       <c r="H43" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="31.5">
+    <row r="44" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A44" s="38" t="s">
         <v>125</v>
       </c>
@@ -3053,17 +2954,14 @@
       </c>
       <c r="D44" s="34"/>
       <c r="E44" s="24"/>
-      <c r="F44" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F44" s="28"/>
       <c r="G44" s="26"/>
       <c r="H44" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="47.25">
+    <row r="45" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
         <v>128</v>
       </c>
@@ -3075,17 +2973,14 @@
       </c>
       <c r="D45" s="34"/>
       <c r="E45" s="24"/>
-      <c r="F45" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F45" s="28"/>
       <c r="G45" s="26"/>
       <c r="H45" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
         <v>131</v>
       </c>
@@ -3097,17 +2992,14 @@
       </c>
       <c r="D46" s="34"/>
       <c r="E46" s="24"/>
-      <c r="F46" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F46" s="28"/>
       <c r="G46" s="26"/>
       <c r="H46" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="38" t="s">
         <v>134</v>
       </c>
@@ -3119,17 +3011,14 @@
       </c>
       <c r="D47" s="34"/>
       <c r="E47" s="24"/>
-      <c r="F47" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F47" s="28"/>
       <c r="G47" s="26"/>
       <c r="H47" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="38" t="s">
         <v>137</v>
       </c>
@@ -3141,17 +3030,14 @@
       </c>
       <c r="D48" s="34"/>
       <c r="E48" s="24"/>
-      <c r="F48" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F48" s="28"/>
       <c r="G48" s="26"/>
       <c r="H48" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="31.5">
+    <row r="49" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
         <v>140</v>
       </c>
@@ -3163,17 +3049,14 @@
       </c>
       <c r="D49" s="34"/>
       <c r="E49" s="24"/>
-      <c r="F49" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F49" s="28"/>
       <c r="G49" s="26"/>
       <c r="H49" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="31.5">
+    <row r="50" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="38" t="s">
         <v>143</v>
       </c>
@@ -3185,17 +3068,14 @@
       </c>
       <c r="D50" s="34"/>
       <c r="E50" s="24"/>
-      <c r="F50" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F50" s="28"/>
       <c r="G50" s="26"/>
       <c r="H50" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="38" t="s">
         <v>146</v>
       </c>
@@ -3205,19 +3085,28 @@
       <c r="C51" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="D51" s="34"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="28">
+      <c r="D51" s="34">
+        <f>SUM(D52:D58)</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="49">
+        <f t="shared" ref="E51:G51" si="1">SUM(E52:E58)</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G51" s="26"/>
+      <c r="G51" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="H51" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
         <v>149</v>
       </c>
@@ -3229,17 +3118,14 @@
       </c>
       <c r="D52" s="34"/>
       <c r="E52" s="24"/>
-      <c r="F52" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F52" s="28"/>
       <c r="G52" s="26"/>
       <c r="H52" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
         <v>152</v>
       </c>
@@ -3251,17 +3137,14 @@
       </c>
       <c r="D53" s="34"/>
       <c r="E53" s="24"/>
-      <c r="F53" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F53" s="28"/>
       <c r="G53" s="26"/>
       <c r="H53" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="38" t="s">
         <v>155</v>
       </c>
@@ -3273,17 +3156,14 @@
       </c>
       <c r="D54" s="34"/>
       <c r="E54" s="24"/>
-      <c r="F54" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F54" s="28"/>
       <c r="G54" s="26"/>
       <c r="H54" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="38" t="s">
         <v>158</v>
       </c>
@@ -3295,17 +3175,14 @@
       </c>
       <c r="D55" s="34"/>
       <c r="E55" s="24"/>
-      <c r="F55" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F55" s="28"/>
       <c r="G55" s="26"/>
       <c r="H55" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="38" t="s">
         <v>161</v>
       </c>
@@ -3317,17 +3194,14 @@
       </c>
       <c r="D56" s="34"/>
       <c r="E56" s="24"/>
-      <c r="F56" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F56" s="28"/>
       <c r="G56" s="26"/>
       <c r="H56" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="38" t="s">
         <v>164</v>
       </c>
@@ -3339,17 +3213,14 @@
       </c>
       <c r="D57" s="34"/>
       <c r="E57" s="24"/>
-      <c r="F57" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F57" s="28"/>
       <c r="G57" s="26"/>
       <c r="H57" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="38" t="s">
         <v>167</v>
       </c>
@@ -3361,17 +3232,14 @@
       </c>
       <c r="D58" s="34"/>
       <c r="E58" s="24"/>
-      <c r="F58" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F58" s="28"/>
       <c r="G58" s="26"/>
       <c r="H58" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
         <v>170</v>
       </c>
@@ -3383,17 +3251,14 @@
       </c>
       <c r="D59" s="34"/>
       <c r="E59" s="24"/>
-      <c r="F59" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F59" s="28"/>
       <c r="G59" s="26"/>
       <c r="H59" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="38" t="s">
         <v>173</v>
       </c>
@@ -3411,10 +3276,7 @@
         <f>SUM(E61:E86)-E67-E82</f>
         <v>0</v>
       </c>
-      <c r="F60" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F60" s="51"/>
       <c r="G60" s="50">
         <f>SUM(G61:G86)-G67-G82</f>
         <v>0</v>
@@ -3424,7 +3286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="38" t="s">
         <v>176</v>
       </c>
@@ -3436,17 +3298,14 @@
       </c>
       <c r="D61" s="34"/>
       <c r="E61" s="24"/>
-      <c r="F61" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F61" s="28"/>
       <c r="G61" s="26"/>
       <c r="H61" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="38" t="s">
         <v>178</v>
       </c>
@@ -3458,17 +3317,14 @@
       </c>
       <c r="D62" s="34"/>
       <c r="E62" s="24"/>
-      <c r="F62" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F62" s="28"/>
       <c r="G62" s="26"/>
       <c r="H62" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="38" t="s">
         <v>180</v>
       </c>
@@ -3480,17 +3336,14 @@
       </c>
       <c r="D63" s="34"/>
       <c r="E63" s="24"/>
-      <c r="F63" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F63" s="28"/>
       <c r="G63" s="26"/>
       <c r="H63" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="38" t="s">
         <v>182</v>
       </c>
@@ -3502,17 +3355,14 @@
       </c>
       <c r="D64" s="34"/>
       <c r="E64" s="24"/>
-      <c r="F64" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F64" s="28"/>
       <c r="G64" s="26"/>
       <c r="H64" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="38" t="s">
         <v>184</v>
       </c>
@@ -3524,17 +3374,14 @@
       </c>
       <c r="D65" s="34"/>
       <c r="E65" s="24"/>
-      <c r="F65" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F65" s="28"/>
       <c r="G65" s="26"/>
       <c r="H65" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="47.25">
+    <row r="66" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A66" s="38" t="s">
         <v>186</v>
       </c>
@@ -3546,17 +3393,14 @@
       </c>
       <c r="D66" s="34"/>
       <c r="E66" s="24"/>
-      <c r="F66" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F66" s="28"/>
       <c r="G66" s="26"/>
       <c r="H66" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="38" t="s">
         <v>188</v>
       </c>
@@ -3568,17 +3412,14 @@
       </c>
       <c r="D67" s="34"/>
       <c r="E67" s="24"/>
-      <c r="F67" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F67" s="28"/>
       <c r="G67" s="26"/>
       <c r="H67" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="38" t="s">
         <v>190</v>
       </c>
@@ -3590,17 +3431,14 @@
       </c>
       <c r="D68" s="34"/>
       <c r="E68" s="24"/>
-      <c r="F68" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F68" s="28"/>
       <c r="G68" s="26"/>
       <c r="H68" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
         <v>192</v>
       </c>
@@ -3612,17 +3450,14 @@
       </c>
       <c r="D69" s="34"/>
       <c r="E69" s="24"/>
-      <c r="F69" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F69" s="28"/>
       <c r="G69" s="26"/>
       <c r="H69" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="38" t="s">
         <v>194</v>
       </c>
@@ -3634,17 +3469,14 @@
       </c>
       <c r="D70" s="34"/>
       <c r="E70" s="24"/>
-      <c r="F70" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F70" s="28"/>
       <c r="G70" s="26"/>
       <c r="H70" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="38" t="s">
         <v>196</v>
       </c>
@@ -3656,17 +3488,14 @@
       </c>
       <c r="D71" s="34"/>
       <c r="E71" s="24"/>
-      <c r="F71" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F71" s="28"/>
       <c r="G71" s="26"/>
       <c r="H71" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="31.5">
+    <row r="72" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A72" s="38" t="s">
         <v>198</v>
       </c>
@@ -3678,17 +3507,14 @@
       </c>
       <c r="D72" s="34"/>
       <c r="E72" s="24"/>
-      <c r="F72" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F72" s="28"/>
       <c r="G72" s="26"/>
       <c r="H72" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="31.5">
+    <row r="73" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A73" s="38" t="s">
         <v>200</v>
       </c>
@@ -3700,17 +3526,14 @@
       </c>
       <c r="D73" s="34"/>
       <c r="E73" s="24"/>
-      <c r="F73" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F73" s="28"/>
       <c r="G73" s="26"/>
       <c r="H73" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="31.5">
+    <row r="74" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="38" t="s">
         <v>202</v>
       </c>
@@ -3722,17 +3545,14 @@
       </c>
       <c r="D74" s="34"/>
       <c r="E74" s="24"/>
-      <c r="F74" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F74" s="28"/>
       <c r="G74" s="26"/>
       <c r="H74" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="38" t="s">
         <v>204</v>
       </c>
@@ -3744,17 +3564,14 @@
       </c>
       <c r="D75" s="34"/>
       <c r="E75" s="24"/>
-      <c r="F75" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F75" s="28"/>
       <c r="G75" s="26"/>
       <c r="H75" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="38" t="s">
         <v>206</v>
       </c>
@@ -3766,17 +3583,14 @@
       </c>
       <c r="D76" s="34"/>
       <c r="E76" s="24"/>
-      <c r="F76" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F76" s="28"/>
       <c r="G76" s="26"/>
       <c r="H76" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="38" t="s">
         <v>208</v>
       </c>
@@ -3788,17 +3602,14 @@
       </c>
       <c r="D77" s="34"/>
       <c r="E77" s="24"/>
-      <c r="F77" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F77" s="28"/>
       <c r="G77" s="26"/>
       <c r="H77" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="38" t="s">
         <v>210</v>
       </c>
@@ -3810,17 +3621,14 @@
       </c>
       <c r="D78" s="34"/>
       <c r="E78" s="24"/>
-      <c r="F78" s="28">
-        <f t="shared" ref="F78:F108" si="2">E78+G78</f>
-        <v>0</v>
-      </c>
+      <c r="F78" s="28"/>
       <c r="G78" s="26"/>
       <c r="H78" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="31.5">
+    <row r="79" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
         <v>212</v>
       </c>
@@ -3832,17 +3640,14 @@
       </c>
       <c r="D79" s="34"/>
       <c r="E79" s="24"/>
-      <c r="F79" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F79" s="28"/>
       <c r="G79" s="26"/>
       <c r="H79" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="47.25">
+    <row r="80" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A80" s="38" t="s">
         <v>214</v>
       </c>
@@ -3854,17 +3659,14 @@
       </c>
       <c r="D80" s="34"/>
       <c r="E80" s="24"/>
-      <c r="F80" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F80" s="28"/>
       <c r="G80" s="26"/>
       <c r="H80" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="38" t="s">
         <v>216</v>
       </c>
@@ -3876,17 +3678,14 @@
       </c>
       <c r="D81" s="34"/>
       <c r="E81" s="24"/>
-      <c r="F81" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F81" s="28"/>
       <c r="G81" s="26"/>
       <c r="H81" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="38" t="s">
         <v>218</v>
       </c>
@@ -3898,17 +3697,14 @@
       </c>
       <c r="D82" s="34"/>
       <c r="E82" s="24"/>
-      <c r="F82" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F82" s="28"/>
       <c r="G82" s="26"/>
       <c r="H82" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="38" t="s">
         <v>220</v>
       </c>
@@ -3920,17 +3716,14 @@
       </c>
       <c r="D83" s="34"/>
       <c r="E83" s="24"/>
-      <c r="F83" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F83" s="28"/>
       <c r="G83" s="26"/>
       <c r="H83" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="31.5">
+    <row r="84" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A84" s="38" t="s">
         <v>222</v>
       </c>
@@ -3942,17 +3735,14 @@
       </c>
       <c r="D84" s="34"/>
       <c r="E84" s="24"/>
-      <c r="F84" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F84" s="28"/>
       <c r="G84" s="26"/>
       <c r="H84" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="31.5">
+    <row r="85" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" s="38" t="s">
         <v>224</v>
       </c>
@@ -3964,17 +3754,14 @@
       </c>
       <c r="D85" s="34"/>
       <c r="E85" s="24"/>
-      <c r="F85" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F85" s="28"/>
       <c r="G85" s="26"/>
       <c r="H85" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="38" t="s">
         <v>226</v>
       </c>
@@ -3986,17 +3773,14 @@
       </c>
       <c r="D86" s="34"/>
       <c r="E86" s="24"/>
-      <c r="F86" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F86" s="28"/>
       <c r="G86" s="26"/>
       <c r="H86" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="38" t="s">
         <v>228</v>
       </c>
@@ -4008,17 +3792,14 @@
       </c>
       <c r="D87" s="34"/>
       <c r="E87" s="24"/>
-      <c r="F87" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F87" s="28"/>
       <c r="G87" s="26"/>
       <c r="H87" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="38" t="s">
         <v>231</v>
       </c>
@@ -4030,17 +3811,14 @@
       </c>
       <c r="D88" s="34"/>
       <c r="E88" s="24"/>
-      <c r="F88" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F88" s="28"/>
       <c r="G88" s="26"/>
       <c r="H88" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="38" t="s">
         <v>234</v>
       </c>
@@ -4052,17 +3830,14 @@
       </c>
       <c r="D89" s="34"/>
       <c r="E89" s="24"/>
-      <c r="F89" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F89" s="28"/>
       <c r="G89" s="26"/>
       <c r="H89" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="38" t="s">
         <v>237</v>
       </c>
@@ -4074,17 +3849,14 @@
       </c>
       <c r="D90" s="34"/>
       <c r="E90" s="24"/>
-      <c r="F90" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F90" s="28"/>
       <c r="G90" s="26"/>
       <c r="H90" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="38" t="s">
         <v>240</v>
       </c>
@@ -4096,17 +3868,14 @@
       </c>
       <c r="D91" s="34"/>
       <c r="E91" s="24"/>
-      <c r="F91" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F91" s="28"/>
       <c r="G91" s="26"/>
       <c r="H91" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="38" t="s">
         <v>243</v>
       </c>
@@ -4118,17 +3887,14 @@
       </c>
       <c r="D92" s="34"/>
       <c r="E92" s="24"/>
-      <c r="F92" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F92" s="28"/>
       <c r="G92" s="26"/>
       <c r="H92" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="38" t="s">
         <v>246</v>
       </c>
@@ -4140,17 +3906,14 @@
       </c>
       <c r="D93" s="34"/>
       <c r="E93" s="24"/>
-      <c r="F93" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F93" s="28"/>
       <c r="G93" s="26"/>
       <c r="H93" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="38" t="s">
         <v>249</v>
       </c>
@@ -4162,17 +3925,14 @@
       </c>
       <c r="D94" s="34"/>
       <c r="E94" s="24"/>
-      <c r="F94" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F94" s="28"/>
       <c r="G94" s="26"/>
       <c r="H94" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="38" t="s">
         <v>252</v>
       </c>
@@ -4184,17 +3944,14 @@
       </c>
       <c r="D95" s="34"/>
       <c r="E95" s="24"/>
-      <c r="F95" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F95" s="28"/>
       <c r="G95" s="26"/>
       <c r="H95" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="38" t="s">
         <v>255</v>
       </c>
@@ -4206,17 +3963,14 @@
       </c>
       <c r="D96" s="34"/>
       <c r="E96" s="24"/>
-      <c r="F96" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F96" s="28"/>
       <c r="G96" s="26"/>
       <c r="H96" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="38" t="s">
         <v>258</v>
       </c>
@@ -4228,17 +3982,14 @@
       </c>
       <c r="D97" s="34"/>
       <c r="E97" s="24"/>
-      <c r="F97" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F97" s="28"/>
       <c r="G97" s="26"/>
       <c r="H97" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="38" t="s">
         <v>261</v>
       </c>
@@ -4250,17 +4001,14 @@
       </c>
       <c r="D98" s="34"/>
       <c r="E98" s="24"/>
-      <c r="F98" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F98" s="28"/>
       <c r="G98" s="26"/>
       <c r="H98" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="38" t="s">
         <v>264</v>
       </c>
@@ -4272,17 +4020,14 @@
       </c>
       <c r="D99" s="34"/>
       <c r="E99" s="24"/>
-      <c r="F99" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F99" s="28"/>
       <c r="G99" s="26"/>
       <c r="H99" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="38" t="s">
         <v>267</v>
       </c>
@@ -4294,17 +4039,14 @@
       </c>
       <c r="D100" s="34"/>
       <c r="E100" s="24"/>
-      <c r="F100" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F100" s="28"/>
       <c r="G100" s="26"/>
       <c r="H100" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
         <v>270</v>
       </c>
@@ -4316,17 +4058,14 @@
       </c>
       <c r="D101" s="34"/>
       <c r="E101" s="24"/>
-      <c r="F101" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F101" s="28"/>
       <c r="G101" s="26"/>
       <c r="H101" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="38" t="s">
         <v>273</v>
       </c>
@@ -4338,17 +4077,14 @@
       </c>
       <c r="D102" s="34"/>
       <c r="E102" s="24"/>
-      <c r="F102" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F102" s="28"/>
       <c r="G102" s="26"/>
       <c r="H102" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="38" t="s">
         <v>276</v>
       </c>
@@ -4360,17 +4096,14 @@
       </c>
       <c r="D103" s="34"/>
       <c r="E103" s="24"/>
-      <c r="F103" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F103" s="28"/>
       <c r="G103" s="26"/>
       <c r="H103" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="38" t="s">
         <v>279</v>
       </c>
@@ -4382,17 +4115,14 @@
       </c>
       <c r="D104" s="34"/>
       <c r="E104" s="24"/>
-      <c r="F104" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F104" s="28"/>
       <c r="G104" s="26"/>
       <c r="H104" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="38" t="s">
         <v>282</v>
       </c>
@@ -4404,17 +4134,14 @@
       </c>
       <c r="D105" s="34"/>
       <c r="E105" s="24"/>
-      <c r="F105" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F105" s="28"/>
       <c r="G105" s="26"/>
       <c r="H105" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="38" t="s">
         <v>285</v>
       </c>
@@ -4426,17 +4153,14 @@
       </c>
       <c r="D106" s="34"/>
       <c r="E106" s="24"/>
-      <c r="F106" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F106" s="28"/>
       <c r="G106" s="26"/>
       <c r="H106" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="38" t="s">
         <v>288</v>
       </c>
@@ -4448,17 +4172,14 @@
       </c>
       <c r="D107" s="34"/>
       <c r="E107" s="24"/>
-      <c r="F107" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F107" s="28"/>
       <c r="G107" s="26"/>
       <c r="H107" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="38" t="s">
         <v>291</v>
       </c>
@@ -4470,17 +4191,14 @@
       </c>
       <c r="D108" s="34"/>
       <c r="E108" s="24"/>
-      <c r="F108" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="F108" s="28"/>
       <c r="G108" s="26"/>
       <c r="H108" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="38"/>
       <c r="B109" s="41"/>
       <c r="C109" s="19"/>
@@ -4490,7 +4208,7 @@
       <c r="G109" s="26"/>
       <c r="H109" s="29"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="38"/>
       <c r="B110" s="41"/>
       <c r="C110" s="21"/>
@@ -4500,7 +4218,7 @@
       <c r="G110" s="26"/>
       <c r="H110" s="29"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="38"/>
       <c r="B111" s="41"/>
       <c r="C111" s="21"/>
@@ -4510,7 +4228,7 @@
       <c r="G111" s="26"/>
       <c r="H111" s="29"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="38"/>
       <c r="B112" s="41"/>
       <c r="C112" s="21"/>
@@ -4520,7 +4238,7 @@
       <c r="G112" s="26"/>
       <c r="H112" s="29"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="38"/>
       <c r="B113" s="41"/>
       <c r="C113" s="21"/>
@@ -4530,7 +4248,7 @@
       <c r="G113" s="26"/>
       <c r="H113" s="29"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="38"/>
       <c r="B114" s="41"/>
       <c r="C114" s="21"/>
@@ -4540,7 +4258,7 @@
       <c r="G114" s="26"/>
       <c r="H114" s="29"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="38"/>
       <c r="B115" s="41"/>
       <c r="C115" s="21"/>
@@ -4550,7 +4268,7 @@
       <c r="G115" s="26"/>
       <c r="H115" s="29"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="38"/>
       <c r="B116" s="41"/>
       <c r="C116" s="21"/>
@@ -4560,7 +4278,7 @@
       <c r="G116" s="26"/>
       <c r="H116" s="29"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="38"/>
       <c r="B117" s="41"/>
       <c r="C117" s="21"/>
@@ -4570,7 +4288,7 @@
       <c r="G117" s="26"/>
       <c r="H117" s="29"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="38"/>
       <c r="B118" s="41"/>
       <c r="C118" s="21"/>
@@ -4580,7 +4298,7 @@
       <c r="G118" s="26"/>
       <c r="H118" s="29"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="38"/>
       <c r="B119" s="41"/>
       <c r="C119" s="21"/>
@@ -4590,7 +4308,7 @@
       <c r="G119" s="26"/>
       <c r="H119" s="29"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="38"/>
       <c r="B120" s="41"/>
       <c r="C120" s="21"/>
@@ -4600,7 +4318,7 @@
       <c r="G120" s="26"/>
       <c r="H120" s="29"/>
     </row>
-    <row r="121" spans="1:8" s="9" customFormat="1">
+    <row r="121" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="38"/>
       <c r="B121" s="41"/>
       <c r="C121" s="21"/>
@@ -4610,7 +4328,7 @@
       <c r="G121" s="26"/>
       <c r="H121" s="29"/>
     </row>
-    <row r="122" spans="1:8" s="9" customFormat="1">
+    <row r="122" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="38"/>
       <c r="B122" s="41"/>
       <c r="C122" s="21"/>
@@ -4620,7 +4338,7 @@
       <c r="G122" s="26"/>
       <c r="H122" s="29"/>
     </row>
-    <row r="123" spans="1:8" s="9" customFormat="1">
+    <row r="123" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="38"/>
       <c r="B123" s="41"/>
       <c r="C123" s="21"/>
@@ -4630,7 +4348,7 @@
       <c r="G123" s="26"/>
       <c r="H123" s="29"/>
     </row>
-    <row r="124" spans="1:8" s="9" customFormat="1">
+    <row r="124" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="38"/>
       <c r="B124" s="41"/>
       <c r="C124" s="21"/>
@@ -4640,7 +4358,7 @@
       <c r="G124" s="26"/>
       <c r="H124" s="29"/>
     </row>
-    <row r="125" spans="1:8" s="9" customFormat="1">
+    <row r="125" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="38"/>
       <c r="B125" s="41"/>
       <c r="C125" s="21"/>
@@ -4650,7 +4368,7 @@
       <c r="G125" s="26"/>
       <c r="H125" s="29"/>
     </row>
-    <row r="126" spans="1:8" s="9" customFormat="1">
+    <row r="126" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="38"/>
       <c r="B126" s="41"/>
       <c r="C126" s="21"/>
@@ -4660,7 +4378,7 @@
       <c r="G126" s="26"/>
       <c r="H126" s="29"/>
     </row>
-    <row r="127" spans="1:8" s="9" customFormat="1">
+    <row r="127" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="38"/>
       <c r="B127" s="41"/>
       <c r="C127" s="21"/>
@@ -4670,7 +4388,7 @@
       <c r="G127" s="26"/>
       <c r="H127" s="29"/>
     </row>
-    <row r="128" spans="1:8" s="9" customFormat="1">
+    <row r="128" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="38"/>
       <c r="B128" s="41"/>
       <c r="C128" s="19"/>
@@ -4680,7 +4398,7 @@
       <c r="G128" s="26"/>
       <c r="H128" s="29"/>
     </row>
-    <row r="129" spans="1:8" s="7" customFormat="1">
+    <row r="129" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="38"/>
       <c r="B129" s="41"/>
       <c r="C129" s="20"/>
@@ -4690,7 +4408,7 @@
       <c r="G129" s="24"/>
       <c r="H129" s="29"/>
     </row>
-    <row r="130" spans="1:8" s="7" customFormat="1">
+    <row r="130" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="38"/>
       <c r="B130" s="41"/>
       <c r="C130" s="19"/>
@@ -4700,7 +4418,7 @@
       <c r="G130" s="24"/>
       <c r="H130" s="29"/>
     </row>
-    <row r="131" spans="1:8" s="7" customFormat="1">
+    <row r="131" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="38"/>
       <c r="B131" s="41"/>
       <c r="C131" s="19"/>
@@ -4710,7 +4428,7 @@
       <c r="G131" s="24"/>
       <c r="H131" s="29"/>
     </row>
-    <row r="132" spans="1:8" s="7" customFormat="1">
+    <row r="132" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="38"/>
       <c r="B132" s="41"/>
       <c r="C132" s="21"/>
@@ -4720,7 +4438,7 @@
       <c r="G132" s="24"/>
       <c r="H132" s="29"/>
     </row>
-    <row r="133" spans="1:8" s="7" customFormat="1">
+    <row r="133" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="38"/>
       <c r="B133" s="41"/>
       <c r="C133" s="21"/>
@@ -4730,7 +4448,7 @@
       <c r="G133" s="24"/>
       <c r="H133" s="29"/>
     </row>
-    <row r="134" spans="1:8" s="7" customFormat="1">
+    <row r="134" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="38"/>
       <c r="B134" s="41"/>
       <c r="C134" s="19"/>
@@ -4740,7 +4458,7 @@
       <c r="G134" s="24"/>
       <c r="H134" s="29"/>
     </row>
-    <row r="135" spans="1:8" s="7" customFormat="1">
+    <row r="135" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="38"/>
       <c r="B135" s="41"/>
       <c r="C135" s="21"/>
@@ -4750,7 +4468,7 @@
       <c r="G135" s="24"/>
       <c r="H135" s="29"/>
     </row>
-    <row r="136" spans="1:8" s="7" customFormat="1">
+    <row r="136" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="38"/>
       <c r="B136" s="41"/>
       <c r="C136" s="22"/>
@@ -4760,7 +4478,7 @@
       <c r="G136" s="24"/>
       <c r="H136" s="29"/>
     </row>
-    <row r="137" spans="1:8" s="7" customFormat="1">
+    <row r="137" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="38"/>
       <c r="B137" s="41"/>
       <c r="C137" s="21"/>
@@ -4770,7 +4488,7 @@
       <c r="G137" s="24"/>
       <c r="H137" s="29"/>
     </row>
-    <row r="138" spans="1:8" s="7" customFormat="1">
+    <row r="138" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="38"/>
       <c r="B138" s="41"/>
       <c r="C138" s="21"/>
@@ -4780,7 +4498,7 @@
       <c r="G138" s="24"/>
       <c r="H138" s="29"/>
     </row>
-    <row r="139" spans="1:8" s="7" customFormat="1">
+    <row r="139" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="38"/>
       <c r="B139" s="41"/>
       <c r="C139" s="21"/>
@@ -4790,7 +4508,7 @@
       <c r="G139" s="24"/>
       <c r="H139" s="29"/>
     </row>
-    <row r="140" spans="1:8" s="7" customFormat="1">
+    <row r="140" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="38"/>
       <c r="B140" s="41"/>
       <c r="C140" s="21"/>
@@ -4800,7 +4518,7 @@
       <c r="G140" s="24"/>
       <c r="H140" s="29"/>
     </row>
-    <row r="141" spans="1:8" s="7" customFormat="1">
+    <row r="141" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="38"/>
       <c r="B141" s="41"/>
       <c r="C141" s="21"/>
@@ -4810,7 +4528,7 @@
       <c r="G141" s="24"/>
       <c r="H141" s="29"/>
     </row>
-    <row r="142" spans="1:8" s="7" customFormat="1">
+    <row r="142" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="38"/>
       <c r="B142" s="41"/>
       <c r="C142" s="21"/>
@@ -4820,7 +4538,7 @@
       <c r="G142" s="24"/>
       <c r="H142" s="29"/>
     </row>
-    <row r="143" spans="1:8" s="7" customFormat="1">
+    <row r="143" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="38"/>
       <c r="B143" s="41"/>
       <c r="C143" s="21"/>
@@ -4830,7 +4548,7 @@
       <c r="G143" s="24"/>
       <c r="H143" s="29"/>
     </row>
-    <row r="144" spans="1:8" s="7" customFormat="1">
+    <row r="144" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="38"/>
       <c r="B144" s="41"/>
       <c r="C144" s="21"/>
@@ -4840,7 +4558,7 @@
       <c r="G144" s="24"/>
       <c r="H144" s="29"/>
     </row>
-    <row r="145" spans="1:8" s="7" customFormat="1">
+    <row r="145" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="38"/>
       <c r="B145" s="41"/>
       <c r="C145" s="21"/>
@@ -4850,7 +4568,7 @@
       <c r="G145" s="24"/>
       <c r="H145" s="29"/>
     </row>
-    <row r="146" spans="1:8" s="7" customFormat="1">
+    <row r="146" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="38"/>
       <c r="B146" s="41"/>
       <c r="C146" s="21"/>
@@ -4860,7 +4578,7 @@
       <c r="G146" s="24"/>
       <c r="H146" s="29"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="38"/>
       <c r="B147" s="41"/>
       <c r="C147" s="21"/>
@@ -4870,7 +4588,7 @@
       <c r="G147" s="24"/>
       <c r="H147" s="29"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="38"/>
       <c r="B148" s="41"/>
       <c r="C148" s="21"/>
@@ -4880,7 +4598,7 @@
       <c r="G148" s="24"/>
       <c r="H148" s="29"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="38"/>
       <c r="B149" s="41"/>
       <c r="C149" s="21"/>
@@ -4890,7 +4608,7 @@
       <c r="G149" s="24"/>
       <c r="H149" s="29"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="38"/>
       <c r="B150" s="41"/>
       <c r="C150" s="21"/>
@@ -4900,7 +4618,7 @@
       <c r="G150" s="24"/>
       <c r="H150" s="29"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="38"/>
       <c r="B151" s="41"/>
       <c r="C151" s="21"/>
@@ -4910,7 +4628,7 @@
       <c r="G151" s="24"/>
       <c r="H151" s="29"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="38"/>
       <c r="B152" s="41"/>
       <c r="C152" s="21"/>
@@ -4920,7 +4638,7 @@
       <c r="G152" s="24"/>
       <c r="H152" s="29"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="38"/>
       <c r="B153" s="41"/>
       <c r="C153" s="21"/>
@@ -4930,7 +4648,7 @@
       <c r="G153" s="24"/>
       <c r="H153" s="29"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="38"/>
       <c r="B154" s="41"/>
       <c r="C154" s="21"/>
@@ -4940,7 +4658,7 @@
       <c r="G154" s="24"/>
       <c r="H154" s="29"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="38"/>
       <c r="B155" s="41"/>
       <c r="C155" s="21"/>
@@ -4950,7 +4668,7 @@
       <c r="G155" s="24"/>
       <c r="H155" s="29"/>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="38"/>
       <c r="B156" s="41"/>
       <c r="C156" s="21"/>
@@ -4960,7 +4678,7 @@
       <c r="G156" s="24"/>
       <c r="H156" s="29"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="38"/>
       <c r="B157" s="41"/>
       <c r="C157" s="21"/>
@@ -4970,7 +4688,7 @@
       <c r="G157" s="24"/>
       <c r="H157" s="29"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="38"/>
       <c r="B158" s="41"/>
       <c r="C158" s="21"/>
@@ -4980,7 +4698,7 @@
       <c r="G158" s="24"/>
       <c r="H158" s="29"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="38"/>
       <c r="B159" s="41"/>
       <c r="C159" s="21"/>
@@ -4990,7 +4708,7 @@
       <c r="G159" s="24"/>
       <c r="H159" s="29"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="38"/>
       <c r="B160" s="41"/>
       <c r="C160" s="21"/>
@@ -5000,7 +4718,7 @@
       <c r="G160" s="24"/>
       <c r="H160" s="29"/>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="38"/>
       <c r="B161" s="41"/>
       <c r="C161" s="21"/>
@@ -5010,7 +4728,7 @@
       <c r="G161" s="24"/>
       <c r="H161" s="29"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="38"/>
       <c r="B162" s="41"/>
       <c r="C162" s="21"/>
@@ -5020,7 +4738,7 @@
       <c r="G162" s="24"/>
       <c r="H162" s="29"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="38"/>
       <c r="B163" s="41"/>
       <c r="C163" s="21"/>
@@ -5030,7 +4748,7 @@
       <c r="G163" s="24"/>
       <c r="H163" s="29"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="38"/>
       <c r="B164" s="41"/>
       <c r="C164" s="21"/>
@@ -5040,7 +4758,7 @@
       <c r="G164" s="26"/>
       <c r="H164" s="29"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="38"/>
       <c r="B165" s="41"/>
       <c r="C165" s="21"/>
@@ -5050,7 +4768,7 @@
       <c r="G165" s="26"/>
       <c r="H165" s="29"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="38"/>
       <c r="B166" s="41"/>
       <c r="C166" s="21"/>
@@ -5060,7 +4778,7 @@
       <c r="G166" s="26"/>
       <c r="H166" s="29"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="38"/>
       <c r="B167" s="41"/>
       <c r="C167" s="21"/>
@@ -5070,7 +4788,7 @@
       <c r="G167" s="26"/>
       <c r="H167" s="29"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="38"/>
       <c r="B168" s="41"/>
       <c r="C168" s="21"/>
@@ -5080,7 +4798,7 @@
       <c r="G168" s="26"/>
       <c r="H168" s="29"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="38"/>
       <c r="B169" s="41"/>
       <c r="C169" s="21"/>
@@ -5090,7 +4808,7 @@
       <c r="G169" s="26"/>
       <c r="H169" s="29"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="38"/>
       <c r="B170" s="41"/>
       <c r="C170" s="21"/>
@@ -5100,7 +4818,7 @@
       <c r="G170" s="26"/>
       <c r="H170" s="29"/>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="38"/>
       <c r="B171" s="41"/>
       <c r="C171" s="21"/>
@@ -5110,7 +4828,7 @@
       <c r="G171" s="26"/>
       <c r="H171" s="29"/>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="38"/>
       <c r="B172" s="41"/>
       <c r="C172" s="21"/>
@@ -5120,7 +4838,7 @@
       <c r="G172" s="26"/>
       <c r="H172" s="29"/>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="38"/>
       <c r="B173" s="41"/>
       <c r="C173" s="21"/>
@@ -5130,7 +4848,7 @@
       <c r="G173" s="26"/>
       <c r="H173" s="29"/>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="38"/>
       <c r="B174" s="41"/>
       <c r="C174" s="21"/>
@@ -5140,7 +4858,7 @@
       <c r="G174" s="26"/>
       <c r="H174" s="29"/>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="38"/>
       <c r="B175" s="41"/>
       <c r="C175" s="21"/>
@@ -5150,7 +4868,7 @@
       <c r="G175" s="26"/>
       <c r="H175" s="29"/>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="38"/>
       <c r="B176" s="41"/>
       <c r="C176" s="21"/>
@@ -5160,7 +4878,7 @@
       <c r="G176" s="26"/>
       <c r="H176" s="29"/>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="38"/>
       <c r="B177" s="41"/>
       <c r="C177" s="21"/>
@@ -5170,7 +4888,7 @@
       <c r="G177" s="26"/>
       <c r="H177" s="29"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="38"/>
       <c r="B178" s="41"/>
       <c r="C178" s="21"/>
@@ -5180,7 +4898,7 @@
       <c r="G178" s="24"/>
       <c r="H178" s="29"/>
     </row>
-    <row r="179" spans="1:8" s="7" customFormat="1">
+    <row r="179" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="38"/>
       <c r="B179" s="41"/>
       <c r="C179" s="21"/>
@@ -5190,7 +4908,7 @@
       <c r="G179" s="24"/>
       <c r="H179" s="29"/>
     </row>
-    <row r="180" spans="1:8" s="7" customFormat="1">
+    <row r="180" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="38"/>
       <c r="B180" s="41"/>
       <c r="C180" s="21"/>
@@ -5200,7 +4918,7 @@
       <c r="G180" s="24"/>
       <c r="H180" s="29"/>
     </row>
-    <row r="181" spans="1:8" s="7" customFormat="1">
+    <row r="181" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="38"/>
       <c r="B181" s="41"/>
       <c r="C181" s="21"/>
@@ -5210,7 +4928,7 @@
       <c r="G181" s="24"/>
       <c r="H181" s="29"/>
     </row>
-    <row r="182" spans="1:8" s="7" customFormat="1">
+    <row r="182" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="38"/>
       <c r="B182" s="41"/>
       <c r="C182" s="21"/>
@@ -5220,7 +4938,7 @@
       <c r="G182" s="26"/>
       <c r="H182" s="29"/>
     </row>
-    <row r="183" spans="1:8" s="7" customFormat="1">
+    <row r="183" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="38"/>
       <c r="B183" s="41"/>
       <c r="C183" s="21"/>
@@ -5230,7 +4948,7 @@
       <c r="G183" s="26"/>
       <c r="H183" s="29"/>
     </row>
-    <row r="184" spans="1:8" s="7" customFormat="1">
+    <row r="184" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="38"/>
       <c r="B184" s="41"/>
       <c r="C184" s="21"/>
@@ -5240,7 +4958,7 @@
       <c r="G184" s="24"/>
       <c r="H184" s="29"/>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="39"/>
       <c r="B185" s="42"/>
       <c r="C185" s="23"/>
@@ -5250,14 +4968,14 @@
       <c r="G185" s="27"/>
       <c r="H185" s="30"/>
     </row>
-    <row r="186" spans="1:8" ht="12" customHeight="1">
+    <row r="186" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="10"/>
       <c r="B186" s="13"/>
       <c r="C186" s="11"/>
       <c r="D186" s="11"/>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8" ht="12" customHeight="1">
+    <row r="187" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="10"/>
       <c r="B187" s="13"/>
       <c r="C187" s="2" t="s">
@@ -5265,47 +4983,47 @@
       </c>
       <c r="H187" s="7"/>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
       <c r="C188" s="12"/>
       <c r="D188" s="12"/>
-      <c r="E188" s="53" t="s">
+      <c r="E188" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="F188" s="53"/>
-      <c r="G188" s="53"/>
-      <c r="H188" s="53"/>
-    </row>
-    <row r="189" spans="1:8" ht="19.5" customHeight="1">
+      <c r="F188" s="54"/>
+      <c r="G188" s="54"/>
+      <c r="H188" s="54"/>
+    </row>
+    <row r="189" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D189" s="3"/>
-      <c r="E189" s="56" t="s">
+      <c r="E189" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F189" s="56"/>
-      <c r="G189" s="56"/>
-      <c r="H189" s="56"/>
-    </row>
-    <row r="190" spans="1:8">
+      <c r="F189" s="57"/>
+      <c r="G189" s="57"/>
+      <c r="H189" s="57"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="11"/>
       <c r="B190" s="11"/>
       <c r="C190" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D190" s="11"/>
-      <c r="E190" s="53" t="s">
+      <c r="E190" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F190" s="53"/>
-      <c r="G190" s="53"/>
-      <c r="H190" s="53"/>
-    </row>
-    <row r="191" spans="1:8" ht="18" customHeight="1">
+      <c r="F190" s="54"/>
+      <c r="G190" s="54"/>
+      <c r="H190" s="54"/>
+    </row>
+    <row r="191" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5314,42 +5032,42 @@
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
     </row>
-    <row r="194" spans="3:3">
+    <row r="194" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C194" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="3:3" ht="30.6" customHeight="1">
+    <row r="195" spans="3:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="3:3">
+    <row r="196" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C196" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="3:3">
+    <row r="197" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C197" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="3:3">
+    <row r="198" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C198" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="3:3">
+    <row r="199" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C199" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="3:3">
+    <row r="200" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C200" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="204" spans="3:3">
+    <row r="204" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
     </row>
   </sheetData>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cap nhat CN\IMS_REPORT KHNV - New\EXCEL_TEMPLATE\KHNV\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11280"/>
+    <workbookView xWindow="1992" yWindow="-120" windowWidth="19440" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="BIEU 02 -2022" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'BIEU 02 -2022'!$A$1:$H$190</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'BIEU 02 -2022'!$A$1:$H$192</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BIEU 02 -2022'!$7:$11</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="254">
   <si>
     <t>Biểu số 02/NHCS-KH</t>
   </si>
@@ -618,348 +623,207 @@
     <t>XD00038</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>XD00039</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>XD00040</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>XD00041</t>
   </si>
   <si>
-    <t>153</t>
-  </si>
-  <si>
     <t>XD00042</t>
   </si>
   <si>
-    <t>154</t>
-  </si>
-  <si>
     <t>XD00043</t>
   </si>
   <si>
-    <t>155</t>
-  </si>
-  <si>
     <t>XD00044</t>
   </si>
   <si>
-    <t>156</t>
-  </si>
-  <si>
     <t>XD00045</t>
   </si>
   <si>
-    <t>157</t>
-  </si>
-  <si>
     <t>XD00046</t>
   </si>
   <si>
-    <t>158</t>
-  </si>
-  <si>
     <t>XD00047</t>
   </si>
   <si>
-    <t>159</t>
-  </si>
-  <si>
     <t>XD00048</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>XD00049</t>
   </si>
   <si>
-    <t>161</t>
-  </si>
-  <si>
     <t>XD00050</t>
   </si>
   <si>
-    <t>162</t>
-  </si>
-  <si>
     <t>XD00051</t>
   </si>
   <si>
-    <t>163</t>
-  </si>
-  <si>
     <t>XD00052</t>
   </si>
   <si>
-    <t>164</t>
-  </si>
-  <si>
     <t>XD00053</t>
   </si>
   <si>
-    <t>165</t>
-  </si>
-  <si>
     <t>XD00054</t>
   </si>
   <si>
-    <t>166</t>
-  </si>
-  <si>
     <t>XD00055</t>
   </si>
   <si>
-    <t>167</t>
-  </si>
-  <si>
     <t>XD00056</t>
   </si>
   <si>
-    <t>168</t>
-  </si>
-  <si>
     <t>XD00057</t>
   </si>
   <si>
-    <t>169</t>
-  </si>
-  <si>
     <t>XD00058</t>
   </si>
   <si>
-    <t>170</t>
-  </si>
-  <si>
     <t>XD00059</t>
   </si>
   <si>
-    <t>171</t>
-  </si>
-  <si>
     <t>XD00060</t>
   </si>
   <si>
-    <t>172</t>
-  </si>
-  <si>
     <t>XD00061</t>
   </si>
   <si>
-    <t>173</t>
-  </si>
-  <si>
     <t>XD00062</t>
   </si>
   <si>
-    <t>174</t>
-  </si>
-  <si>
     <t>XD00063</t>
   </si>
   <si>
-    <t>175</t>
-  </si>
-  <si>
     <t>XD00175</t>
   </si>
   <si>
     <t>QUỸ AN TOÀN CHI TRẢ</t>
   </si>
   <si>
-    <t>176</t>
-  </si>
-  <si>
     <t>XD00176</t>
   </si>
   <si>
     <t xml:space="preserve">THUYẾT MINH MỘT SỐ CHỈ TIÊU </t>
   </si>
   <si>
-    <t>177</t>
-  </si>
-  <si>
     <t>XD00067</t>
   </si>
   <si>
     <t xml:space="preserve">Số hộ nghèo theo chuẩn hộ nghèo (giai đoạn 2021-2025) </t>
   </si>
   <si>
-    <t>178</t>
-  </si>
-  <si>
     <t>XD00068</t>
   </si>
   <si>
     <t xml:space="preserve">Số hộ nghèo đang còn dư nợ NHCSXH </t>
   </si>
   <si>
-    <t>179</t>
-  </si>
-  <si>
     <t>XD00069</t>
   </si>
   <si>
     <t xml:space="preserve">Số hộ nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
   </si>
   <si>
-    <t>180</t>
-  </si>
-  <si>
     <t>XD00070</t>
   </si>
   <si>
     <t xml:space="preserve">Số hộ cận nghèo theo chuẩn hộ cận nghèo (giai đoạn 2021-2025) </t>
   </si>
   <si>
-    <t>181</t>
-  </si>
-  <si>
     <t>XD00071</t>
   </si>
   <si>
     <t xml:space="preserve">Số hộ cận nghèo đang còn dư nợ NHCSXH </t>
   </si>
   <si>
-    <t>182</t>
-  </si>
-  <si>
     <t>XD00072</t>
   </si>
   <si>
     <t xml:space="preserve">Số hộ cận nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
   </si>
   <si>
-    <t>183</t>
-  </si>
-  <si>
     <t>XD00073</t>
   </si>
   <si>
     <t>Số hộ mới thoát nghèo (giai đoạn 2019-2021)</t>
   </si>
   <si>
-    <t>184</t>
-  </si>
-  <si>
     <t>XD00074</t>
   </si>
   <si>
     <t>Số hộ gia đình sản xuất kinh doanh vùng khó khăn trên địa bàn</t>
   </si>
   <si>
-    <t>185</t>
-  </si>
-  <si>
     <t>XD00075</t>
   </si>
   <si>
     <t xml:space="preserve">Số hộ gia đình SXKD đang còn dư nợ NHCSXH </t>
   </si>
   <si>
-    <t>186</t>
-  </si>
-  <si>
     <t>XD00076</t>
   </si>
   <si>
     <t xml:space="preserve">Số hộ gia đình SXKD đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
   </si>
   <si>
-    <t>187</t>
-  </si>
-  <si>
     <t>XD00077</t>
   </si>
   <si>
     <t xml:space="preserve">Số thương nhân hoạt động thương mại tại vùng khó khăn </t>
   </si>
   <si>
-    <t>188</t>
-  </si>
-  <si>
     <t>XD00078</t>
   </si>
   <si>
     <t xml:space="preserve">Tổng số HSSV theo học các Trường ĐH, CĐ, THCN và dạy nghề </t>
   </si>
   <si>
-    <t>189</t>
-  </si>
-  <si>
     <t>XD00079</t>
   </si>
   <si>
     <t xml:space="preserve">Số HSSV đang còn dư nợ NHCSXH </t>
   </si>
   <si>
-    <t>190</t>
-  </si>
-  <si>
     <t>XD00080</t>
   </si>
   <si>
     <t xml:space="preserve">Số lao động có nhu cầu vay vốn giải quyết việc làm </t>
   </si>
   <si>
-    <t>191</t>
-  </si>
-  <si>
     <t>XD00081</t>
   </si>
   <si>
     <t>Số lao động được vay vốn giải quyết việc làm trong năm</t>
   </si>
   <si>
-    <t>192</t>
-  </si>
-  <si>
     <t>XD00082</t>
   </si>
   <si>
     <t>Số lao động dự kiến được thu hút từ vay vốn giải quyết việc làm</t>
   </si>
   <si>
-    <t>193</t>
-  </si>
-  <si>
     <t>XD00083</t>
   </si>
   <si>
     <t xml:space="preserve">Tổng số lao động có nhu cầu vay vốn đi lao động có thời hạn ở nước ngoài </t>
   </si>
   <si>
-    <t>194</t>
-  </si>
-  <si>
     <t>XD00084</t>
   </si>
   <si>
     <t>Số công trình NS-VSMT NT dự kiến được xây dựng từ nguồn vốn vay NHCSXH</t>
   </si>
   <si>
-    <t>195</t>
-  </si>
-  <si>
     <t>XD00195</t>
   </si>
   <si>
     <t>Tổng số xã trên địa bàn</t>
   </si>
   <si>
-    <t>196</t>
-  </si>
-  <si>
     <t>XD00196</t>
   </si>
   <si>
@@ -970,13 +834,28 @@
   </si>
   <si>
     <t>Trong đó: Cho vay để ký quỹ đối với người lao động đi làm việc tại Hàn Quốc</t>
+  </si>
+  <si>
+    <t>Cho vay để ký quỹ đối với người lao động đi làm việc tại Hàn Quốc</t>
+  </si>
+  <si>
+    <t>Cho vay trả lương ngừng việc theo QĐ15</t>
+  </si>
+  <si>
+    <t>Cho vay hỗ trợ người sử dụng lao động vay vốn trả lương theo QĐ 23/2021/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>XD00085</t>
+  </si>
+  <si>
+    <t>XD00086</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1279,7 +1158,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1435,6 +1314,10 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1779,7 +1662,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1790,336 +1673,336 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I204"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I206"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="80.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.85546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="80.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" style="1" customWidth="1"/>
-    <col min="9" max="257" width="9.140625" style="1"/>
-    <col min="258" max="258" width="6.42578125" style="1" customWidth="1"/>
-    <col min="259" max="259" width="80.140625" style="1" customWidth="1"/>
-    <col min="260" max="260" width="22.42578125" style="1" customWidth="1"/>
-    <col min="261" max="264" width="14.28515625" style="1" customWidth="1"/>
-    <col min="265" max="513" width="9.140625" style="1"/>
-    <col min="514" max="514" width="6.42578125" style="1" customWidth="1"/>
-    <col min="515" max="515" width="80.140625" style="1" customWidth="1"/>
-    <col min="516" max="516" width="22.42578125" style="1" customWidth="1"/>
-    <col min="517" max="520" width="14.28515625" style="1" customWidth="1"/>
-    <col min="521" max="769" width="9.140625" style="1"/>
-    <col min="770" max="770" width="6.42578125" style="1" customWidth="1"/>
-    <col min="771" max="771" width="80.140625" style="1" customWidth="1"/>
-    <col min="772" max="772" width="22.42578125" style="1" customWidth="1"/>
-    <col min="773" max="776" width="14.28515625" style="1" customWidth="1"/>
-    <col min="777" max="1025" width="9.140625" style="1"/>
-    <col min="1026" max="1026" width="6.42578125" style="1" customWidth="1"/>
-    <col min="1027" max="1027" width="80.140625" style="1" customWidth="1"/>
-    <col min="1028" max="1028" width="22.42578125" style="1" customWidth="1"/>
-    <col min="1029" max="1032" width="14.28515625" style="1" customWidth="1"/>
-    <col min="1033" max="1281" width="9.140625" style="1"/>
-    <col min="1282" max="1282" width="6.42578125" style="1" customWidth="1"/>
-    <col min="1283" max="1283" width="80.140625" style="1" customWidth="1"/>
-    <col min="1284" max="1284" width="22.42578125" style="1" customWidth="1"/>
-    <col min="1285" max="1288" width="14.28515625" style="1" customWidth="1"/>
-    <col min="1289" max="1537" width="9.140625" style="1"/>
-    <col min="1538" max="1538" width="6.42578125" style="1" customWidth="1"/>
-    <col min="1539" max="1539" width="80.140625" style="1" customWidth="1"/>
-    <col min="1540" max="1540" width="22.42578125" style="1" customWidth="1"/>
-    <col min="1541" max="1544" width="14.28515625" style="1" customWidth="1"/>
-    <col min="1545" max="1793" width="9.140625" style="1"/>
-    <col min="1794" max="1794" width="6.42578125" style="1" customWidth="1"/>
-    <col min="1795" max="1795" width="80.140625" style="1" customWidth="1"/>
-    <col min="1796" max="1796" width="22.42578125" style="1" customWidth="1"/>
-    <col min="1797" max="1800" width="14.28515625" style="1" customWidth="1"/>
-    <col min="1801" max="2049" width="9.140625" style="1"/>
-    <col min="2050" max="2050" width="6.42578125" style="1" customWidth="1"/>
-    <col min="2051" max="2051" width="80.140625" style="1" customWidth="1"/>
-    <col min="2052" max="2052" width="22.42578125" style="1" customWidth="1"/>
-    <col min="2053" max="2056" width="14.28515625" style="1" customWidth="1"/>
-    <col min="2057" max="2305" width="9.140625" style="1"/>
-    <col min="2306" max="2306" width="6.42578125" style="1" customWidth="1"/>
-    <col min="2307" max="2307" width="80.140625" style="1" customWidth="1"/>
-    <col min="2308" max="2308" width="22.42578125" style="1" customWidth="1"/>
-    <col min="2309" max="2312" width="14.28515625" style="1" customWidth="1"/>
-    <col min="2313" max="2561" width="9.140625" style="1"/>
-    <col min="2562" max="2562" width="6.42578125" style="1" customWidth="1"/>
-    <col min="2563" max="2563" width="80.140625" style="1" customWidth="1"/>
-    <col min="2564" max="2564" width="22.42578125" style="1" customWidth="1"/>
-    <col min="2565" max="2568" width="14.28515625" style="1" customWidth="1"/>
-    <col min="2569" max="2817" width="9.140625" style="1"/>
-    <col min="2818" max="2818" width="6.42578125" style="1" customWidth="1"/>
-    <col min="2819" max="2819" width="80.140625" style="1" customWidth="1"/>
-    <col min="2820" max="2820" width="22.42578125" style="1" customWidth="1"/>
-    <col min="2821" max="2824" width="14.28515625" style="1" customWidth="1"/>
-    <col min="2825" max="3073" width="9.140625" style="1"/>
-    <col min="3074" max="3074" width="6.42578125" style="1" customWidth="1"/>
-    <col min="3075" max="3075" width="80.140625" style="1" customWidth="1"/>
-    <col min="3076" max="3076" width="22.42578125" style="1" customWidth="1"/>
-    <col min="3077" max="3080" width="14.28515625" style="1" customWidth="1"/>
-    <col min="3081" max="3329" width="9.140625" style="1"/>
-    <col min="3330" max="3330" width="6.42578125" style="1" customWidth="1"/>
-    <col min="3331" max="3331" width="80.140625" style="1" customWidth="1"/>
-    <col min="3332" max="3332" width="22.42578125" style="1" customWidth="1"/>
-    <col min="3333" max="3336" width="14.28515625" style="1" customWidth="1"/>
-    <col min="3337" max="3585" width="9.140625" style="1"/>
-    <col min="3586" max="3586" width="6.42578125" style="1" customWidth="1"/>
-    <col min="3587" max="3587" width="80.140625" style="1" customWidth="1"/>
-    <col min="3588" max="3588" width="22.42578125" style="1" customWidth="1"/>
-    <col min="3589" max="3592" width="14.28515625" style="1" customWidth="1"/>
-    <col min="3593" max="3841" width="9.140625" style="1"/>
-    <col min="3842" max="3842" width="6.42578125" style="1" customWidth="1"/>
-    <col min="3843" max="3843" width="80.140625" style="1" customWidth="1"/>
-    <col min="3844" max="3844" width="22.42578125" style="1" customWidth="1"/>
-    <col min="3845" max="3848" width="14.28515625" style="1" customWidth="1"/>
-    <col min="3849" max="4097" width="9.140625" style="1"/>
-    <col min="4098" max="4098" width="6.42578125" style="1" customWidth="1"/>
-    <col min="4099" max="4099" width="80.140625" style="1" customWidth="1"/>
-    <col min="4100" max="4100" width="22.42578125" style="1" customWidth="1"/>
-    <col min="4101" max="4104" width="14.28515625" style="1" customWidth="1"/>
-    <col min="4105" max="4353" width="9.140625" style="1"/>
-    <col min="4354" max="4354" width="6.42578125" style="1" customWidth="1"/>
-    <col min="4355" max="4355" width="80.140625" style="1" customWidth="1"/>
-    <col min="4356" max="4356" width="22.42578125" style="1" customWidth="1"/>
-    <col min="4357" max="4360" width="14.28515625" style="1" customWidth="1"/>
-    <col min="4361" max="4609" width="9.140625" style="1"/>
-    <col min="4610" max="4610" width="6.42578125" style="1" customWidth="1"/>
-    <col min="4611" max="4611" width="80.140625" style="1" customWidth="1"/>
-    <col min="4612" max="4612" width="22.42578125" style="1" customWidth="1"/>
-    <col min="4613" max="4616" width="14.28515625" style="1" customWidth="1"/>
-    <col min="4617" max="4865" width="9.140625" style="1"/>
-    <col min="4866" max="4866" width="6.42578125" style="1" customWidth="1"/>
-    <col min="4867" max="4867" width="80.140625" style="1" customWidth="1"/>
-    <col min="4868" max="4868" width="22.42578125" style="1" customWidth="1"/>
-    <col min="4869" max="4872" width="14.28515625" style="1" customWidth="1"/>
-    <col min="4873" max="5121" width="9.140625" style="1"/>
-    <col min="5122" max="5122" width="6.42578125" style="1" customWidth="1"/>
-    <col min="5123" max="5123" width="80.140625" style="1" customWidth="1"/>
-    <col min="5124" max="5124" width="22.42578125" style="1" customWidth="1"/>
-    <col min="5125" max="5128" width="14.28515625" style="1" customWidth="1"/>
-    <col min="5129" max="5377" width="9.140625" style="1"/>
-    <col min="5378" max="5378" width="6.42578125" style="1" customWidth="1"/>
-    <col min="5379" max="5379" width="80.140625" style="1" customWidth="1"/>
-    <col min="5380" max="5380" width="22.42578125" style="1" customWidth="1"/>
-    <col min="5381" max="5384" width="14.28515625" style="1" customWidth="1"/>
-    <col min="5385" max="5633" width="9.140625" style="1"/>
-    <col min="5634" max="5634" width="6.42578125" style="1" customWidth="1"/>
-    <col min="5635" max="5635" width="80.140625" style="1" customWidth="1"/>
-    <col min="5636" max="5636" width="22.42578125" style="1" customWidth="1"/>
-    <col min="5637" max="5640" width="14.28515625" style="1" customWidth="1"/>
-    <col min="5641" max="5889" width="9.140625" style="1"/>
-    <col min="5890" max="5890" width="6.42578125" style="1" customWidth="1"/>
-    <col min="5891" max="5891" width="80.140625" style="1" customWidth="1"/>
-    <col min="5892" max="5892" width="22.42578125" style="1" customWidth="1"/>
-    <col min="5893" max="5896" width="14.28515625" style="1" customWidth="1"/>
-    <col min="5897" max="6145" width="9.140625" style="1"/>
-    <col min="6146" max="6146" width="6.42578125" style="1" customWidth="1"/>
-    <col min="6147" max="6147" width="80.140625" style="1" customWidth="1"/>
-    <col min="6148" max="6148" width="22.42578125" style="1" customWidth="1"/>
-    <col min="6149" max="6152" width="14.28515625" style="1" customWidth="1"/>
-    <col min="6153" max="6401" width="9.140625" style="1"/>
-    <col min="6402" max="6402" width="6.42578125" style="1" customWidth="1"/>
-    <col min="6403" max="6403" width="80.140625" style="1" customWidth="1"/>
-    <col min="6404" max="6404" width="22.42578125" style="1" customWidth="1"/>
-    <col min="6405" max="6408" width="14.28515625" style="1" customWidth="1"/>
-    <col min="6409" max="6657" width="9.140625" style="1"/>
-    <col min="6658" max="6658" width="6.42578125" style="1" customWidth="1"/>
-    <col min="6659" max="6659" width="80.140625" style="1" customWidth="1"/>
-    <col min="6660" max="6660" width="22.42578125" style="1" customWidth="1"/>
-    <col min="6661" max="6664" width="14.28515625" style="1" customWidth="1"/>
-    <col min="6665" max="6913" width="9.140625" style="1"/>
-    <col min="6914" max="6914" width="6.42578125" style="1" customWidth="1"/>
-    <col min="6915" max="6915" width="80.140625" style="1" customWidth="1"/>
-    <col min="6916" max="6916" width="22.42578125" style="1" customWidth="1"/>
-    <col min="6917" max="6920" width="14.28515625" style="1" customWidth="1"/>
-    <col min="6921" max="7169" width="9.140625" style="1"/>
-    <col min="7170" max="7170" width="6.42578125" style="1" customWidth="1"/>
-    <col min="7171" max="7171" width="80.140625" style="1" customWidth="1"/>
-    <col min="7172" max="7172" width="22.42578125" style="1" customWidth="1"/>
-    <col min="7173" max="7176" width="14.28515625" style="1" customWidth="1"/>
-    <col min="7177" max="7425" width="9.140625" style="1"/>
-    <col min="7426" max="7426" width="6.42578125" style="1" customWidth="1"/>
-    <col min="7427" max="7427" width="80.140625" style="1" customWidth="1"/>
-    <col min="7428" max="7428" width="22.42578125" style="1" customWidth="1"/>
-    <col min="7429" max="7432" width="14.28515625" style="1" customWidth="1"/>
-    <col min="7433" max="7681" width="9.140625" style="1"/>
-    <col min="7682" max="7682" width="6.42578125" style="1" customWidth="1"/>
-    <col min="7683" max="7683" width="80.140625" style="1" customWidth="1"/>
-    <col min="7684" max="7684" width="22.42578125" style="1" customWidth="1"/>
-    <col min="7685" max="7688" width="14.28515625" style="1" customWidth="1"/>
-    <col min="7689" max="7937" width="9.140625" style="1"/>
-    <col min="7938" max="7938" width="6.42578125" style="1" customWidth="1"/>
-    <col min="7939" max="7939" width="80.140625" style="1" customWidth="1"/>
-    <col min="7940" max="7940" width="22.42578125" style="1" customWidth="1"/>
-    <col min="7941" max="7944" width="14.28515625" style="1" customWidth="1"/>
-    <col min="7945" max="8193" width="9.140625" style="1"/>
-    <col min="8194" max="8194" width="6.42578125" style="1" customWidth="1"/>
-    <col min="8195" max="8195" width="80.140625" style="1" customWidth="1"/>
-    <col min="8196" max="8196" width="22.42578125" style="1" customWidth="1"/>
-    <col min="8197" max="8200" width="14.28515625" style="1" customWidth="1"/>
-    <col min="8201" max="8449" width="9.140625" style="1"/>
-    <col min="8450" max="8450" width="6.42578125" style="1" customWidth="1"/>
-    <col min="8451" max="8451" width="80.140625" style="1" customWidth="1"/>
-    <col min="8452" max="8452" width="22.42578125" style="1" customWidth="1"/>
-    <col min="8453" max="8456" width="14.28515625" style="1" customWidth="1"/>
-    <col min="8457" max="8705" width="9.140625" style="1"/>
-    <col min="8706" max="8706" width="6.42578125" style="1" customWidth="1"/>
-    <col min="8707" max="8707" width="80.140625" style="1" customWidth="1"/>
-    <col min="8708" max="8708" width="22.42578125" style="1" customWidth="1"/>
-    <col min="8709" max="8712" width="14.28515625" style="1" customWidth="1"/>
-    <col min="8713" max="8961" width="9.140625" style="1"/>
-    <col min="8962" max="8962" width="6.42578125" style="1" customWidth="1"/>
-    <col min="8963" max="8963" width="80.140625" style="1" customWidth="1"/>
-    <col min="8964" max="8964" width="22.42578125" style="1" customWidth="1"/>
-    <col min="8965" max="8968" width="14.28515625" style="1" customWidth="1"/>
-    <col min="8969" max="9217" width="9.140625" style="1"/>
-    <col min="9218" max="9218" width="6.42578125" style="1" customWidth="1"/>
-    <col min="9219" max="9219" width="80.140625" style="1" customWidth="1"/>
-    <col min="9220" max="9220" width="22.42578125" style="1" customWidth="1"/>
-    <col min="9221" max="9224" width="14.28515625" style="1" customWidth="1"/>
-    <col min="9225" max="9473" width="9.140625" style="1"/>
-    <col min="9474" max="9474" width="6.42578125" style="1" customWidth="1"/>
-    <col min="9475" max="9475" width="80.140625" style="1" customWidth="1"/>
-    <col min="9476" max="9476" width="22.42578125" style="1" customWidth="1"/>
-    <col min="9477" max="9480" width="14.28515625" style="1" customWidth="1"/>
-    <col min="9481" max="9729" width="9.140625" style="1"/>
-    <col min="9730" max="9730" width="6.42578125" style="1" customWidth="1"/>
-    <col min="9731" max="9731" width="80.140625" style="1" customWidth="1"/>
-    <col min="9732" max="9732" width="22.42578125" style="1" customWidth="1"/>
-    <col min="9733" max="9736" width="14.28515625" style="1" customWidth="1"/>
-    <col min="9737" max="9985" width="9.140625" style="1"/>
-    <col min="9986" max="9986" width="6.42578125" style="1" customWidth="1"/>
-    <col min="9987" max="9987" width="80.140625" style="1" customWidth="1"/>
-    <col min="9988" max="9988" width="22.42578125" style="1" customWidth="1"/>
-    <col min="9989" max="9992" width="14.28515625" style="1" customWidth="1"/>
-    <col min="9993" max="10241" width="9.140625" style="1"/>
-    <col min="10242" max="10242" width="6.42578125" style="1" customWidth="1"/>
-    <col min="10243" max="10243" width="80.140625" style="1" customWidth="1"/>
-    <col min="10244" max="10244" width="22.42578125" style="1" customWidth="1"/>
-    <col min="10245" max="10248" width="14.28515625" style="1" customWidth="1"/>
-    <col min="10249" max="10497" width="9.140625" style="1"/>
-    <col min="10498" max="10498" width="6.42578125" style="1" customWidth="1"/>
-    <col min="10499" max="10499" width="80.140625" style="1" customWidth="1"/>
-    <col min="10500" max="10500" width="22.42578125" style="1" customWidth="1"/>
-    <col min="10501" max="10504" width="14.28515625" style="1" customWidth="1"/>
-    <col min="10505" max="10753" width="9.140625" style="1"/>
-    <col min="10754" max="10754" width="6.42578125" style="1" customWidth="1"/>
-    <col min="10755" max="10755" width="80.140625" style="1" customWidth="1"/>
-    <col min="10756" max="10756" width="22.42578125" style="1" customWidth="1"/>
-    <col min="10757" max="10760" width="14.28515625" style="1" customWidth="1"/>
-    <col min="10761" max="11009" width="9.140625" style="1"/>
-    <col min="11010" max="11010" width="6.42578125" style="1" customWidth="1"/>
-    <col min="11011" max="11011" width="80.140625" style="1" customWidth="1"/>
-    <col min="11012" max="11012" width="22.42578125" style="1" customWidth="1"/>
-    <col min="11013" max="11016" width="14.28515625" style="1" customWidth="1"/>
-    <col min="11017" max="11265" width="9.140625" style="1"/>
-    <col min="11266" max="11266" width="6.42578125" style="1" customWidth="1"/>
-    <col min="11267" max="11267" width="80.140625" style="1" customWidth="1"/>
-    <col min="11268" max="11268" width="22.42578125" style="1" customWidth="1"/>
-    <col min="11269" max="11272" width="14.28515625" style="1" customWidth="1"/>
-    <col min="11273" max="11521" width="9.140625" style="1"/>
-    <col min="11522" max="11522" width="6.42578125" style="1" customWidth="1"/>
-    <col min="11523" max="11523" width="80.140625" style="1" customWidth="1"/>
-    <col min="11524" max="11524" width="22.42578125" style="1" customWidth="1"/>
-    <col min="11525" max="11528" width="14.28515625" style="1" customWidth="1"/>
-    <col min="11529" max="11777" width="9.140625" style="1"/>
-    <col min="11778" max="11778" width="6.42578125" style="1" customWidth="1"/>
-    <col min="11779" max="11779" width="80.140625" style="1" customWidth="1"/>
-    <col min="11780" max="11780" width="22.42578125" style="1" customWidth="1"/>
-    <col min="11781" max="11784" width="14.28515625" style="1" customWidth="1"/>
-    <col min="11785" max="12033" width="9.140625" style="1"/>
-    <col min="12034" max="12034" width="6.42578125" style="1" customWidth="1"/>
-    <col min="12035" max="12035" width="80.140625" style="1" customWidth="1"/>
-    <col min="12036" max="12036" width="22.42578125" style="1" customWidth="1"/>
-    <col min="12037" max="12040" width="14.28515625" style="1" customWidth="1"/>
-    <col min="12041" max="12289" width="9.140625" style="1"/>
-    <col min="12290" max="12290" width="6.42578125" style="1" customWidth="1"/>
-    <col min="12291" max="12291" width="80.140625" style="1" customWidth="1"/>
-    <col min="12292" max="12292" width="22.42578125" style="1" customWidth="1"/>
-    <col min="12293" max="12296" width="14.28515625" style="1" customWidth="1"/>
-    <col min="12297" max="12545" width="9.140625" style="1"/>
-    <col min="12546" max="12546" width="6.42578125" style="1" customWidth="1"/>
-    <col min="12547" max="12547" width="80.140625" style="1" customWidth="1"/>
-    <col min="12548" max="12548" width="22.42578125" style="1" customWidth="1"/>
-    <col min="12549" max="12552" width="14.28515625" style="1" customWidth="1"/>
-    <col min="12553" max="12801" width="9.140625" style="1"/>
-    <col min="12802" max="12802" width="6.42578125" style="1" customWidth="1"/>
-    <col min="12803" max="12803" width="80.140625" style="1" customWidth="1"/>
-    <col min="12804" max="12804" width="22.42578125" style="1" customWidth="1"/>
-    <col min="12805" max="12808" width="14.28515625" style="1" customWidth="1"/>
-    <col min="12809" max="13057" width="9.140625" style="1"/>
-    <col min="13058" max="13058" width="6.42578125" style="1" customWidth="1"/>
-    <col min="13059" max="13059" width="80.140625" style="1" customWidth="1"/>
-    <col min="13060" max="13060" width="22.42578125" style="1" customWidth="1"/>
-    <col min="13061" max="13064" width="14.28515625" style="1" customWidth="1"/>
-    <col min="13065" max="13313" width="9.140625" style="1"/>
-    <col min="13314" max="13314" width="6.42578125" style="1" customWidth="1"/>
-    <col min="13315" max="13315" width="80.140625" style="1" customWidth="1"/>
-    <col min="13316" max="13316" width="22.42578125" style="1" customWidth="1"/>
-    <col min="13317" max="13320" width="14.28515625" style="1" customWidth="1"/>
-    <col min="13321" max="13569" width="9.140625" style="1"/>
-    <col min="13570" max="13570" width="6.42578125" style="1" customWidth="1"/>
-    <col min="13571" max="13571" width="80.140625" style="1" customWidth="1"/>
-    <col min="13572" max="13572" width="22.42578125" style="1" customWidth="1"/>
-    <col min="13573" max="13576" width="14.28515625" style="1" customWidth="1"/>
-    <col min="13577" max="13825" width="9.140625" style="1"/>
-    <col min="13826" max="13826" width="6.42578125" style="1" customWidth="1"/>
-    <col min="13827" max="13827" width="80.140625" style="1" customWidth="1"/>
-    <col min="13828" max="13828" width="22.42578125" style="1" customWidth="1"/>
-    <col min="13829" max="13832" width="14.28515625" style="1" customWidth="1"/>
-    <col min="13833" max="14081" width="9.140625" style="1"/>
-    <col min="14082" max="14082" width="6.42578125" style="1" customWidth="1"/>
-    <col min="14083" max="14083" width="80.140625" style="1" customWidth="1"/>
-    <col min="14084" max="14084" width="22.42578125" style="1" customWidth="1"/>
-    <col min="14085" max="14088" width="14.28515625" style="1" customWidth="1"/>
-    <col min="14089" max="14337" width="9.140625" style="1"/>
-    <col min="14338" max="14338" width="6.42578125" style="1" customWidth="1"/>
-    <col min="14339" max="14339" width="80.140625" style="1" customWidth="1"/>
-    <col min="14340" max="14340" width="22.42578125" style="1" customWidth="1"/>
-    <col min="14341" max="14344" width="14.28515625" style="1" customWidth="1"/>
-    <col min="14345" max="14593" width="9.140625" style="1"/>
-    <col min="14594" max="14594" width="6.42578125" style="1" customWidth="1"/>
-    <col min="14595" max="14595" width="80.140625" style="1" customWidth="1"/>
-    <col min="14596" max="14596" width="22.42578125" style="1" customWidth="1"/>
-    <col min="14597" max="14600" width="14.28515625" style="1" customWidth="1"/>
-    <col min="14601" max="14849" width="9.140625" style="1"/>
-    <col min="14850" max="14850" width="6.42578125" style="1" customWidth="1"/>
-    <col min="14851" max="14851" width="80.140625" style="1" customWidth="1"/>
-    <col min="14852" max="14852" width="22.42578125" style="1" customWidth="1"/>
-    <col min="14853" max="14856" width="14.28515625" style="1" customWidth="1"/>
-    <col min="14857" max="15105" width="9.140625" style="1"/>
-    <col min="15106" max="15106" width="6.42578125" style="1" customWidth="1"/>
-    <col min="15107" max="15107" width="80.140625" style="1" customWidth="1"/>
-    <col min="15108" max="15108" width="22.42578125" style="1" customWidth="1"/>
-    <col min="15109" max="15112" width="14.28515625" style="1" customWidth="1"/>
-    <col min="15113" max="15361" width="9.140625" style="1"/>
-    <col min="15362" max="15362" width="6.42578125" style="1" customWidth="1"/>
-    <col min="15363" max="15363" width="80.140625" style="1" customWidth="1"/>
-    <col min="15364" max="15364" width="22.42578125" style="1" customWidth="1"/>
-    <col min="15365" max="15368" width="14.28515625" style="1" customWidth="1"/>
-    <col min="15369" max="15617" width="9.140625" style="1"/>
-    <col min="15618" max="15618" width="6.42578125" style="1" customWidth="1"/>
-    <col min="15619" max="15619" width="80.140625" style="1" customWidth="1"/>
-    <col min="15620" max="15620" width="22.42578125" style="1" customWidth="1"/>
-    <col min="15621" max="15624" width="14.28515625" style="1" customWidth="1"/>
-    <col min="15625" max="15873" width="9.140625" style="1"/>
-    <col min="15874" max="15874" width="6.42578125" style="1" customWidth="1"/>
-    <col min="15875" max="15875" width="80.140625" style="1" customWidth="1"/>
-    <col min="15876" max="15876" width="22.42578125" style="1" customWidth="1"/>
-    <col min="15877" max="15880" width="14.28515625" style="1" customWidth="1"/>
-    <col min="15881" max="16129" width="9.140625" style="1"/>
-    <col min="16130" max="16130" width="6.42578125" style="1" customWidth="1"/>
-    <col min="16131" max="16131" width="80.140625" style="1" customWidth="1"/>
-    <col min="16132" max="16132" width="22.42578125" style="1" customWidth="1"/>
-    <col min="16133" max="16136" width="14.28515625" style="1" customWidth="1"/>
-    <col min="16137" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="17.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" style="1" customWidth="1"/>
+    <col min="9" max="257" width="9.109375" style="1"/>
+    <col min="258" max="258" width="6.44140625" style="1" customWidth="1"/>
+    <col min="259" max="259" width="80.109375" style="1" customWidth="1"/>
+    <col min="260" max="260" width="22.44140625" style="1" customWidth="1"/>
+    <col min="261" max="264" width="14.33203125" style="1" customWidth="1"/>
+    <col min="265" max="513" width="9.109375" style="1"/>
+    <col min="514" max="514" width="6.44140625" style="1" customWidth="1"/>
+    <col min="515" max="515" width="80.109375" style="1" customWidth="1"/>
+    <col min="516" max="516" width="22.44140625" style="1" customWidth="1"/>
+    <col min="517" max="520" width="14.33203125" style="1" customWidth="1"/>
+    <col min="521" max="769" width="9.109375" style="1"/>
+    <col min="770" max="770" width="6.44140625" style="1" customWidth="1"/>
+    <col min="771" max="771" width="80.109375" style="1" customWidth="1"/>
+    <col min="772" max="772" width="22.44140625" style="1" customWidth="1"/>
+    <col min="773" max="776" width="14.33203125" style="1" customWidth="1"/>
+    <col min="777" max="1025" width="9.109375" style="1"/>
+    <col min="1026" max="1026" width="6.44140625" style="1" customWidth="1"/>
+    <col min="1027" max="1027" width="80.109375" style="1" customWidth="1"/>
+    <col min="1028" max="1028" width="22.44140625" style="1" customWidth="1"/>
+    <col min="1029" max="1032" width="14.33203125" style="1" customWidth="1"/>
+    <col min="1033" max="1281" width="9.109375" style="1"/>
+    <col min="1282" max="1282" width="6.44140625" style="1" customWidth="1"/>
+    <col min="1283" max="1283" width="80.109375" style="1" customWidth="1"/>
+    <col min="1284" max="1284" width="22.44140625" style="1" customWidth="1"/>
+    <col min="1285" max="1288" width="14.33203125" style="1" customWidth="1"/>
+    <col min="1289" max="1537" width="9.109375" style="1"/>
+    <col min="1538" max="1538" width="6.44140625" style="1" customWidth="1"/>
+    <col min="1539" max="1539" width="80.109375" style="1" customWidth="1"/>
+    <col min="1540" max="1540" width="22.44140625" style="1" customWidth="1"/>
+    <col min="1541" max="1544" width="14.33203125" style="1" customWidth="1"/>
+    <col min="1545" max="1793" width="9.109375" style="1"/>
+    <col min="1794" max="1794" width="6.44140625" style="1" customWidth="1"/>
+    <col min="1795" max="1795" width="80.109375" style="1" customWidth="1"/>
+    <col min="1796" max="1796" width="22.44140625" style="1" customWidth="1"/>
+    <col min="1797" max="1800" width="14.33203125" style="1" customWidth="1"/>
+    <col min="1801" max="2049" width="9.109375" style="1"/>
+    <col min="2050" max="2050" width="6.44140625" style="1" customWidth="1"/>
+    <col min="2051" max="2051" width="80.109375" style="1" customWidth="1"/>
+    <col min="2052" max="2052" width="22.44140625" style="1" customWidth="1"/>
+    <col min="2053" max="2056" width="14.33203125" style="1" customWidth="1"/>
+    <col min="2057" max="2305" width="9.109375" style="1"/>
+    <col min="2306" max="2306" width="6.44140625" style="1" customWidth="1"/>
+    <col min="2307" max="2307" width="80.109375" style="1" customWidth="1"/>
+    <col min="2308" max="2308" width="22.44140625" style="1" customWidth="1"/>
+    <col min="2309" max="2312" width="14.33203125" style="1" customWidth="1"/>
+    <col min="2313" max="2561" width="9.109375" style="1"/>
+    <col min="2562" max="2562" width="6.44140625" style="1" customWidth="1"/>
+    <col min="2563" max="2563" width="80.109375" style="1" customWidth="1"/>
+    <col min="2564" max="2564" width="22.44140625" style="1" customWidth="1"/>
+    <col min="2565" max="2568" width="14.33203125" style="1" customWidth="1"/>
+    <col min="2569" max="2817" width="9.109375" style="1"/>
+    <col min="2818" max="2818" width="6.44140625" style="1" customWidth="1"/>
+    <col min="2819" max="2819" width="80.109375" style="1" customWidth="1"/>
+    <col min="2820" max="2820" width="22.44140625" style="1" customWidth="1"/>
+    <col min="2821" max="2824" width="14.33203125" style="1" customWidth="1"/>
+    <col min="2825" max="3073" width="9.109375" style="1"/>
+    <col min="3074" max="3074" width="6.44140625" style="1" customWidth="1"/>
+    <col min="3075" max="3075" width="80.109375" style="1" customWidth="1"/>
+    <col min="3076" max="3076" width="22.44140625" style="1" customWidth="1"/>
+    <col min="3077" max="3080" width="14.33203125" style="1" customWidth="1"/>
+    <col min="3081" max="3329" width="9.109375" style="1"/>
+    <col min="3330" max="3330" width="6.44140625" style="1" customWidth="1"/>
+    <col min="3331" max="3331" width="80.109375" style="1" customWidth="1"/>
+    <col min="3332" max="3332" width="22.44140625" style="1" customWidth="1"/>
+    <col min="3333" max="3336" width="14.33203125" style="1" customWidth="1"/>
+    <col min="3337" max="3585" width="9.109375" style="1"/>
+    <col min="3586" max="3586" width="6.44140625" style="1" customWidth="1"/>
+    <col min="3587" max="3587" width="80.109375" style="1" customWidth="1"/>
+    <col min="3588" max="3588" width="22.44140625" style="1" customWidth="1"/>
+    <col min="3589" max="3592" width="14.33203125" style="1" customWidth="1"/>
+    <col min="3593" max="3841" width="9.109375" style="1"/>
+    <col min="3842" max="3842" width="6.44140625" style="1" customWidth="1"/>
+    <col min="3843" max="3843" width="80.109375" style="1" customWidth="1"/>
+    <col min="3844" max="3844" width="22.44140625" style="1" customWidth="1"/>
+    <col min="3845" max="3848" width="14.33203125" style="1" customWidth="1"/>
+    <col min="3849" max="4097" width="9.109375" style="1"/>
+    <col min="4098" max="4098" width="6.44140625" style="1" customWidth="1"/>
+    <col min="4099" max="4099" width="80.109375" style="1" customWidth="1"/>
+    <col min="4100" max="4100" width="22.44140625" style="1" customWidth="1"/>
+    <col min="4101" max="4104" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4105" max="4353" width="9.109375" style="1"/>
+    <col min="4354" max="4354" width="6.44140625" style="1" customWidth="1"/>
+    <col min="4355" max="4355" width="80.109375" style="1" customWidth="1"/>
+    <col min="4356" max="4356" width="22.44140625" style="1" customWidth="1"/>
+    <col min="4357" max="4360" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4361" max="4609" width="9.109375" style="1"/>
+    <col min="4610" max="4610" width="6.44140625" style="1" customWidth="1"/>
+    <col min="4611" max="4611" width="80.109375" style="1" customWidth="1"/>
+    <col min="4612" max="4612" width="22.44140625" style="1" customWidth="1"/>
+    <col min="4613" max="4616" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4617" max="4865" width="9.109375" style="1"/>
+    <col min="4866" max="4866" width="6.44140625" style="1" customWidth="1"/>
+    <col min="4867" max="4867" width="80.109375" style="1" customWidth="1"/>
+    <col min="4868" max="4868" width="22.44140625" style="1" customWidth="1"/>
+    <col min="4869" max="4872" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4873" max="5121" width="9.109375" style="1"/>
+    <col min="5122" max="5122" width="6.44140625" style="1" customWidth="1"/>
+    <col min="5123" max="5123" width="80.109375" style="1" customWidth="1"/>
+    <col min="5124" max="5124" width="22.44140625" style="1" customWidth="1"/>
+    <col min="5125" max="5128" width="14.33203125" style="1" customWidth="1"/>
+    <col min="5129" max="5377" width="9.109375" style="1"/>
+    <col min="5378" max="5378" width="6.44140625" style="1" customWidth="1"/>
+    <col min="5379" max="5379" width="80.109375" style="1" customWidth="1"/>
+    <col min="5380" max="5380" width="22.44140625" style="1" customWidth="1"/>
+    <col min="5381" max="5384" width="14.33203125" style="1" customWidth="1"/>
+    <col min="5385" max="5633" width="9.109375" style="1"/>
+    <col min="5634" max="5634" width="6.44140625" style="1" customWidth="1"/>
+    <col min="5635" max="5635" width="80.109375" style="1" customWidth="1"/>
+    <col min="5636" max="5636" width="22.44140625" style="1" customWidth="1"/>
+    <col min="5637" max="5640" width="14.33203125" style="1" customWidth="1"/>
+    <col min="5641" max="5889" width="9.109375" style="1"/>
+    <col min="5890" max="5890" width="6.44140625" style="1" customWidth="1"/>
+    <col min="5891" max="5891" width="80.109375" style="1" customWidth="1"/>
+    <col min="5892" max="5892" width="22.44140625" style="1" customWidth="1"/>
+    <col min="5893" max="5896" width="14.33203125" style="1" customWidth="1"/>
+    <col min="5897" max="6145" width="9.109375" style="1"/>
+    <col min="6146" max="6146" width="6.44140625" style="1" customWidth="1"/>
+    <col min="6147" max="6147" width="80.109375" style="1" customWidth="1"/>
+    <col min="6148" max="6148" width="22.44140625" style="1" customWidth="1"/>
+    <col min="6149" max="6152" width="14.33203125" style="1" customWidth="1"/>
+    <col min="6153" max="6401" width="9.109375" style="1"/>
+    <col min="6402" max="6402" width="6.44140625" style="1" customWidth="1"/>
+    <col min="6403" max="6403" width="80.109375" style="1" customWidth="1"/>
+    <col min="6404" max="6404" width="22.44140625" style="1" customWidth="1"/>
+    <col min="6405" max="6408" width="14.33203125" style="1" customWidth="1"/>
+    <col min="6409" max="6657" width="9.109375" style="1"/>
+    <col min="6658" max="6658" width="6.44140625" style="1" customWidth="1"/>
+    <col min="6659" max="6659" width="80.109375" style="1" customWidth="1"/>
+    <col min="6660" max="6660" width="22.44140625" style="1" customWidth="1"/>
+    <col min="6661" max="6664" width="14.33203125" style="1" customWidth="1"/>
+    <col min="6665" max="6913" width="9.109375" style="1"/>
+    <col min="6914" max="6914" width="6.44140625" style="1" customWidth="1"/>
+    <col min="6915" max="6915" width="80.109375" style="1" customWidth="1"/>
+    <col min="6916" max="6916" width="22.44140625" style="1" customWidth="1"/>
+    <col min="6917" max="6920" width="14.33203125" style="1" customWidth="1"/>
+    <col min="6921" max="7169" width="9.109375" style="1"/>
+    <col min="7170" max="7170" width="6.44140625" style="1" customWidth="1"/>
+    <col min="7171" max="7171" width="80.109375" style="1" customWidth="1"/>
+    <col min="7172" max="7172" width="22.44140625" style="1" customWidth="1"/>
+    <col min="7173" max="7176" width="14.33203125" style="1" customWidth="1"/>
+    <col min="7177" max="7425" width="9.109375" style="1"/>
+    <col min="7426" max="7426" width="6.44140625" style="1" customWidth="1"/>
+    <col min="7427" max="7427" width="80.109375" style="1" customWidth="1"/>
+    <col min="7428" max="7428" width="22.44140625" style="1" customWidth="1"/>
+    <col min="7429" max="7432" width="14.33203125" style="1" customWidth="1"/>
+    <col min="7433" max="7681" width="9.109375" style="1"/>
+    <col min="7682" max="7682" width="6.44140625" style="1" customWidth="1"/>
+    <col min="7683" max="7683" width="80.109375" style="1" customWidth="1"/>
+    <col min="7684" max="7684" width="22.44140625" style="1" customWidth="1"/>
+    <col min="7685" max="7688" width="14.33203125" style="1" customWidth="1"/>
+    <col min="7689" max="7937" width="9.109375" style="1"/>
+    <col min="7938" max="7938" width="6.44140625" style="1" customWidth="1"/>
+    <col min="7939" max="7939" width="80.109375" style="1" customWidth="1"/>
+    <col min="7940" max="7940" width="22.44140625" style="1" customWidth="1"/>
+    <col min="7941" max="7944" width="14.33203125" style="1" customWidth="1"/>
+    <col min="7945" max="8193" width="9.109375" style="1"/>
+    <col min="8194" max="8194" width="6.44140625" style="1" customWidth="1"/>
+    <col min="8195" max="8195" width="80.109375" style="1" customWidth="1"/>
+    <col min="8196" max="8196" width="22.44140625" style="1" customWidth="1"/>
+    <col min="8197" max="8200" width="14.33203125" style="1" customWidth="1"/>
+    <col min="8201" max="8449" width="9.109375" style="1"/>
+    <col min="8450" max="8450" width="6.44140625" style="1" customWidth="1"/>
+    <col min="8451" max="8451" width="80.109375" style="1" customWidth="1"/>
+    <col min="8452" max="8452" width="22.44140625" style="1" customWidth="1"/>
+    <col min="8453" max="8456" width="14.33203125" style="1" customWidth="1"/>
+    <col min="8457" max="8705" width="9.109375" style="1"/>
+    <col min="8706" max="8706" width="6.44140625" style="1" customWidth="1"/>
+    <col min="8707" max="8707" width="80.109375" style="1" customWidth="1"/>
+    <col min="8708" max="8708" width="22.44140625" style="1" customWidth="1"/>
+    <col min="8709" max="8712" width="14.33203125" style="1" customWidth="1"/>
+    <col min="8713" max="8961" width="9.109375" style="1"/>
+    <col min="8962" max="8962" width="6.44140625" style="1" customWidth="1"/>
+    <col min="8963" max="8963" width="80.109375" style="1" customWidth="1"/>
+    <col min="8964" max="8964" width="22.44140625" style="1" customWidth="1"/>
+    <col min="8965" max="8968" width="14.33203125" style="1" customWidth="1"/>
+    <col min="8969" max="9217" width="9.109375" style="1"/>
+    <col min="9218" max="9218" width="6.44140625" style="1" customWidth="1"/>
+    <col min="9219" max="9219" width="80.109375" style="1" customWidth="1"/>
+    <col min="9220" max="9220" width="22.44140625" style="1" customWidth="1"/>
+    <col min="9221" max="9224" width="14.33203125" style="1" customWidth="1"/>
+    <col min="9225" max="9473" width="9.109375" style="1"/>
+    <col min="9474" max="9474" width="6.44140625" style="1" customWidth="1"/>
+    <col min="9475" max="9475" width="80.109375" style="1" customWidth="1"/>
+    <col min="9476" max="9476" width="22.44140625" style="1" customWidth="1"/>
+    <col min="9477" max="9480" width="14.33203125" style="1" customWidth="1"/>
+    <col min="9481" max="9729" width="9.109375" style="1"/>
+    <col min="9730" max="9730" width="6.44140625" style="1" customWidth="1"/>
+    <col min="9731" max="9731" width="80.109375" style="1" customWidth="1"/>
+    <col min="9732" max="9732" width="22.44140625" style="1" customWidth="1"/>
+    <col min="9733" max="9736" width="14.33203125" style="1" customWidth="1"/>
+    <col min="9737" max="9985" width="9.109375" style="1"/>
+    <col min="9986" max="9986" width="6.44140625" style="1" customWidth="1"/>
+    <col min="9987" max="9987" width="80.109375" style="1" customWidth="1"/>
+    <col min="9988" max="9988" width="22.44140625" style="1" customWidth="1"/>
+    <col min="9989" max="9992" width="14.33203125" style="1" customWidth="1"/>
+    <col min="9993" max="10241" width="9.109375" style="1"/>
+    <col min="10242" max="10242" width="6.44140625" style="1" customWidth="1"/>
+    <col min="10243" max="10243" width="80.109375" style="1" customWidth="1"/>
+    <col min="10244" max="10244" width="22.44140625" style="1" customWidth="1"/>
+    <col min="10245" max="10248" width="14.33203125" style="1" customWidth="1"/>
+    <col min="10249" max="10497" width="9.109375" style="1"/>
+    <col min="10498" max="10498" width="6.44140625" style="1" customWidth="1"/>
+    <col min="10499" max="10499" width="80.109375" style="1" customWidth="1"/>
+    <col min="10500" max="10500" width="22.44140625" style="1" customWidth="1"/>
+    <col min="10501" max="10504" width="14.33203125" style="1" customWidth="1"/>
+    <col min="10505" max="10753" width="9.109375" style="1"/>
+    <col min="10754" max="10754" width="6.44140625" style="1" customWidth="1"/>
+    <col min="10755" max="10755" width="80.109375" style="1" customWidth="1"/>
+    <col min="10756" max="10756" width="22.44140625" style="1" customWidth="1"/>
+    <col min="10757" max="10760" width="14.33203125" style="1" customWidth="1"/>
+    <col min="10761" max="11009" width="9.109375" style="1"/>
+    <col min="11010" max="11010" width="6.44140625" style="1" customWidth="1"/>
+    <col min="11011" max="11011" width="80.109375" style="1" customWidth="1"/>
+    <col min="11012" max="11012" width="22.44140625" style="1" customWidth="1"/>
+    <col min="11013" max="11016" width="14.33203125" style="1" customWidth="1"/>
+    <col min="11017" max="11265" width="9.109375" style="1"/>
+    <col min="11266" max="11266" width="6.44140625" style="1" customWidth="1"/>
+    <col min="11267" max="11267" width="80.109375" style="1" customWidth="1"/>
+    <col min="11268" max="11268" width="22.44140625" style="1" customWidth="1"/>
+    <col min="11269" max="11272" width="14.33203125" style="1" customWidth="1"/>
+    <col min="11273" max="11521" width="9.109375" style="1"/>
+    <col min="11522" max="11522" width="6.44140625" style="1" customWidth="1"/>
+    <col min="11523" max="11523" width="80.109375" style="1" customWidth="1"/>
+    <col min="11524" max="11524" width="22.44140625" style="1" customWidth="1"/>
+    <col min="11525" max="11528" width="14.33203125" style="1" customWidth="1"/>
+    <col min="11529" max="11777" width="9.109375" style="1"/>
+    <col min="11778" max="11778" width="6.44140625" style="1" customWidth="1"/>
+    <col min="11779" max="11779" width="80.109375" style="1" customWidth="1"/>
+    <col min="11780" max="11780" width="22.44140625" style="1" customWidth="1"/>
+    <col min="11781" max="11784" width="14.33203125" style="1" customWidth="1"/>
+    <col min="11785" max="12033" width="9.109375" style="1"/>
+    <col min="12034" max="12034" width="6.44140625" style="1" customWidth="1"/>
+    <col min="12035" max="12035" width="80.109375" style="1" customWidth="1"/>
+    <col min="12036" max="12036" width="22.44140625" style="1" customWidth="1"/>
+    <col min="12037" max="12040" width="14.33203125" style="1" customWidth="1"/>
+    <col min="12041" max="12289" width="9.109375" style="1"/>
+    <col min="12290" max="12290" width="6.44140625" style="1" customWidth="1"/>
+    <col min="12291" max="12291" width="80.109375" style="1" customWidth="1"/>
+    <col min="12292" max="12292" width="22.44140625" style="1" customWidth="1"/>
+    <col min="12293" max="12296" width="14.33203125" style="1" customWidth="1"/>
+    <col min="12297" max="12545" width="9.109375" style="1"/>
+    <col min="12546" max="12546" width="6.44140625" style="1" customWidth="1"/>
+    <col min="12547" max="12547" width="80.109375" style="1" customWidth="1"/>
+    <col min="12548" max="12548" width="22.44140625" style="1" customWidth="1"/>
+    <col min="12549" max="12552" width="14.33203125" style="1" customWidth="1"/>
+    <col min="12553" max="12801" width="9.109375" style="1"/>
+    <col min="12802" max="12802" width="6.44140625" style="1" customWidth="1"/>
+    <col min="12803" max="12803" width="80.109375" style="1" customWidth="1"/>
+    <col min="12804" max="12804" width="22.44140625" style="1" customWidth="1"/>
+    <col min="12805" max="12808" width="14.33203125" style="1" customWidth="1"/>
+    <col min="12809" max="13057" width="9.109375" style="1"/>
+    <col min="13058" max="13058" width="6.44140625" style="1" customWidth="1"/>
+    <col min="13059" max="13059" width="80.109375" style="1" customWidth="1"/>
+    <col min="13060" max="13060" width="22.44140625" style="1" customWidth="1"/>
+    <col min="13061" max="13064" width="14.33203125" style="1" customWidth="1"/>
+    <col min="13065" max="13313" width="9.109375" style="1"/>
+    <col min="13314" max="13314" width="6.44140625" style="1" customWidth="1"/>
+    <col min="13315" max="13315" width="80.109375" style="1" customWidth="1"/>
+    <col min="13316" max="13316" width="22.44140625" style="1" customWidth="1"/>
+    <col min="13317" max="13320" width="14.33203125" style="1" customWidth="1"/>
+    <col min="13321" max="13569" width="9.109375" style="1"/>
+    <col min="13570" max="13570" width="6.44140625" style="1" customWidth="1"/>
+    <col min="13571" max="13571" width="80.109375" style="1" customWidth="1"/>
+    <col min="13572" max="13572" width="22.44140625" style="1" customWidth="1"/>
+    <col min="13573" max="13576" width="14.33203125" style="1" customWidth="1"/>
+    <col min="13577" max="13825" width="9.109375" style="1"/>
+    <col min="13826" max="13826" width="6.44140625" style="1" customWidth="1"/>
+    <col min="13827" max="13827" width="80.109375" style="1" customWidth="1"/>
+    <col min="13828" max="13828" width="22.44140625" style="1" customWidth="1"/>
+    <col min="13829" max="13832" width="14.33203125" style="1" customWidth="1"/>
+    <col min="13833" max="14081" width="9.109375" style="1"/>
+    <col min="14082" max="14082" width="6.44140625" style="1" customWidth="1"/>
+    <col min="14083" max="14083" width="80.109375" style="1" customWidth="1"/>
+    <col min="14084" max="14084" width="22.44140625" style="1" customWidth="1"/>
+    <col min="14085" max="14088" width="14.33203125" style="1" customWidth="1"/>
+    <col min="14089" max="14337" width="9.109375" style="1"/>
+    <col min="14338" max="14338" width="6.44140625" style="1" customWidth="1"/>
+    <col min="14339" max="14339" width="80.109375" style="1" customWidth="1"/>
+    <col min="14340" max="14340" width="22.44140625" style="1" customWidth="1"/>
+    <col min="14341" max="14344" width="14.33203125" style="1" customWidth="1"/>
+    <col min="14345" max="14593" width="9.109375" style="1"/>
+    <col min="14594" max="14594" width="6.44140625" style="1" customWidth="1"/>
+    <col min="14595" max="14595" width="80.109375" style="1" customWidth="1"/>
+    <col min="14596" max="14596" width="22.44140625" style="1" customWidth="1"/>
+    <col min="14597" max="14600" width="14.33203125" style="1" customWidth="1"/>
+    <col min="14601" max="14849" width="9.109375" style="1"/>
+    <col min="14850" max="14850" width="6.44140625" style="1" customWidth="1"/>
+    <col min="14851" max="14851" width="80.109375" style="1" customWidth="1"/>
+    <col min="14852" max="14852" width="22.44140625" style="1" customWidth="1"/>
+    <col min="14853" max="14856" width="14.33203125" style="1" customWidth="1"/>
+    <col min="14857" max="15105" width="9.109375" style="1"/>
+    <col min="15106" max="15106" width="6.44140625" style="1" customWidth="1"/>
+    <col min="15107" max="15107" width="80.109375" style="1" customWidth="1"/>
+    <col min="15108" max="15108" width="22.44140625" style="1" customWidth="1"/>
+    <col min="15109" max="15112" width="14.33203125" style="1" customWidth="1"/>
+    <col min="15113" max="15361" width="9.109375" style="1"/>
+    <col min="15362" max="15362" width="6.44140625" style="1" customWidth="1"/>
+    <col min="15363" max="15363" width="80.109375" style="1" customWidth="1"/>
+    <col min="15364" max="15364" width="22.44140625" style="1" customWidth="1"/>
+    <col min="15365" max="15368" width="14.33203125" style="1" customWidth="1"/>
+    <col min="15369" max="15617" width="9.109375" style="1"/>
+    <col min="15618" max="15618" width="6.44140625" style="1" customWidth="1"/>
+    <col min="15619" max="15619" width="80.109375" style="1" customWidth="1"/>
+    <col min="15620" max="15620" width="22.44140625" style="1" customWidth="1"/>
+    <col min="15621" max="15624" width="14.33203125" style="1" customWidth="1"/>
+    <col min="15625" max="15873" width="9.109375" style="1"/>
+    <col min="15874" max="15874" width="6.44140625" style="1" customWidth="1"/>
+    <col min="15875" max="15875" width="80.109375" style="1" customWidth="1"/>
+    <col min="15876" max="15876" width="22.44140625" style="1" customWidth="1"/>
+    <col min="15877" max="15880" width="14.33203125" style="1" customWidth="1"/>
+    <col min="15881" max="16129" width="9.109375" style="1"/>
+    <col min="16130" max="16130" width="6.44140625" style="1" customWidth="1"/>
+    <col min="16131" max="16131" width="80.109375" style="1" customWidth="1"/>
+    <col min="16132" max="16132" width="22.44140625" style="1" customWidth="1"/>
+    <col min="16133" max="16136" width="14.33203125" style="1" customWidth="1"/>
+    <col min="16137" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="F1" s="3"/>
@@ -2128,124 +2011,124 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-    </row>
-    <row r="5" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="56" t="s">
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+    </row>
+    <row r="5" spans="1:9" ht="21.9" customHeight="1">
+      <c r="A5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-    </row>
-    <row r="6" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F6" s="54" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+    </row>
+    <row r="6" spans="1:9" ht="23.25" customHeight="1">
+      <c r="F6" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-    </row>
-    <row r="7" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+    </row>
+    <row r="7" spans="1:9" ht="21.6" customHeight="1">
+      <c r="A7" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-    </row>
-    <row r="8" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="58" t="s">
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+    </row>
+    <row r="8" spans="1:9" ht="26.4" customHeight="1">
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="61" t="s">
+      <c r="G8" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="62"/>
-    </row>
-    <row r="9" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="63" t="s">
+      <c r="H8" s="63"/>
+    </row>
+    <row r="9" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A9" s="53"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="63" t="s">
+      <c r="H9" s="64" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-    </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="21" customHeight="1">
+      <c r="A10" s="53"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="6">
         <v>1</v>
       </c>
@@ -2269,7 +2152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" s="37" t="s">
         <v>30</v>
       </c>
@@ -2297,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" s="38" t="s">
         <v>33</v>
       </c>
@@ -2321,12 +2204,12 @@
         <v>0</v>
       </c>
       <c r="H13" s="29">
-        <f t="shared" ref="H13:H108" si="0">IFERROR(G13/E13,0)</f>
+        <f t="shared" ref="H13:H110" si="0">IFERROR(G13/E13,0)</f>
         <v>0</v>
       </c>
       <c r="I13" s="46"/>
     </row>
-    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="7" customFormat="1">
       <c r="A14" s="38" t="s">
         <v>36</v>
       </c>
@@ -2355,7 +2238,7 @@
       </c>
       <c r="I14" s="47"/>
     </row>
-    <row r="15" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="7" customFormat="1">
       <c r="A15" s="38" t="s">
         <v>39</v>
       </c>
@@ -2383,7 +2266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="8" customFormat="1">
       <c r="A16" s="38" t="s">
         <v>42</v>
       </c>
@@ -2402,7 +2285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" s="8" customFormat="1">
       <c r="A17" s="38" t="s">
         <v>45</v>
       </c>
@@ -2421,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" s="8" customFormat="1">
       <c r="A18" s="38" t="s">
         <v>48</v>
       </c>
@@ -2440,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" s="8" customFormat="1">
       <c r="A19" s="38" t="s">
         <v>51</v>
       </c>
@@ -2459,7 +2342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="8" customFormat="1">
       <c r="A20" s="38" t="s">
         <v>54</v>
       </c>
@@ -2478,7 +2361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="38" t="s">
         <v>57</v>
       </c>
@@ -2506,7 +2389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="38" t="s">
         <v>60</v>
       </c>
@@ -2516,7 +2399,7 @@
       <c r="C22" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="34"/>
+      <c r="D22" s="52"/>
       <c r="E22" s="24"/>
       <c r="F22" s="28"/>
       <c r="G22" s="49"/>
@@ -2525,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="38" t="s">
         <v>63</v>
       </c>
@@ -2535,7 +2418,7 @@
       <c r="C23" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="34"/>
+      <c r="D23" s="52"/>
       <c r="E23" s="24"/>
       <c r="F23" s="28"/>
       <c r="G23" s="49"/>
@@ -2544,7 +2427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" s="2" customFormat="1">
       <c r="A24" s="38" t="s">
         <v>66</v>
       </c>
@@ -2555,16 +2438,16 @@
         <v>68</v>
       </c>
       <c r="D24" s="34">
-        <f>D25+D60+D87</f>
+        <f>D25+D62+D89</f>
         <v>0</v>
       </c>
       <c r="E24" s="48">
-        <f>E25+E60+E87</f>
+        <f>E25+E62+E89</f>
         <v>0</v>
       </c>
       <c r="F24" s="28"/>
       <c r="G24" s="49">
-        <f>G25+G60+G87</f>
+        <f>G25+G62+G89</f>
         <v>0</v>
       </c>
       <c r="H24" s="29">
@@ -2572,7 +2455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" s="7" customFormat="1">
       <c r="A25" s="38" t="s">
         <v>69</v>
       </c>
@@ -2600,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="38" t="s">
         <v>72</v>
       </c>
@@ -2619,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="38" t="s">
         <v>75</v>
       </c>
@@ -2638,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="38" t="s">
         <v>78</v>
       </c>
@@ -2657,7 +2540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="38" t="s">
         <v>81</v>
       </c>
@@ -2676,7 +2559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="38" t="s">
         <v>84</v>
       </c>
@@ -2695,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="46.8">
       <c r="A31" s="38" t="s">
         <v>87</v>
       </c>
@@ -2714,7 +2597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="38" t="s">
         <v>90</v>
       </c>
@@ -2722,7 +2605,7 @@
         <v>91</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="24"/>
@@ -2733,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="38" t="s">
         <v>92</v>
       </c>
@@ -2752,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="38" t="s">
         <v>95</v>
       </c>
@@ -2771,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="38" t="s">
         <v>98</v>
       </c>
@@ -2790,7 +2673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="38" t="s">
         <v>101</v>
       </c>
@@ -2809,7 +2692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="31.2">
       <c r="A37" s="38" t="s">
         <v>104</v>
       </c>
@@ -2828,7 +2711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="38" t="s">
         <v>107</v>
       </c>
@@ -2847,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="31.2">
       <c r="A39" s="38" t="s">
         <v>110</v>
       </c>
@@ -2866,7 +2749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="38" t="s">
         <v>113</v>
       </c>
@@ -2885,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="38" t="s">
         <v>116</v>
       </c>
@@ -2904,7 +2787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="38" t="s">
         <v>119</v>
       </c>
@@ -2923,7 +2806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="38" t="s">
         <v>122</v>
       </c>
@@ -2942,7 +2825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="31.2">
       <c r="A44" s="38" t="s">
         <v>125</v>
       </c>
@@ -2961,7 +2844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="46.8">
       <c r="A45" s="38" t="s">
         <v>128</v>
       </c>
@@ -2980,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="38" t="s">
         <v>131</v>
       </c>
@@ -2999,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="38" t="s">
         <v>134</v>
       </c>
@@ -3018,15 +2901,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="38" t="s">
         <v>137</v>
       </c>
       <c r="B48" s="41" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="D48" s="34"/>
       <c r="E48" s="24"/>
@@ -3037,15 +2920,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="38" t="s">
         <v>140</v>
       </c>
       <c r="B49" s="41" t="s">
-        <v>141</v>
+        <v>253</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>142</v>
+        <v>251</v>
       </c>
       <c r="D49" s="34"/>
       <c r="E49" s="24"/>
@@ -3056,15 +2939,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="38" t="s">
         <v>143</v>
       </c>
       <c r="B50" s="41" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D50" s="34"/>
       <c r="E50" s="24"/>
@@ -3075,46 +2958,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="31.2">
       <c r="A51" s="38" t="s">
         <v>146</v>
       </c>
       <c r="B51" s="41" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D51" s="34">
-        <f>SUM(D52:D58)</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="49">
-        <f t="shared" ref="E51:G51" si="1">SUM(E52:E58)</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="D51" s="34"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="50"/>
       <c r="H51" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="31.2">
       <c r="A52" s="38" t="s">
         <v>149</v>
       </c>
       <c r="B52" s="41" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D52" s="34"/>
       <c r="E52" s="24"/>
@@ -3125,34 +2996,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="38" t="s">
         <v>152</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D53" s="34"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="26"/>
+        <v>148</v>
+      </c>
+      <c r="D53" s="34">
+        <f>SUM(D54:D60)</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="24">
+        <f>SUM(E54:E60)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="28">
+        <f>SUM(F55:F60)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="26">
+        <f>SUM(G54:G60)</f>
+        <v>0</v>
+      </c>
       <c r="H53" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="38" t="s">
         <v>155</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D54" s="34"/>
       <c r="E54" s="24"/>
@@ -3163,15 +3046,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="38" t="s">
         <v>158</v>
       </c>
       <c r="B55" s="41" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D55" s="34"/>
       <c r="E55" s="24"/>
@@ -3182,15 +3065,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="38" t="s">
         <v>161</v>
       </c>
       <c r="B56" s="41" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D56" s="34"/>
       <c r="E56" s="24"/>
@@ -3201,15 +3084,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="38" t="s">
         <v>164</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D57" s="34"/>
       <c r="E57" s="24"/>
@@ -3220,15 +3103,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="38" t="s">
         <v>167</v>
       </c>
       <c r="B58" s="41" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D58" s="34"/>
       <c r="E58" s="24"/>
@@ -3239,15 +3122,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="38" t="s">
         <v>170</v>
       </c>
       <c r="B59" s="41" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D59" s="34"/>
       <c r="E59" s="24"/>
@@ -3258,81 +3141,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="38" t="s">
         <v>173</v>
       </c>
       <c r="B60" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="C60" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="D60" s="34">
-        <f>SUM(D61:D86)-D67-D82</f>
-        <v>0</v>
-      </c>
-      <c r="E60" s="49">
-        <f>SUM(E61:E86)-E67-E82</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="51"/>
-      <c r="G60" s="50">
-        <f>SUM(G61:G86)-G67-G82</f>
-        <v>0</v>
-      </c>
-      <c r="H60" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D60" s="34"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="29"/>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="38" t="s">
         <v>176</v>
       </c>
       <c r="B61" s="41" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="D61" s="34"/>
       <c r="E61" s="24"/>
       <c r="F61" s="28"/>
       <c r="G61" s="26"/>
-      <c r="H61" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="38" t="s">
-        <v>178</v>
+      <c r="H61" s="29"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="38">
+        <v>150</v>
       </c>
       <c r="B62" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D62" s="34"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="26"/>
+        <v>174</v>
+      </c>
+      <c r="C62" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="D62" s="34">
+        <f>SUM(D63:D88)-D69-D84</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="49">
+        <f>SUM(E63:E88)-E69-E84</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="51"/>
+      <c r="G62" s="50">
+        <f>SUM(G63:G88)-G69-G84</f>
+        <v>0</v>
+      </c>
       <c r="H62" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="38" t="s">
-        <v>180</v>
+    <row r="63" spans="1:8">
+      <c r="A63" s="38">
+        <v>151</v>
       </c>
       <c r="B63" s="41" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D63" s="34"/>
       <c r="E63" s="24"/>
@@ -3343,15 +3220,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="38" t="s">
-        <v>182</v>
+    <row r="64" spans="1:8">
+      <c r="A64" s="38">
+        <v>152</v>
       </c>
       <c r="B64" s="41" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D64" s="34"/>
       <c r="E64" s="24"/>
@@ -3362,15 +3239,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="38" t="s">
-        <v>184</v>
+    <row r="65" spans="1:8">
+      <c r="A65" s="38">
+        <v>153</v>
       </c>
       <c r="B65" s="41" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D65" s="34"/>
       <c r="E65" s="24"/>
@@ -3381,15 +3258,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="38" t="s">
-        <v>186</v>
+    <row r="66" spans="1:8">
+      <c r="A66" s="38">
+        <v>154</v>
       </c>
       <c r="B66" s="41" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D66" s="34"/>
       <c r="E66" s="24"/>
@@ -3400,15 +3277,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="38" t="s">
-        <v>188</v>
+    <row r="67" spans="1:8">
+      <c r="A67" s="38">
+        <v>155</v>
       </c>
       <c r="B67" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C67" s="44" t="s">
-        <v>295</v>
+        <v>181</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>86</v>
       </c>
       <c r="D67" s="34"/>
       <c r="E67" s="24"/>
@@ -3419,15 +3296,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="38" t="s">
-        <v>190</v>
+    <row r="68" spans="1:8" ht="46.8">
+      <c r="A68" s="38">
+        <v>156</v>
       </c>
       <c r="B68" s="41" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D68" s="34"/>
       <c r="E68" s="24"/>
@@ -3438,15 +3315,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="38" t="s">
-        <v>192</v>
+    <row r="69" spans="1:8">
+      <c r="A69" s="38">
+        <v>157</v>
       </c>
       <c r="B69" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>97</v>
+        <v>183</v>
+      </c>
+      <c r="C69" s="44" t="s">
+        <v>248</v>
       </c>
       <c r="D69" s="34"/>
       <c r="E69" s="24"/>
@@ -3457,15 +3334,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="38" t="s">
-        <v>194</v>
+    <row r="70" spans="1:8">
+      <c r="A70" s="38">
+        <v>158</v>
       </c>
       <c r="B70" s="41" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D70" s="34"/>
       <c r="E70" s="24"/>
@@ -3476,15 +3353,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="38" t="s">
-        <v>196</v>
+    <row r="71" spans="1:8">
+      <c r="A71" s="38">
+        <v>159</v>
       </c>
       <c r="B71" s="41" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D71" s="34"/>
       <c r="E71" s="24"/>
@@ -3495,15 +3372,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="38" t="s">
-        <v>198</v>
+    <row r="72" spans="1:8">
+      <c r="A72" s="38">
+        <v>160</v>
       </c>
       <c r="B72" s="41" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D72" s="34"/>
       <c r="E72" s="24"/>
@@ -3514,15 +3391,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="38" t="s">
-        <v>200</v>
+    <row r="73" spans="1:8">
+      <c r="A73" s="38">
+        <v>161</v>
       </c>
       <c r="B73" s="41" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D73" s="34"/>
       <c r="E73" s="24"/>
@@ -3533,15 +3410,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="38" t="s">
-        <v>202</v>
+    <row r="74" spans="1:8" ht="31.2">
+      <c r="A74" s="38">
+        <v>162</v>
       </c>
       <c r="B74" s="41" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D74" s="34"/>
       <c r="E74" s="24"/>
@@ -3552,15 +3429,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="38" t="s">
-        <v>204</v>
+    <row r="75" spans="1:8">
+      <c r="A75" s="38">
+        <v>163</v>
       </c>
       <c r="B75" s="41" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D75" s="34"/>
       <c r="E75" s="24"/>
@@ -3571,15 +3448,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="38" t="s">
-        <v>206</v>
+    <row r="76" spans="1:8" ht="31.2">
+      <c r="A76" s="38">
+        <v>164</v>
       </c>
       <c r="B76" s="41" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D76" s="34"/>
       <c r="E76" s="24"/>
@@ -3590,15 +3467,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="38" t="s">
-        <v>208</v>
+    <row r="77" spans="1:8">
+      <c r="A77" s="38">
+        <v>165</v>
       </c>
       <c r="B77" s="41" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D77" s="34"/>
       <c r="E77" s="24"/>
@@ -3609,15 +3486,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="38" t="s">
-        <v>210</v>
+    <row r="78" spans="1:8">
+      <c r="A78" s="38">
+        <v>166</v>
       </c>
       <c r="B78" s="41" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D78" s="34"/>
       <c r="E78" s="24"/>
@@ -3628,15 +3505,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="38" t="s">
-        <v>212</v>
+    <row r="79" spans="1:8">
+      <c r="A79" s="38">
+        <v>167</v>
       </c>
       <c r="B79" s="41" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D79" s="34"/>
       <c r="E79" s="24"/>
@@ -3647,15 +3524,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A80" s="38" t="s">
-        <v>214</v>
+    <row r="80" spans="1:8">
+      <c r="A80" s="38">
+        <v>168</v>
       </c>
       <c r="B80" s="41" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D80" s="34"/>
       <c r="E80" s="24"/>
@@ -3666,15 +3543,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="38" t="s">
-        <v>216</v>
+    <row r="81" spans="1:8" ht="31.2">
+      <c r="A81" s="38">
+        <v>169</v>
       </c>
       <c r="B81" s="41" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D81" s="34"/>
       <c r="E81" s="24"/>
@@ -3685,15 +3562,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="38" t="s">
-        <v>218</v>
+    <row r="82" spans="1:8" ht="46.8">
+      <c r="A82" s="38">
+        <v>170</v>
       </c>
       <c r="B82" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="C82" s="44" t="s">
-        <v>136</v>
+        <v>196</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>130</v>
       </c>
       <c r="D82" s="34"/>
       <c r="E82" s="24"/>
@@ -3704,15 +3581,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="38" t="s">
-        <v>220</v>
+    <row r="83" spans="1:8">
+      <c r="A83" s="38">
+        <v>171</v>
       </c>
       <c r="B83" s="41" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D83" s="34"/>
       <c r="E83" s="24"/>
@@ -3723,15 +3600,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="38" t="s">
-        <v>222</v>
+    <row r="84" spans="1:8">
+      <c r="A84" s="38">
+        <v>172</v>
       </c>
       <c r="B84" s="41" t="s">
-        <v>223</v>
-      </c>
-      <c r="C84" s="21" t="s">
-        <v>142</v>
+        <v>198</v>
+      </c>
+      <c r="C84" s="44" t="s">
+        <v>136</v>
       </c>
       <c r="D84" s="34"/>
       <c r="E84" s="24"/>
@@ -3742,15 +3619,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="38" t="s">
-        <v>224</v>
+    <row r="85" spans="1:8">
+      <c r="A85" s="38">
+        <v>173</v>
       </c>
       <c r="B85" s="41" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D85" s="34"/>
       <c r="E85" s="24"/>
@@ -3761,15 +3638,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="38" t="s">
-        <v>226</v>
+    <row r="86" spans="1:8" ht="31.2">
+      <c r="A86" s="38">
+        <v>174</v>
       </c>
       <c r="B86" s="41" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="D86" s="34"/>
       <c r="E86" s="24"/>
@@ -3780,15 +3657,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="38" t="s">
-        <v>228</v>
+    <row r="87" spans="1:8" ht="31.2">
+      <c r="A87" s="38">
+        <v>175</v>
       </c>
       <c r="B87" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="C87" s="45" t="s">
-        <v>230</v>
+        <v>201</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>145</v>
       </c>
       <c r="D87" s="34"/>
       <c r="E87" s="24"/>
@@ -3799,15 +3676,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="38" t="s">
-        <v>231</v>
+    <row r="88" spans="1:8">
+      <c r="A88" s="38">
+        <v>176</v>
       </c>
       <c r="B88" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="C88" s="45" t="s">
-        <v>233</v>
+        <v>202</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>172</v>
       </c>
       <c r="D88" s="34"/>
       <c r="E88" s="24"/>
@@ -3818,15 +3695,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="38" t="s">
-        <v>234</v>
+    <row r="89" spans="1:8">
+      <c r="A89" s="38">
+        <v>177</v>
       </c>
       <c r="B89" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>236</v>
+        <v>203</v>
+      </c>
+      <c r="C89" s="45" t="s">
+        <v>204</v>
       </c>
       <c r="D89" s="34"/>
       <c r="E89" s="24"/>
@@ -3837,15 +3714,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="38" t="s">
-        <v>237</v>
+    <row r="90" spans="1:8">
+      <c r="A90" s="38">
+        <v>178</v>
       </c>
       <c r="B90" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="C90" s="21" t="s">
-        <v>239</v>
+        <v>205</v>
+      </c>
+      <c r="C90" s="45" t="s">
+        <v>206</v>
       </c>
       <c r="D90" s="34"/>
       <c r="E90" s="24"/>
@@ -3856,15 +3733,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="38" t="s">
-        <v>240</v>
+    <row r="91" spans="1:8">
+      <c r="A91" s="38">
+        <v>179</v>
       </c>
       <c r="B91" s="41" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="D91" s="34"/>
       <c r="E91" s="24"/>
@@ -3875,15 +3752,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="38" t="s">
-        <v>243</v>
+    <row r="92" spans="1:8">
+      <c r="A92" s="38">
+        <v>180</v>
       </c>
       <c r="B92" s="41" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="D92" s="34"/>
       <c r="E92" s="24"/>
@@ -3894,15 +3771,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="38" t="s">
-        <v>246</v>
+    <row r="93" spans="1:8">
+      <c r="A93" s="38">
+        <v>181</v>
       </c>
       <c r="B93" s="41" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="D93" s="34"/>
       <c r="E93" s="24"/>
@@ -3913,15 +3790,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="38" t="s">
-        <v>249</v>
+    <row r="94" spans="1:8">
+      <c r="A94" s="38">
+        <v>182</v>
       </c>
       <c r="B94" s="41" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="D94" s="34"/>
       <c r="E94" s="24"/>
@@ -3932,15 +3809,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="38" t="s">
-        <v>252</v>
+    <row r="95" spans="1:8">
+      <c r="A95" s="38">
+        <v>183</v>
       </c>
       <c r="B95" s="41" t="s">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c r="D95" s="34"/>
       <c r="E95" s="24"/>
@@ -3951,15 +3828,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="38" t="s">
-        <v>255</v>
+    <row r="96" spans="1:8">
+      <c r="A96" s="38">
+        <v>184</v>
       </c>
       <c r="B96" s="41" t="s">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>257</v>
+        <v>218</v>
       </c>
       <c r="D96" s="34"/>
       <c r="E96" s="24"/>
@@ -3970,15 +3847,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="38" t="s">
-        <v>258</v>
+    <row r="97" spans="1:8">
+      <c r="A97" s="38">
+        <v>185</v>
       </c>
       <c r="B97" s="41" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="D97" s="34"/>
       <c r="E97" s="24"/>
@@ -3989,15 +3866,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="38" t="s">
-        <v>261</v>
+    <row r="98" spans="1:8">
+      <c r="A98" s="38">
+        <v>186</v>
       </c>
       <c r="B98" s="41" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="D98" s="34"/>
       <c r="E98" s="24"/>
@@ -4008,15 +3885,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="38" t="s">
-        <v>264</v>
+    <row r="99" spans="1:8">
+      <c r="A99" s="38">
+        <v>187</v>
       </c>
       <c r="B99" s="41" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="D99" s="34"/>
       <c r="E99" s="24"/>
@@ -4027,15 +3904,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="38" t="s">
-        <v>267</v>
+    <row r="100" spans="1:8">
+      <c r="A100" s="38">
+        <v>188</v>
       </c>
       <c r="B100" s="41" t="s">
-        <v>268</v>
+        <v>225</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="D100" s="34"/>
       <c r="E100" s="24"/>
@@ -4046,15 +3923,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="38" t="s">
-        <v>270</v>
+    <row r="101" spans="1:8">
+      <c r="A101" s="38">
+        <v>189</v>
       </c>
       <c r="B101" s="41" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="D101" s="34"/>
       <c r="E101" s="24"/>
@@ -4065,15 +3942,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="38" t="s">
-        <v>273</v>
+    <row r="102" spans="1:8">
+      <c r="A102" s="38">
+        <v>190</v>
       </c>
       <c r="B102" s="41" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="D102" s="34"/>
       <c r="E102" s="24"/>
@@ -4084,15 +3961,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="38" t="s">
-        <v>276</v>
+    <row r="103" spans="1:8">
+      <c r="A103" s="38">
+        <v>191</v>
       </c>
       <c r="B103" s="41" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="D103" s="34"/>
       <c r="E103" s="24"/>
@@ -4103,15 +3980,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="38" t="s">
-        <v>279</v>
+    <row r="104" spans="1:8">
+      <c r="A104" s="38">
+        <v>192</v>
       </c>
       <c r="B104" s="41" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="D104" s="34"/>
       <c r="E104" s="24"/>
@@ -4122,15 +3999,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="38" t="s">
-        <v>282</v>
+    <row r="105" spans="1:8">
+      <c r="A105" s="38">
+        <v>193</v>
       </c>
       <c r="B105" s="41" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="D105" s="34"/>
       <c r="E105" s="24"/>
@@ -4141,15 +4018,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="38" t="s">
-        <v>285</v>
+    <row r="106" spans="1:8">
+      <c r="A106" s="38">
+        <v>194</v>
       </c>
       <c r="B106" s="41" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="D106" s="34"/>
       <c r="E106" s="24"/>
@@ -4160,15 +4037,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="38" t="s">
-        <v>288</v>
+    <row r="107" spans="1:8">
+      <c r="A107" s="38">
+        <v>195</v>
       </c>
       <c r="B107" s="41" t="s">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="D107" s="34"/>
       <c r="E107" s="24"/>
@@ -4179,15 +4056,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="38" t="s">
-        <v>291</v>
+    <row r="108" spans="1:8">
+      <c r="A108" s="38">
+        <v>196</v>
       </c>
       <c r="B108" s="41" t="s">
-        <v>292</v>
+        <v>241</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="D108" s="34"/>
       <c r="E108" s="24"/>
@@ -4198,37 +4075,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="38"/>
-      <c r="B109" s="41"/>
-      <c r="C109" s="19"/>
+    <row r="109" spans="1:8">
+      <c r="A109" s="38">
+        <v>197</v>
+      </c>
+      <c r="B109" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C109" s="21" t="s">
+        <v>244</v>
+      </c>
       <c r="D109" s="34"/>
       <c r="E109" s="24"/>
       <c r="F109" s="28"/>
       <c r="G109" s="26"/>
-      <c r="H109" s="29"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="38"/>
-      <c r="B110" s="41"/>
-      <c r="C110" s="21"/>
+      <c r="H109" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="38">
+        <v>198</v>
+      </c>
+      <c r="B110" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>246</v>
+      </c>
       <c r="D110" s="34"/>
       <c r="E110" s="24"/>
       <c r="F110" s="28"/>
       <c r="G110" s="26"/>
-      <c r="H110" s="29"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H110" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" s="38"/>
       <c r="B111" s="41"/>
-      <c r="C111" s="21"/>
+      <c r="C111" s="19"/>
       <c r="D111" s="34"/>
       <c r="E111" s="24"/>
       <c r="F111" s="28"/>
       <c r="G111" s="26"/>
       <c r="H111" s="29"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="38"/>
       <c r="B112" s="41"/>
       <c r="C112" s="21"/>
@@ -4238,7 +4133,7 @@
       <c r="G112" s="26"/>
       <c r="H112" s="29"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="38"/>
       <c r="B113" s="41"/>
       <c r="C113" s="21"/>
@@ -4248,7 +4143,7 @@
       <c r="G113" s="26"/>
       <c r="H113" s="29"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="38"/>
       <c r="B114" s="41"/>
       <c r="C114" s="21"/>
@@ -4258,7 +4153,7 @@
       <c r="G114" s="26"/>
       <c r="H114" s="29"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="38"/>
       <c r="B115" s="41"/>
       <c r="C115" s="21"/>
@@ -4268,7 +4163,7 @@
       <c r="G115" s="26"/>
       <c r="H115" s="29"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="38"/>
       <c r="B116" s="41"/>
       <c r="C116" s="21"/>
@@ -4278,7 +4173,7 @@
       <c r="G116" s="26"/>
       <c r="H116" s="29"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="38"/>
       <c r="B117" s="41"/>
       <c r="C117" s="21"/>
@@ -4288,7 +4183,7 @@
       <c r="G117" s="26"/>
       <c r="H117" s="29"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="38"/>
       <c r="B118" s="41"/>
       <c r="C118" s="21"/>
@@ -4298,7 +4193,7 @@
       <c r="G118" s="26"/>
       <c r="H118" s="29"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="38"/>
       <c r="B119" s="41"/>
       <c r="C119" s="21"/>
@@ -4308,7 +4203,7 @@
       <c r="G119" s="26"/>
       <c r="H119" s="29"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="38"/>
       <c r="B120" s="41"/>
       <c r="C120" s="21"/>
@@ -4318,27 +4213,27 @@
       <c r="G120" s="26"/>
       <c r="H120" s="29"/>
     </row>
-    <row r="121" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="38"/>
       <c r="B121" s="41"/>
       <c r="C121" s="21"/>
       <c r="D121" s="34"/>
-      <c r="E121" s="26"/>
+      <c r="E121" s="24"/>
       <c r="F121" s="28"/>
       <c r="G121" s="26"/>
       <c r="H121" s="29"/>
     </row>
-    <row r="122" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8">
       <c r="A122" s="38"/>
       <c r="B122" s="41"/>
       <c r="C122" s="21"/>
       <c r="D122" s="34"/>
-      <c r="E122" s="26"/>
+      <c r="E122" s="24"/>
       <c r="F122" s="28"/>
       <c r="G122" s="26"/>
       <c r="H122" s="29"/>
     </row>
-    <row r="123" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" s="9" customFormat="1">
       <c r="A123" s="38"/>
       <c r="B123" s="41"/>
       <c r="C123" s="21"/>
@@ -4348,7 +4243,7 @@
       <c r="G123" s="26"/>
       <c r="H123" s="29"/>
     </row>
-    <row r="124" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" s="9" customFormat="1">
       <c r="A124" s="38"/>
       <c r="B124" s="41"/>
       <c r="C124" s="21"/>
@@ -4358,7 +4253,7 @@
       <c r="G124" s="26"/>
       <c r="H124" s="29"/>
     </row>
-    <row r="125" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" s="9" customFormat="1">
       <c r="A125" s="38"/>
       <c r="B125" s="41"/>
       <c r="C125" s="21"/>
@@ -4368,7 +4263,7 @@
       <c r="G125" s="26"/>
       <c r="H125" s="29"/>
     </row>
-    <row r="126" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" s="9" customFormat="1">
       <c r="A126" s="38"/>
       <c r="B126" s="41"/>
       <c r="C126" s="21"/>
@@ -4378,7 +4273,7 @@
       <c r="G126" s="26"/>
       <c r="H126" s="29"/>
     </row>
-    <row r="127" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" s="9" customFormat="1">
       <c r="A127" s="38"/>
       <c r="B127" s="41"/>
       <c r="C127" s="21"/>
@@ -4388,77 +4283,77 @@
       <c r="G127" s="26"/>
       <c r="H127" s="29"/>
     </row>
-    <row r="128" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" s="9" customFormat="1">
       <c r="A128" s="38"/>
       <c r="B128" s="41"/>
-      <c r="C128" s="19"/>
+      <c r="C128" s="21"/>
       <c r="D128" s="34"/>
       <c r="E128" s="26"/>
       <c r="F128" s="28"/>
       <c r="G128" s="26"/>
       <c r="H128" s="29"/>
     </row>
-    <row r="129" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" s="9" customFormat="1">
       <c r="A129" s="38"/>
       <c r="B129" s="41"/>
-      <c r="C129" s="20"/>
+      <c r="C129" s="21"/>
       <c r="D129" s="34"/>
-      <c r="E129" s="24"/>
+      <c r="E129" s="26"/>
       <c r="F129" s="28"/>
-      <c r="G129" s="24"/>
+      <c r="G129" s="26"/>
       <c r="H129" s="29"/>
     </row>
-    <row r="130" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" s="9" customFormat="1">
       <c r="A130" s="38"/>
       <c r="B130" s="41"/>
       <c r="C130" s="19"/>
       <c r="D130" s="34"/>
-      <c r="E130" s="24"/>
+      <c r="E130" s="26"/>
       <c r="F130" s="28"/>
-      <c r="G130" s="24"/>
+      <c r="G130" s="26"/>
       <c r="H130" s="29"/>
     </row>
-    <row r="131" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" s="7" customFormat="1">
       <c r="A131" s="38"/>
       <c r="B131" s="41"/>
-      <c r="C131" s="19"/>
+      <c r="C131" s="20"/>
       <c r="D131" s="34"/>
       <c r="E131" s="24"/>
       <c r="F131" s="28"/>
       <c r="G131" s="24"/>
       <c r="H131" s="29"/>
     </row>
-    <row r="132" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" s="7" customFormat="1">
       <c r="A132" s="38"/>
       <c r="B132" s="41"/>
-      <c r="C132" s="21"/>
+      <c r="C132" s="19"/>
       <c r="D132" s="34"/>
       <c r="E132" s="24"/>
       <c r="F132" s="28"/>
       <c r="G132" s="24"/>
       <c r="H132" s="29"/>
     </row>
-    <row r="133" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" s="7" customFormat="1">
       <c r="A133" s="38"/>
       <c r="B133" s="41"/>
-      <c r="C133" s="21"/>
+      <c r="C133" s="19"/>
       <c r="D133" s="34"/>
       <c r="E133" s="24"/>
       <c r="F133" s="28"/>
       <c r="G133" s="24"/>
       <c r="H133" s="29"/>
     </row>
-    <row r="134" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" s="7" customFormat="1">
       <c r="A134" s="38"/>
       <c r="B134" s="41"/>
-      <c r="C134" s="19"/>
+      <c r="C134" s="21"/>
       <c r="D134" s="34"/>
       <c r="E134" s="24"/>
       <c r="F134" s="28"/>
       <c r="G134" s="24"/>
       <c r="H134" s="29"/>
     </row>
-    <row r="135" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" s="7" customFormat="1">
       <c r="A135" s="38"/>
       <c r="B135" s="41"/>
       <c r="C135" s="21"/>
@@ -4468,17 +4363,17 @@
       <c r="G135" s="24"/>
       <c r="H135" s="29"/>
     </row>
-    <row r="136" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" s="7" customFormat="1">
       <c r="A136" s="38"/>
       <c r="B136" s="41"/>
-      <c r="C136" s="22"/>
+      <c r="C136" s="19"/>
       <c r="D136" s="34"/>
       <c r="E136" s="24"/>
       <c r="F136" s="28"/>
       <c r="G136" s="24"/>
       <c r="H136" s="29"/>
     </row>
-    <row r="137" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" s="7" customFormat="1">
       <c r="A137" s="38"/>
       <c r="B137" s="41"/>
       <c r="C137" s="21"/>
@@ -4488,17 +4383,17 @@
       <c r="G137" s="24"/>
       <c r="H137" s="29"/>
     </row>
-    <row r="138" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" s="7" customFormat="1">
       <c r="A138" s="38"/>
       <c r="B138" s="41"/>
-      <c r="C138" s="21"/>
+      <c r="C138" s="22"/>
       <c r="D138" s="34"/>
       <c r="E138" s="24"/>
       <c r="F138" s="28"/>
       <c r="G138" s="24"/>
       <c r="H138" s="29"/>
     </row>
-    <row r="139" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" s="7" customFormat="1">
       <c r="A139" s="38"/>
       <c r="B139" s="41"/>
       <c r="C139" s="21"/>
@@ -4508,7 +4403,7 @@
       <c r="G139" s="24"/>
       <c r="H139" s="29"/>
     </row>
-    <row r="140" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" s="7" customFormat="1">
       <c r="A140" s="38"/>
       <c r="B140" s="41"/>
       <c r="C140" s="21"/>
@@ -4518,7 +4413,7 @@
       <c r="G140" s="24"/>
       <c r="H140" s="29"/>
     </row>
-    <row r="141" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" s="7" customFormat="1">
       <c r="A141" s="38"/>
       <c r="B141" s="41"/>
       <c r="C141" s="21"/>
@@ -4528,7 +4423,7 @@
       <c r="G141" s="24"/>
       <c r="H141" s="29"/>
     </row>
-    <row r="142" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" s="7" customFormat="1">
       <c r="A142" s="38"/>
       <c r="B142" s="41"/>
       <c r="C142" s="21"/>
@@ -4538,7 +4433,7 @@
       <c r="G142" s="24"/>
       <c r="H142" s="29"/>
     </row>
-    <row r="143" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" s="7" customFormat="1">
       <c r="A143" s="38"/>
       <c r="B143" s="41"/>
       <c r="C143" s="21"/>
@@ -4548,7 +4443,7 @@
       <c r="G143" s="24"/>
       <c r="H143" s="29"/>
     </row>
-    <row r="144" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" s="7" customFormat="1">
       <c r="A144" s="38"/>
       <c r="B144" s="41"/>
       <c r="C144" s="21"/>
@@ -4558,7 +4453,7 @@
       <c r="G144" s="24"/>
       <c r="H144" s="29"/>
     </row>
-    <row r="145" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" s="7" customFormat="1">
       <c r="A145" s="38"/>
       <c r="B145" s="41"/>
       <c r="C145" s="21"/>
@@ -4568,7 +4463,7 @@
       <c r="G145" s="24"/>
       <c r="H145" s="29"/>
     </row>
-    <row r="146" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" s="7" customFormat="1">
       <c r="A146" s="38"/>
       <c r="B146" s="41"/>
       <c r="C146" s="21"/>
@@ -4578,7 +4473,7 @@
       <c r="G146" s="24"/>
       <c r="H146" s="29"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" s="7" customFormat="1">
       <c r="A147" s="38"/>
       <c r="B147" s="41"/>
       <c r="C147" s="21"/>
@@ -4588,7 +4483,7 @@
       <c r="G147" s="24"/>
       <c r="H147" s="29"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" s="7" customFormat="1">
       <c r="A148" s="38"/>
       <c r="B148" s="41"/>
       <c r="C148" s="21"/>
@@ -4598,7 +4493,7 @@
       <c r="G148" s="24"/>
       <c r="H148" s="29"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8">
       <c r="A149" s="38"/>
       <c r="B149" s="41"/>
       <c r="C149" s="21"/>
@@ -4608,7 +4503,7 @@
       <c r="G149" s="24"/>
       <c r="H149" s="29"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8">
       <c r="A150" s="38"/>
       <c r="B150" s="41"/>
       <c r="C150" s="21"/>
@@ -4618,7 +4513,7 @@
       <c r="G150" s="24"/>
       <c r="H150" s="29"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8">
       <c r="A151" s="38"/>
       <c r="B151" s="41"/>
       <c r="C151" s="21"/>
@@ -4628,7 +4523,7 @@
       <c r="G151" s="24"/>
       <c r="H151" s="29"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8">
       <c r="A152" s="38"/>
       <c r="B152" s="41"/>
       <c r="C152" s="21"/>
@@ -4638,7 +4533,7 @@
       <c r="G152" s="24"/>
       <c r="H152" s="29"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8">
       <c r="A153" s="38"/>
       <c r="B153" s="41"/>
       <c r="C153" s="21"/>
@@ -4648,7 +4543,7 @@
       <c r="G153" s="24"/>
       <c r="H153" s="29"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8">
       <c r="A154" s="38"/>
       <c r="B154" s="41"/>
       <c r="C154" s="21"/>
@@ -4658,7 +4553,7 @@
       <c r="G154" s="24"/>
       <c r="H154" s="29"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8">
       <c r="A155" s="38"/>
       <c r="B155" s="41"/>
       <c r="C155" s="21"/>
@@ -4668,7 +4563,7 @@
       <c r="G155" s="24"/>
       <c r="H155" s="29"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8">
       <c r="A156" s="38"/>
       <c r="B156" s="41"/>
       <c r="C156" s="21"/>
@@ -4678,7 +4573,7 @@
       <c r="G156" s="24"/>
       <c r="H156" s="29"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8">
       <c r="A157" s="38"/>
       <c r="B157" s="41"/>
       <c r="C157" s="21"/>
@@ -4688,7 +4583,7 @@
       <c r="G157" s="24"/>
       <c r="H157" s="29"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8">
       <c r="A158" s="38"/>
       <c r="B158" s="41"/>
       <c r="C158" s="21"/>
@@ -4698,7 +4593,7 @@
       <c r="G158" s="24"/>
       <c r="H158" s="29"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8">
       <c r="A159" s="38"/>
       <c r="B159" s="41"/>
       <c r="C159" s="21"/>
@@ -4708,7 +4603,7 @@
       <c r="G159" s="24"/>
       <c r="H159" s="29"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8">
       <c r="A160" s="38"/>
       <c r="B160" s="41"/>
       <c r="C160" s="21"/>
@@ -4718,7 +4613,7 @@
       <c r="G160" s="24"/>
       <c r="H160" s="29"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8">
       <c r="A161" s="38"/>
       <c r="B161" s="41"/>
       <c r="C161" s="21"/>
@@ -4728,7 +4623,7 @@
       <c r="G161" s="24"/>
       <c r="H161" s="29"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8">
       <c r="A162" s="38"/>
       <c r="B162" s="41"/>
       <c r="C162" s="21"/>
@@ -4738,7 +4633,7 @@
       <c r="G162" s="24"/>
       <c r="H162" s="29"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8">
       <c r="A163" s="38"/>
       <c r="B163" s="41"/>
       <c r="C163" s="21"/>
@@ -4748,27 +4643,27 @@
       <c r="G163" s="24"/>
       <c r="H163" s="29"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8">
       <c r="A164" s="38"/>
       <c r="B164" s="41"/>
       <c r="C164" s="21"/>
       <c r="D164" s="34"/>
       <c r="E164" s="24"/>
       <c r="F164" s="28"/>
-      <c r="G164" s="26"/>
+      <c r="G164" s="24"/>
       <c r="H164" s="29"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8">
       <c r="A165" s="38"/>
       <c r="B165" s="41"/>
       <c r="C165" s="21"/>
       <c r="D165" s="34"/>
       <c r="E165" s="24"/>
       <c r="F165" s="28"/>
-      <c r="G165" s="26"/>
+      <c r="G165" s="24"/>
       <c r="H165" s="29"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8">
       <c r="A166" s="38"/>
       <c r="B166" s="41"/>
       <c r="C166" s="21"/>
@@ -4778,7 +4673,7 @@
       <c r="G166" s="26"/>
       <c r="H166" s="29"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8">
       <c r="A167" s="38"/>
       <c r="B167" s="41"/>
       <c r="C167" s="21"/>
@@ -4788,7 +4683,7 @@
       <c r="G167" s="26"/>
       <c r="H167" s="29"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8">
       <c r="A168" s="38"/>
       <c r="B168" s="41"/>
       <c r="C168" s="21"/>
@@ -4798,7 +4693,7 @@
       <c r="G168" s="26"/>
       <c r="H168" s="29"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8">
       <c r="A169" s="38"/>
       <c r="B169" s="41"/>
       <c r="C169" s="21"/>
@@ -4808,7 +4703,7 @@
       <c r="G169" s="26"/>
       <c r="H169" s="29"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8">
       <c r="A170" s="38"/>
       <c r="B170" s="41"/>
       <c r="C170" s="21"/>
@@ -4818,7 +4713,7 @@
       <c r="G170" s="26"/>
       <c r="H170" s="29"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8">
       <c r="A171" s="38"/>
       <c r="B171" s="41"/>
       <c r="C171" s="21"/>
@@ -4828,7 +4723,7 @@
       <c r="G171" s="26"/>
       <c r="H171" s="29"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8">
       <c r="A172" s="38"/>
       <c r="B172" s="41"/>
       <c r="C172" s="21"/>
@@ -4838,7 +4733,7 @@
       <c r="G172" s="26"/>
       <c r="H172" s="29"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8">
       <c r="A173" s="38"/>
       <c r="B173" s="41"/>
       <c r="C173" s="21"/>
@@ -4848,7 +4743,7 @@
       <c r="G173" s="26"/>
       <c r="H173" s="29"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8">
       <c r="A174" s="38"/>
       <c r="B174" s="41"/>
       <c r="C174" s="21"/>
@@ -4858,7 +4753,7 @@
       <c r="G174" s="26"/>
       <c r="H174" s="29"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8">
       <c r="A175" s="38"/>
       <c r="B175" s="41"/>
       <c r="C175" s="21"/>
@@ -4868,7 +4763,7 @@
       <c r="G175" s="26"/>
       <c r="H175" s="29"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8">
       <c r="A176" s="38"/>
       <c r="B176" s="41"/>
       <c r="C176" s="21"/>
@@ -4878,7 +4773,7 @@
       <c r="G176" s="26"/>
       <c r="H176" s="29"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8">
       <c r="A177" s="38"/>
       <c r="B177" s="41"/>
       <c r="C177" s="21"/>
@@ -4888,27 +4783,27 @@
       <c r="G177" s="26"/>
       <c r="H177" s="29"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8">
       <c r="A178" s="38"/>
       <c r="B178" s="41"/>
       <c r="C178" s="21"/>
       <c r="D178" s="34"/>
       <c r="E178" s="24"/>
       <c r="F178" s="28"/>
-      <c r="G178" s="24"/>
+      <c r="G178" s="26"/>
       <c r="H178" s="29"/>
     </row>
-    <row r="179" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8">
       <c r="A179" s="38"/>
       <c r="B179" s="41"/>
       <c r="C179" s="21"/>
       <c r="D179" s="34"/>
       <c r="E179" s="24"/>
       <c r="F179" s="28"/>
-      <c r="G179" s="24"/>
+      <c r="G179" s="26"/>
       <c r="H179" s="29"/>
     </row>
-    <row r="180" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8">
       <c r="A180" s="38"/>
       <c r="B180" s="41"/>
       <c r="C180" s="21"/>
@@ -4918,7 +4813,7 @@
       <c r="G180" s="24"/>
       <c r="H180" s="29"/>
     </row>
-    <row r="181" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" s="7" customFormat="1">
       <c r="A181" s="38"/>
       <c r="B181" s="41"/>
       <c r="C181" s="21"/>
@@ -4928,157 +4823,177 @@
       <c r="G181" s="24"/>
       <c r="H181" s="29"/>
     </row>
-    <row r="182" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" s="7" customFormat="1">
       <c r="A182" s="38"/>
       <c r="B182" s="41"/>
       <c r="C182" s="21"/>
       <c r="D182" s="34"/>
-      <c r="E182" s="26"/>
+      <c r="E182" s="24"/>
       <c r="F182" s="28"/>
-      <c r="G182" s="26"/>
+      <c r="G182" s="24"/>
       <c r="H182" s="29"/>
     </row>
-    <row r="183" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" s="7" customFormat="1">
       <c r="A183" s="38"/>
       <c r="B183" s="41"/>
       <c r="C183" s="21"/>
       <c r="D183" s="34"/>
-      <c r="E183" s="26"/>
+      <c r="E183" s="24"/>
       <c r="F183" s="28"/>
-      <c r="G183" s="26"/>
+      <c r="G183" s="24"/>
       <c r="H183" s="29"/>
     </row>
-    <row r="184" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" s="7" customFormat="1">
       <c r="A184" s="38"/>
       <c r="B184" s="41"/>
       <c r="C184" s="21"/>
       <c r="D184" s="34"/>
-      <c r="E184" s="24"/>
+      <c r="E184" s="26"/>
       <c r="F184" s="28"/>
-      <c r="G184" s="24"/>
+      <c r="G184" s="26"/>
       <c r="H184" s="29"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="39"/>
-      <c r="B185" s="42"/>
-      <c r="C185" s="23"/>
-      <c r="D185" s="35"/>
-      <c r="E185" s="27"/>
-      <c r="F185" s="32"/>
-      <c r="G185" s="27"/>
-      <c r="H185" s="30"/>
-    </row>
-    <row r="186" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="10"/>
-      <c r="B186" s="13"/>
-      <c r="C186" s="11"/>
-      <c r="D186" s="11"/>
-      <c r="H186" s="7"/>
-    </row>
-    <row r="187" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="10"/>
-      <c r="B187" s="13"/>
-      <c r="C187" s="2" t="s">
+    <row r="185" spans="1:8" s="7" customFormat="1">
+      <c r="A185" s="38"/>
+      <c r="B185" s="41"/>
+      <c r="C185" s="21"/>
+      <c r="D185" s="34"/>
+      <c r="E185" s="26"/>
+      <c r="F185" s="28"/>
+      <c r="G185" s="26"/>
+      <c r="H185" s="29"/>
+    </row>
+    <row r="186" spans="1:8" s="7" customFormat="1">
+      <c r="A186" s="38"/>
+      <c r="B186" s="41"/>
+      <c r="C186" s="21"/>
+      <c r="D186" s="34"/>
+      <c r="E186" s="24"/>
+      <c r="F186" s="28"/>
+      <c r="G186" s="24"/>
+      <c r="H186" s="29"/>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="39"/>
+      <c r="B187" s="42"/>
+      <c r="C187" s="23"/>
+      <c r="D187" s="35"/>
+      <c r="E187" s="27"/>
+      <c r="F187" s="32"/>
+      <c r="G187" s="27"/>
+      <c r="H187" s="30"/>
+    </row>
+    <row r="188" spans="1:8" ht="12" customHeight="1">
+      <c r="A188" s="10"/>
+      <c r="B188" s="13"/>
+      <c r="C188" s="11"/>
+      <c r="D188" s="11"/>
+      <c r="H188" s="7"/>
+    </row>
+    <row r="189" spans="1:8" ht="12" customHeight="1">
+      <c r="A189" s="10"/>
+      <c r="B189" s="13"/>
+      <c r="C189" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H187" s="7"/>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A188" s="12"/>
-      <c r="B188" s="12"/>
-      <c r="C188" s="12"/>
-      <c r="D188" s="12"/>
-      <c r="E188" s="54" t="s">
+      <c r="H189" s="7"/>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="12"/>
+      <c r="B190" s="12"/>
+      <c r="C190" s="12"/>
+      <c r="D190" s="12"/>
+      <c r="E190" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="F188" s="54"/>
-      <c r="G188" s="54"/>
-      <c r="H188" s="54"/>
-    </row>
-    <row r="189" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="3"/>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3" t="s">
+      <c r="F190" s="55"/>
+      <c r="G190" s="55"/>
+      <c r="H190" s="55"/>
+    </row>
+    <row r="191" spans="1:8" ht="19.5" customHeight="1">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D189" s="3"/>
-      <c r="E189" s="57" t="s">
+      <c r="D191" s="3"/>
+      <c r="E191" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F189" s="57"/>
-      <c r="G189" s="57"/>
-      <c r="H189" s="57"/>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A190" s="11"/>
-      <c r="B190" s="11"/>
-      <c r="C190" s="11" t="s">
+      <c r="F191" s="58"/>
+      <c r="G191" s="58"/>
+      <c r="H191" s="58"/>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="11"/>
+      <c r="B192" s="11"/>
+      <c r="C192" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D190" s="11"/>
-      <c r="E190" s="54" t="s">
+      <c r="D192" s="11"/>
+      <c r="E192" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="F190" s="54"/>
-      <c r="G190" s="54"/>
-      <c r="H190" s="54"/>
-    </row>
-    <row r="191" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="1"/>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
-      <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
-    </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C194" s="3" t="s">
+      <c r="F192" s="55"/>
+      <c r="G192" s="55"/>
+      <c r="H192" s="55"/>
+    </row>
+    <row r="193" spans="1:7" ht="18" customHeight="1">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1"/>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="C196" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="3:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C195" s="2" t="s">
+    <row r="197" spans="1:7" ht="30.6" customHeight="1">
+      <c r="C197" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C196" s="2" t="s">
+    <row r="198" spans="1:7">
+      <c r="C198" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C197" s="2" t="s">
+    <row r="199" spans="1:7">
+      <c r="C199" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C198" s="2" t="s">
+    <row r="200" spans="1:7">
+      <c r="C200" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C199" s="2" t="s">
+    <row r="201" spans="1:7">
+      <c r="C201" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C200" s="2" t="s">
+    <row r="202" spans="1:7">
+      <c r="C202" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C204" s="3"/>
+    <row r="206" spans="1:7">
+      <c r="C206" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="E189:H189"/>
-    <mergeCell ref="E190:H190"/>
+    <mergeCell ref="E191:H191"/>
+    <mergeCell ref="E192:H192"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
-    <mergeCell ref="E188:H188"/>
+    <mergeCell ref="E190:H190"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E4:H4"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1992" yWindow="-120" windowWidth="19440" windowHeight="11280"/>
+    <workbookView xWindow="8328" yWindow="-120" windowWidth="19440" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="BIEU 02 -2022" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'BIEU 02 -2022'!$A$1:$H$192</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'BIEU 02 -2022'!$A$1:$H$193</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BIEU 02 -2022'!$7:$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -1158,7 +1158,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1311,9 +1311,6 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
@@ -1673,7 +1670,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:I207"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="6.44140625" style="2" customWidth="1"/>
@@ -2016,11 +2013,11 @@
         <v>29</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="5"/>
@@ -2029,104 +2026,104 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
     </row>
     <row r="5" spans="1:9" ht="21.9" customHeight="1">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
     </row>
     <row r="6" spans="1:9" ht="23.25" customHeight="1">
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
     </row>
     <row r="7" spans="1:9" ht="21.6" customHeight="1">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:9" ht="26.4" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="59" t="s">
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="62" t="s">
+      <c r="G8" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="63"/>
+      <c r="H8" s="62"/>
     </row>
     <row r="9" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="64" t="s">
+      <c r="A9" s="52"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="63" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="6">
@@ -2170,7 +2167,10 @@
         <f>E13+E21</f>
         <v>0</v>
       </c>
-      <c r="F12" s="31"/>
+      <c r="F12" s="31">
+        <f>E12+G12</f>
+        <v>0</v>
+      </c>
       <c r="G12" s="43">
         <f>G13+G21</f>
         <v>0</v>
@@ -2198,13 +2198,16 @@
         <f>E14+E15</f>
         <v>0</v>
       </c>
-      <c r="F13" s="28"/>
+      <c r="F13" s="31">
+        <f t="shared" ref="F13:F76" si="0">E13+G13</f>
+        <v>0</v>
+      </c>
       <c r="G13" s="48">
         <f>G14+G15</f>
         <v>0</v>
       </c>
       <c r="H13" s="29">
-        <f t="shared" ref="H13:H110" si="0">IFERROR(G13/E13,0)</f>
+        <f t="shared" ref="H13:H111" si="1">IFERROR(G13/E13,0)</f>
         <v>0</v>
       </c>
       <c r="I13" s="46"/>
@@ -2227,13 +2230,16 @@
         <f>E24-E21-E15</f>
         <v>0</v>
       </c>
-      <c r="F14" s="28"/>
+      <c r="F14" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G14" s="49">
         <f>G24-G21-G15</f>
         <v>0</v>
       </c>
       <c r="H14" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="47"/>
@@ -2256,13 +2262,16 @@
         <f>E16+E20</f>
         <v>0</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G15" s="49">
         <f>G16+G20</f>
         <v>0</v>
       </c>
       <c r="H15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2278,10 +2287,13 @@
       </c>
       <c r="D16" s="34"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="28"/>
+      <c r="F16" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G16" s="49"/>
       <c r="H16" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2297,10 +2309,13 @@
       </c>
       <c r="D17" s="34"/>
       <c r="E17" s="26"/>
-      <c r="F17" s="28"/>
+      <c r="F17" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G17" s="50"/>
       <c r="H17" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2316,10 +2331,13 @@
       </c>
       <c r="D18" s="34"/>
       <c r="E18" s="26"/>
-      <c r="F18" s="28"/>
+      <c r="F18" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G18" s="50"/>
       <c r="H18" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2335,10 +2353,13 @@
       </c>
       <c r="D19" s="34"/>
       <c r="E19" s="26"/>
-      <c r="F19" s="28"/>
+      <c r="F19" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G19" s="50"/>
       <c r="H19" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2354,10 +2375,13 @@
       </c>
       <c r="D20" s="34"/>
       <c r="E20" s="24"/>
-      <c r="F20" s="28"/>
+      <c r="F20" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G20" s="49"/>
       <c r="H20" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2379,13 +2403,16 @@
         <f>E22+E23</f>
         <v>0</v>
       </c>
-      <c r="F21" s="28"/>
+      <c r="F21" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G21" s="49">
         <f>G22+G23</f>
         <v>0</v>
       </c>
       <c r="H21" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2399,12 +2426,15 @@
       <c r="C22" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="52"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="28"/>
+      <c r="F22" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G22" s="49"/>
       <c r="H22" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2418,12 +2448,15 @@
       <c r="C23" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="52"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="24"/>
-      <c r="F23" s="28"/>
+      <c r="F23" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G23" s="49"/>
       <c r="H23" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2438,20 +2471,23 @@
         <v>68</v>
       </c>
       <c r="D24" s="34">
-        <f>D25+D62+D89</f>
+        <f>D25+D62+D90</f>
         <v>0</v>
       </c>
       <c r="E24" s="48">
-        <f>E25+E62+E89</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="28"/>
+        <f>E25+E62+E90</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G24" s="49">
-        <f>G25+G62+G89</f>
+        <f>G25+G62+G90</f>
         <v>0</v>
       </c>
       <c r="H24" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2466,20 +2502,23 @@
         <v>71</v>
       </c>
       <c r="D25" s="34">
-        <f>SUM(D26:D51)-D32-D47+D59</f>
+        <f>SUM(D26:D53)-D32-D47+D61</f>
         <v>0</v>
       </c>
       <c r="E25" s="49">
-        <f>SUM(E26:E51)-E32-E47+E59</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="28"/>
+        <f>SUM(E26:E53)-E32-E47+E61</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G25" s="49">
-        <f>SUM(G26:G51)-G32-G47+G59</f>
+        <f>SUM(G26:G53)-G32-G47+G61</f>
         <v>0</v>
       </c>
       <c r="H25" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2495,10 +2534,13 @@
       </c>
       <c r="D26" s="34"/>
       <c r="E26" s="24"/>
-      <c r="F26" s="28"/>
+      <c r="F26" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G26" s="24"/>
       <c r="H26" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2514,10 +2556,13 @@
       </c>
       <c r="D27" s="34"/>
       <c r="E27" s="26"/>
-      <c r="F27" s="28"/>
+      <c r="F27" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G27" s="26"/>
       <c r="H27" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2533,10 +2578,13 @@
       </c>
       <c r="D28" s="34"/>
       <c r="E28" s="26"/>
-      <c r="F28" s="28"/>
+      <c r="F28" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G28" s="26"/>
       <c r="H28" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2552,10 +2600,13 @@
       </c>
       <c r="D29" s="34"/>
       <c r="E29" s="24"/>
-      <c r="F29" s="28"/>
+      <c r="F29" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G29" s="24"/>
       <c r="H29" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2571,10 +2622,13 @@
       </c>
       <c r="D30" s="34"/>
       <c r="E30" s="24"/>
-      <c r="F30" s="28"/>
+      <c r="F30" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G30" s="26"/>
       <c r="H30" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2590,10 +2644,13 @@
       </c>
       <c r="D31" s="34"/>
       <c r="E31" s="24"/>
-      <c r="F31" s="28"/>
+      <c r="F31" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G31" s="26"/>
       <c r="H31" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2609,10 +2666,13 @@
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="24"/>
-      <c r="F32" s="28"/>
+      <c r="F32" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G32" s="26"/>
       <c r="H32" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2628,10 +2688,13 @@
       </c>
       <c r="D33" s="34"/>
       <c r="E33" s="24"/>
-      <c r="F33" s="28"/>
+      <c r="F33" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G33" s="25"/>
       <c r="H33" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2647,10 +2710,13 @@
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="24"/>
-      <c r="F34" s="28"/>
+      <c r="F34" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G34" s="26"/>
       <c r="H34" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2666,10 +2732,13 @@
       </c>
       <c r="D35" s="34"/>
       <c r="E35" s="24"/>
-      <c r="F35" s="28"/>
+      <c r="F35" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G35" s="26"/>
       <c r="H35" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2685,10 +2754,13 @@
       </c>
       <c r="D36" s="34"/>
       <c r="E36" s="24"/>
-      <c r="F36" s="28"/>
+      <c r="F36" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G36" s="26"/>
       <c r="H36" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2704,10 +2776,13 @@
       </c>
       <c r="D37" s="34"/>
       <c r="E37" s="24"/>
-      <c r="F37" s="28"/>
+      <c r="F37" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G37" s="26"/>
       <c r="H37" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2723,10 +2798,13 @@
       </c>
       <c r="D38" s="34"/>
       <c r="E38" s="24"/>
-      <c r="F38" s="28"/>
+      <c r="F38" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G38" s="26"/>
       <c r="H38" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2742,10 +2820,13 @@
       </c>
       <c r="D39" s="34"/>
       <c r="E39" s="24"/>
-      <c r="F39" s="28"/>
+      <c r="F39" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G39" s="26"/>
       <c r="H39" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2761,10 +2842,13 @@
       </c>
       <c r="D40" s="34"/>
       <c r="E40" s="24"/>
-      <c r="F40" s="28"/>
+      <c r="F40" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G40" s="26"/>
       <c r="H40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2780,10 +2864,13 @@
       </c>
       <c r="D41" s="34"/>
       <c r="E41" s="24"/>
-      <c r="F41" s="28"/>
+      <c r="F41" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G41" s="26"/>
       <c r="H41" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2799,10 +2886,13 @@
       </c>
       <c r="D42" s="34"/>
       <c r="E42" s="24"/>
-      <c r="F42" s="28"/>
+      <c r="F42" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G42" s="26"/>
       <c r="H42" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2818,10 +2908,13 @@
       </c>
       <c r="D43" s="34"/>
       <c r="E43" s="24"/>
-      <c r="F43" s="28"/>
+      <c r="F43" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G43" s="26"/>
       <c r="H43" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2837,10 +2930,13 @@
       </c>
       <c r="D44" s="34"/>
       <c r="E44" s="24"/>
-      <c r="F44" s="28"/>
+      <c r="F44" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G44" s="26"/>
       <c r="H44" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2856,10 +2952,13 @@
       </c>
       <c r="D45" s="34"/>
       <c r="E45" s="24"/>
-      <c r="F45" s="28"/>
+      <c r="F45" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G45" s="26"/>
       <c r="H45" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2875,10 +2974,13 @@
       </c>
       <c r="D46" s="34"/>
       <c r="E46" s="24"/>
-      <c r="F46" s="28"/>
+      <c r="F46" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G46" s="26"/>
       <c r="H46" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2894,10 +2996,13 @@
       </c>
       <c r="D47" s="34"/>
       <c r="E47" s="24"/>
-      <c r="F47" s="28"/>
+      <c r="F47" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G47" s="26"/>
       <c r="H47" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2913,10 +3018,13 @@
       </c>
       <c r="D48" s="34"/>
       <c r="E48" s="24"/>
-      <c r="F48" s="28"/>
+      <c r="F48" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G48" s="26"/>
       <c r="H48" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2932,10 +3040,13 @@
       </c>
       <c r="D49" s="34"/>
       <c r="E49" s="24"/>
-      <c r="F49" s="28"/>
+      <c r="F49" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G49" s="26"/>
       <c r="H49" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2951,10 +3062,13 @@
       </c>
       <c r="D50" s="34"/>
       <c r="E50" s="24"/>
-      <c r="F50" s="28"/>
+      <c r="F50" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G50" s="26"/>
       <c r="H50" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2970,10 +3084,13 @@
       </c>
       <c r="D51" s="34"/>
       <c r="E51" s="49"/>
-      <c r="F51" s="51"/>
+      <c r="F51" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G51" s="50"/>
       <c r="H51" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2989,10 +3106,13 @@
       </c>
       <c r="D52" s="34"/>
       <c r="E52" s="24"/>
-      <c r="F52" s="28"/>
+      <c r="F52" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G52" s="26"/>
       <c r="H52" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3014,8 +3134,8 @@
         <f>SUM(E54:E60)</f>
         <v>0</v>
       </c>
-      <c r="F53" s="28">
-        <f>SUM(F55:F60)</f>
+      <c r="F53" s="31">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G53" s="26">
@@ -3023,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3039,10 +3159,13 @@
       </c>
       <c r="D54" s="34"/>
       <c r="E54" s="24"/>
-      <c r="F54" s="28"/>
+      <c r="F54" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G54" s="26"/>
       <c r="H54" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3058,10 +3181,13 @@
       </c>
       <c r="D55" s="34"/>
       <c r="E55" s="24"/>
-      <c r="F55" s="28"/>
+      <c r="F55" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G55" s="26"/>
       <c r="H55" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3077,10 +3203,13 @@
       </c>
       <c r="D56" s="34"/>
       <c r="E56" s="24"/>
-      <c r="F56" s="28"/>
+      <c r="F56" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G56" s="26"/>
       <c r="H56" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3096,10 +3225,13 @@
       </c>
       <c r="D57" s="34"/>
       <c r="E57" s="24"/>
-      <c r="F57" s="28"/>
+      <c r="F57" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G57" s="26"/>
       <c r="H57" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3115,10 +3247,13 @@
       </c>
       <c r="D58" s="34"/>
       <c r="E58" s="24"/>
-      <c r="F58" s="28"/>
+      <c r="F58" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G58" s="26"/>
       <c r="H58" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3134,10 +3269,13 @@
       </c>
       <c r="D59" s="34"/>
       <c r="E59" s="24"/>
-      <c r="F59" s="28"/>
+      <c r="F59" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G59" s="26"/>
       <c r="H59" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3153,7 +3291,10 @@
       </c>
       <c r="D60" s="34"/>
       <c r="E60" s="24"/>
-      <c r="F60" s="28"/>
+      <c r="F60" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G60" s="26"/>
       <c r="H60" s="29"/>
     </row>
@@ -3169,7 +3310,10 @@
       </c>
       <c r="D61" s="34"/>
       <c r="E61" s="24"/>
-      <c r="F61" s="28"/>
+      <c r="F61" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G61" s="26"/>
       <c r="H61" s="29"/>
     </row>
@@ -3184,20 +3328,23 @@
         <v>175</v>
       </c>
       <c r="D62" s="34">
-        <f>SUM(D63:D88)-D69-D84</f>
+        <f>SUM(D63:D89)-D69-D84</f>
         <v>0</v>
       </c>
       <c r="E62" s="49">
-        <f>SUM(E63:E88)-E69-E84</f>
-        <v>0</v>
-      </c>
-      <c r="F62" s="51"/>
+        <f>SUM(E63:E89)-E69-E84</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G62" s="50">
-        <f>SUM(G63:G88)-G69-G84</f>
+        <f>SUM(G63:G89)-G69-G84</f>
         <v>0</v>
       </c>
       <c r="H62" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3213,10 +3360,13 @@
       </c>
       <c r="D63" s="34"/>
       <c r="E63" s="24"/>
-      <c r="F63" s="28"/>
+      <c r="F63" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G63" s="26"/>
       <c r="H63" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3232,10 +3382,13 @@
       </c>
       <c r="D64" s="34"/>
       <c r="E64" s="24"/>
-      <c r="F64" s="28"/>
+      <c r="F64" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G64" s="26"/>
       <c r="H64" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3251,10 +3404,13 @@
       </c>
       <c r="D65" s="34"/>
       <c r="E65" s="24"/>
-      <c r="F65" s="28"/>
+      <c r="F65" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G65" s="26"/>
       <c r="H65" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3270,10 +3426,13 @@
       </c>
       <c r="D66" s="34"/>
       <c r="E66" s="24"/>
-      <c r="F66" s="28"/>
+      <c r="F66" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G66" s="26"/>
       <c r="H66" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3289,10 +3448,13 @@
       </c>
       <c r="D67" s="34"/>
       <c r="E67" s="24"/>
-      <c r="F67" s="28"/>
+      <c r="F67" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G67" s="26"/>
       <c r="H67" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3308,10 +3470,13 @@
       </c>
       <c r="D68" s="34"/>
       <c r="E68" s="24"/>
-      <c r="F68" s="28"/>
+      <c r="F68" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G68" s="26"/>
       <c r="H68" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3327,10 +3492,13 @@
       </c>
       <c r="D69" s="34"/>
       <c r="E69" s="24"/>
-      <c r="F69" s="28"/>
+      <c r="F69" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G69" s="26"/>
       <c r="H69" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3346,10 +3514,13 @@
       </c>
       <c r="D70" s="34"/>
       <c r="E70" s="24"/>
-      <c r="F70" s="28"/>
+      <c r="F70" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G70" s="26"/>
       <c r="H70" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3365,10 +3536,13 @@
       </c>
       <c r="D71" s="34"/>
       <c r="E71" s="24"/>
-      <c r="F71" s="28"/>
+      <c r="F71" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G71" s="26"/>
       <c r="H71" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3384,10 +3558,13 @@
       </c>
       <c r="D72" s="34"/>
       <c r="E72" s="24"/>
-      <c r="F72" s="28"/>
+      <c r="F72" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G72" s="26"/>
       <c r="H72" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3403,10 +3580,13 @@
       </c>
       <c r="D73" s="34"/>
       <c r="E73" s="24"/>
-      <c r="F73" s="28"/>
+      <c r="F73" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G73" s="26"/>
       <c r="H73" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3422,10 +3602,13 @@
       </c>
       <c r="D74" s="34"/>
       <c r="E74" s="24"/>
-      <c r="F74" s="28"/>
+      <c r="F74" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G74" s="26"/>
       <c r="H74" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3441,10 +3624,13 @@
       </c>
       <c r="D75" s="34"/>
       <c r="E75" s="24"/>
-      <c r="F75" s="28"/>
+      <c r="F75" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G75" s="26"/>
       <c r="H75" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3460,10 +3646,13 @@
       </c>
       <c r="D76" s="34"/>
       <c r="E76" s="24"/>
-      <c r="F76" s="28"/>
+      <c r="F76" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G76" s="26"/>
       <c r="H76" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3479,10 +3668,13 @@
       </c>
       <c r="D77" s="34"/>
       <c r="E77" s="24"/>
-      <c r="F77" s="28"/>
+      <c r="F77" s="31">
+        <f t="shared" ref="F77:F111" si="2">E77+G77</f>
+        <v>0</v>
+      </c>
       <c r="G77" s="26"/>
       <c r="H77" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3498,10 +3690,13 @@
       </c>
       <c r="D78" s="34"/>
       <c r="E78" s="24"/>
-      <c r="F78" s="28"/>
+      <c r="F78" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G78" s="26"/>
       <c r="H78" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3517,10 +3712,13 @@
       </c>
       <c r="D79" s="34"/>
       <c r="E79" s="24"/>
-      <c r="F79" s="28"/>
+      <c r="F79" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G79" s="26"/>
       <c r="H79" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3536,10 +3734,13 @@
       </c>
       <c r="D80" s="34"/>
       <c r="E80" s="24"/>
-      <c r="F80" s="28"/>
+      <c r="F80" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G80" s="26"/>
       <c r="H80" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3555,10 +3756,13 @@
       </c>
       <c r="D81" s="34"/>
       <c r="E81" s="24"/>
-      <c r="F81" s="28"/>
+      <c r="F81" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G81" s="26"/>
       <c r="H81" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3574,10 +3778,13 @@
       </c>
       <c r="D82" s="34"/>
       <c r="E82" s="24"/>
-      <c r="F82" s="28"/>
+      <c r="F82" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G82" s="26"/>
       <c r="H82" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3593,10 +3800,13 @@
       </c>
       <c r="D83" s="34"/>
       <c r="E83" s="24"/>
-      <c r="F83" s="28"/>
+      <c r="F83" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G83" s="26"/>
       <c r="H83" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3612,10 +3822,13 @@
       </c>
       <c r="D84" s="34"/>
       <c r="E84" s="24"/>
-      <c r="F84" s="28"/>
+      <c r="F84" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G84" s="26"/>
       <c r="H84" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3631,10 +3844,13 @@
       </c>
       <c r="D85" s="34"/>
       <c r="E85" s="24"/>
-      <c r="F85" s="28"/>
+      <c r="F85" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G85" s="26"/>
       <c r="H85" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3650,10 +3866,13 @@
       </c>
       <c r="D86" s="34"/>
       <c r="E86" s="24"/>
-      <c r="F86" s="28"/>
+      <c r="F86" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G86" s="26"/>
       <c r="H86" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3669,10 +3888,13 @@
       </c>
       <c r="D87" s="34"/>
       <c r="E87" s="24"/>
-      <c r="F87" s="28"/>
+      <c r="F87" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G87" s="26"/>
       <c r="H87" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3688,445 +3910,517 @@
       </c>
       <c r="D88" s="34"/>
       <c r="E88" s="24"/>
-      <c r="F88" s="28"/>
+      <c r="F88" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G88" s="26"/>
       <c r="H88" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="38">
-        <v>177</v>
-      </c>
-      <c r="B89" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="C89" s="45" t="s">
-        <v>204</v>
-      </c>
+      <c r="A89" s="38"/>
+      <c r="B89" s="41"/>
+      <c r="C89" s="21"/>
       <c r="D89" s="34"/>
       <c r="E89" s="24"/>
-      <c r="F89" s="28"/>
+      <c r="F89" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G89" s="26"/>
-      <c r="H89" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="H89" s="29"/>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="38">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B90" s="41" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C90" s="45" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D90" s="34"/>
       <c r="E90" s="24"/>
-      <c r="F90" s="28"/>
+      <c r="F90" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G90" s="26"/>
       <c r="H90" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="38">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B91" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="C91" s="21" t="s">
-        <v>208</v>
+        <v>205</v>
+      </c>
+      <c r="C91" s="45" t="s">
+        <v>206</v>
       </c>
       <c r="D91" s="34"/>
       <c r="E91" s="24"/>
-      <c r="F91" s="28"/>
+      <c r="F91" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G91" s="26"/>
       <c r="H91" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="38">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B92" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="D92" s="34"/>
+        <v>208</v>
+      </c>
+      <c r="D92" s="51"/>
       <c r="E92" s="24"/>
-      <c r="F92" s="28"/>
+      <c r="F92" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G92" s="26"/>
       <c r="H92" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="38">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B93" s="41" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="D93" s="34"/>
+        <v>210</v>
+      </c>
+      <c r="D93" s="51"/>
       <c r="E93" s="24"/>
-      <c r="F93" s="28"/>
+      <c r="F93" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G93" s="26"/>
       <c r="H93" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="38">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B94" s="41" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="D94" s="34"/>
+        <v>212</v>
+      </c>
+      <c r="D94" s="51"/>
       <c r="E94" s="24"/>
-      <c r="F94" s="28"/>
+      <c r="F94" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G94" s="26"/>
       <c r="H94" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="38">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B95" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="D95" s="34"/>
+        <v>214</v>
+      </c>
+      <c r="D95" s="51"/>
       <c r="E95" s="24"/>
-      <c r="F95" s="28"/>
+      <c r="F95" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G95" s="26"/>
       <c r="H95" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="38">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B96" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="D96" s="34"/>
+        <v>216</v>
+      </c>
+      <c r="D96" s="51"/>
       <c r="E96" s="24"/>
-      <c r="F96" s="28"/>
+      <c r="F96" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G96" s="26"/>
       <c r="H96" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="38">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B97" s="41" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="D97" s="34"/>
+        <v>218</v>
+      </c>
+      <c r="D97" s="51"/>
       <c r="E97" s="24"/>
-      <c r="F97" s="28"/>
+      <c r="F97" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G97" s="26"/>
       <c r="H97" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="38">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B98" s="41" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="D98" s="34"/>
+        <v>220</v>
+      </c>
+      <c r="D98" s="51"/>
       <c r="E98" s="24"/>
-      <c r="F98" s="28"/>
+      <c r="F98" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G98" s="26"/>
       <c r="H98" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="38">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B99" s="41" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="D99" s="34"/>
+        <v>222</v>
+      </c>
+      <c r="D99" s="51"/>
       <c r="E99" s="24"/>
-      <c r="F99" s="28"/>
+      <c r="F99" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G99" s="26"/>
       <c r="H99" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="38">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B100" s="41" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="D100" s="34"/>
+        <v>224</v>
+      </c>
+      <c r="D100" s="51"/>
       <c r="E100" s="24"/>
-      <c r="F100" s="28"/>
+      <c r="F100" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G100" s="26"/>
       <c r="H100" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="38">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B101" s="41" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="D101" s="34"/>
+        <v>226</v>
+      </c>
+      <c r="D101" s="51"/>
       <c r="E101" s="24"/>
-      <c r="F101" s="28"/>
+      <c r="F101" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G101" s="26"/>
       <c r="H101" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="38">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B102" s="41" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D102" s="34"/>
+        <v>228</v>
+      </c>
+      <c r="D102" s="51"/>
       <c r="E102" s="24"/>
-      <c r="F102" s="28"/>
+      <c r="F102" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G102" s="26"/>
       <c r="H102" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="38">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B103" s="41" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="D103" s="34"/>
+        <v>230</v>
+      </c>
+      <c r="D103" s="51"/>
       <c r="E103" s="24"/>
-      <c r="F103" s="28"/>
+      <c r="F103" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G103" s="26"/>
       <c r="H103" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="38">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B104" s="41" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="D104" s="34"/>
+        <v>232</v>
+      </c>
+      <c r="D104" s="51"/>
       <c r="E104" s="24"/>
-      <c r="F104" s="28"/>
+      <c r="F104" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G104" s="26"/>
       <c r="H104" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="38">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B105" s="41" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="D105" s="34"/>
+        <v>234</v>
+      </c>
+      <c r="D105" s="51"/>
       <c r="E105" s="24"/>
-      <c r="F105" s="28"/>
+      <c r="F105" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G105" s="26"/>
       <c r="H105" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="38">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B106" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="D106" s="34"/>
+        <v>236</v>
+      </c>
+      <c r="D106" s="51"/>
       <c r="E106" s="24"/>
-      <c r="F106" s="28"/>
+      <c r="F106" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G106" s="26"/>
       <c r="H106" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="38">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B107" s="41" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="D107" s="34"/>
+        <v>238</v>
+      </c>
+      <c r="D107" s="51"/>
       <c r="E107" s="24"/>
-      <c r="F107" s="28"/>
+      <c r="F107" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G107" s="26"/>
       <c r="H107" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="38">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B108" s="41" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="D108" s="34"/>
+        <v>240</v>
+      </c>
+      <c r="D108" s="51"/>
       <c r="E108" s="24"/>
-      <c r="F108" s="28"/>
+      <c r="F108" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G108" s="26"/>
       <c r="H108" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="38">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B109" s="41" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="D109" s="34"/>
+        <v>242</v>
+      </c>
+      <c r="D109" s="51"/>
       <c r="E109" s="24"/>
-      <c r="F109" s="28"/>
+      <c r="F109" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G109" s="26"/>
       <c r="H109" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="38">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B110" s="41" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="D110" s="34"/>
+        <v>244</v>
+      </c>
+      <c r="D110" s="51"/>
       <c r="E110" s="24"/>
-      <c r="F110" s="28"/>
+      <c r="F110" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G110" s="26"/>
       <c r="H110" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="38"/>
-      <c r="B111" s="41"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="34"/>
+      <c r="A111" s="38">
+        <v>198</v>
+      </c>
+      <c r="B111" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="D111" s="51"/>
       <c r="E111" s="24"/>
-      <c r="F111" s="28"/>
+      <c r="F111" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G111" s="26"/>
-      <c r="H111" s="29"/>
+      <c r="H111" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="38"/>
       <c r="B112" s="41"/>
-      <c r="C112" s="21"/>
+      <c r="C112" s="19"/>
       <c r="D112" s="34"/>
       <c r="E112" s="24"/>
       <c r="F112" s="28"/>
@@ -4233,12 +4527,12 @@
       <c r="G122" s="26"/>
       <c r="H122" s="29"/>
     </row>
-    <row r="123" spans="1:8" s="9" customFormat="1">
+    <row r="123" spans="1:8">
       <c r="A123" s="38"/>
       <c r="B123" s="41"/>
       <c r="C123" s="21"/>
       <c r="D123" s="34"/>
-      <c r="E123" s="26"/>
+      <c r="E123" s="24"/>
       <c r="F123" s="28"/>
       <c r="G123" s="26"/>
       <c r="H123" s="29"/>
@@ -4306,27 +4600,27 @@
     <row r="130" spans="1:8" s="9" customFormat="1">
       <c r="A130" s="38"/>
       <c r="B130" s="41"/>
-      <c r="C130" s="19"/>
+      <c r="C130" s="21"/>
       <c r="D130" s="34"/>
       <c r="E130" s="26"/>
       <c r="F130" s="28"/>
       <c r="G130" s="26"/>
       <c r="H130" s="29"/>
     </row>
-    <row r="131" spans="1:8" s="7" customFormat="1">
+    <row r="131" spans="1:8" s="9" customFormat="1">
       <c r="A131" s="38"/>
       <c r="B131" s="41"/>
-      <c r="C131" s="20"/>
+      <c r="C131" s="19"/>
       <c r="D131" s="34"/>
-      <c r="E131" s="24"/>
+      <c r="E131" s="26"/>
       <c r="F131" s="28"/>
-      <c r="G131" s="24"/>
+      <c r="G131" s="26"/>
       <c r="H131" s="29"/>
     </row>
     <row r="132" spans="1:8" s="7" customFormat="1">
       <c r="A132" s="38"/>
       <c r="B132" s="41"/>
-      <c r="C132" s="19"/>
+      <c r="C132" s="20"/>
       <c r="D132" s="34"/>
       <c r="E132" s="24"/>
       <c r="F132" s="28"/>
@@ -4346,7 +4640,7 @@
     <row r="134" spans="1:8" s="7" customFormat="1">
       <c r="A134" s="38"/>
       <c r="B134" s="41"/>
-      <c r="C134" s="21"/>
+      <c r="C134" s="19"/>
       <c r="D134" s="34"/>
       <c r="E134" s="24"/>
       <c r="F134" s="28"/>
@@ -4366,7 +4660,7 @@
     <row r="136" spans="1:8" s="7" customFormat="1">
       <c r="A136" s="38"/>
       <c r="B136" s="41"/>
-      <c r="C136" s="19"/>
+      <c r="C136" s="21"/>
       <c r="D136" s="34"/>
       <c r="E136" s="24"/>
       <c r="F136" s="28"/>
@@ -4376,7 +4670,7 @@
     <row r="137" spans="1:8" s="7" customFormat="1">
       <c r="A137" s="38"/>
       <c r="B137" s="41"/>
-      <c r="C137" s="21"/>
+      <c r="C137" s="19"/>
       <c r="D137" s="34"/>
       <c r="E137" s="24"/>
       <c r="F137" s="28"/>
@@ -4386,7 +4680,7 @@
     <row r="138" spans="1:8" s="7" customFormat="1">
       <c r="A138" s="38"/>
       <c r="B138" s="41"/>
-      <c r="C138" s="22"/>
+      <c r="C138" s="21"/>
       <c r="D138" s="34"/>
       <c r="E138" s="24"/>
       <c r="F138" s="28"/>
@@ -4396,7 +4690,7 @@
     <row r="139" spans="1:8" s="7" customFormat="1">
       <c r="A139" s="38"/>
       <c r="B139" s="41"/>
-      <c r="C139" s="21"/>
+      <c r="C139" s="22"/>
       <c r="D139" s="34"/>
       <c r="E139" s="24"/>
       <c r="F139" s="28"/>
@@ -4493,7 +4787,7 @@
       <c r="G148" s="24"/>
       <c r="H148" s="29"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" s="7" customFormat="1">
       <c r="A149" s="38"/>
       <c r="B149" s="41"/>
       <c r="C149" s="21"/>
@@ -4670,7 +4964,7 @@
       <c r="D166" s="34"/>
       <c r="E166" s="24"/>
       <c r="F166" s="28"/>
-      <c r="G166" s="26"/>
+      <c r="G166" s="24"/>
       <c r="H166" s="29"/>
     </row>
     <row r="167" spans="1:8">
@@ -4810,10 +5104,10 @@
       <c r="D180" s="34"/>
       <c r="E180" s="24"/>
       <c r="F180" s="28"/>
-      <c r="G180" s="24"/>
+      <c r="G180" s="26"/>
       <c r="H180" s="29"/>
     </row>
-    <row r="181" spans="1:8" s="7" customFormat="1">
+    <row r="181" spans="1:8">
       <c r="A181" s="38"/>
       <c r="B181" s="41"/>
       <c r="C181" s="21"/>
@@ -4848,9 +5142,9 @@
       <c r="B184" s="41"/>
       <c r="C184" s="21"/>
       <c r="D184" s="34"/>
-      <c r="E184" s="26"/>
+      <c r="E184" s="24"/>
       <c r="F184" s="28"/>
-      <c r="G184" s="26"/>
+      <c r="G184" s="24"/>
       <c r="H184" s="29"/>
     </row>
     <row r="185" spans="1:8" s="7" customFormat="1">
@@ -4868,132 +5162,142 @@
       <c r="B186" s="41"/>
       <c r="C186" s="21"/>
       <c r="D186" s="34"/>
-      <c r="E186" s="24"/>
+      <c r="E186" s="26"/>
       <c r="F186" s="28"/>
-      <c r="G186" s="24"/>
+      <c r="G186" s="26"/>
       <c r="H186" s="29"/>
     </row>
-    <row r="187" spans="1:8">
-      <c r="A187" s="39"/>
-      <c r="B187" s="42"/>
-      <c r="C187" s="23"/>
-      <c r="D187" s="35"/>
-      <c r="E187" s="27"/>
-      <c r="F187" s="32"/>
-      <c r="G187" s="27"/>
-      <c r="H187" s="30"/>
-    </row>
-    <row r="188" spans="1:8" ht="12" customHeight="1">
-      <c r="A188" s="10"/>
-      <c r="B188" s="13"/>
-      <c r="C188" s="11"/>
-      <c r="D188" s="11"/>
-      <c r="H188" s="7"/>
+    <row r="187" spans="1:8" s="7" customFormat="1">
+      <c r="A187" s="38"/>
+      <c r="B187" s="41"/>
+      <c r="C187" s="21"/>
+      <c r="D187" s="34"/>
+      <c r="E187" s="24"/>
+      <c r="F187" s="28"/>
+      <c r="G187" s="24"/>
+      <c r="H187" s="29"/>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="39"/>
+      <c r="B188" s="42"/>
+      <c r="C188" s="23"/>
+      <c r="D188" s="35"/>
+      <c r="E188" s="27"/>
+      <c r="F188" s="32"/>
+      <c r="G188" s="27"/>
+      <c r="H188" s="30"/>
     </row>
     <row r="189" spans="1:8" ht="12" customHeight="1">
       <c r="A189" s="10"/>
       <c r="B189" s="13"/>
-      <c r="C189" s="2" t="s">
+      <c r="C189" s="11"/>
+      <c r="D189" s="11"/>
+      <c r="H189" s="7"/>
+    </row>
+    <row r="190" spans="1:8" ht="12" customHeight="1">
+      <c r="A190" s="10"/>
+      <c r="B190" s="13"/>
+      <c r="C190" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H189" s="7"/>
-    </row>
-    <row r="190" spans="1:8">
-      <c r="A190" s="12"/>
-      <c r="B190" s="12"/>
-      <c r="C190" s="12"/>
-      <c r="D190" s="12"/>
-      <c r="E190" s="55" t="s">
+      <c r="H190" s="7"/>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="12"/>
+      <c r="B191" s="12"/>
+      <c r="C191" s="12"/>
+      <c r="D191" s="12"/>
+      <c r="E191" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="F190" s="55"/>
-      <c r="G190" s="55"/>
-      <c r="H190" s="55"/>
-    </row>
-    <row r="191" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A191" s="3"/>
-      <c r="B191" s="3"/>
-      <c r="C191" s="3" t="s">
+      <c r="F191" s="54"/>
+      <c r="G191" s="54"/>
+      <c r="H191" s="54"/>
+    </row>
+    <row r="192" spans="1:8" ht="19.5" customHeight="1">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D191" s="3"/>
-      <c r="E191" s="58" t="s">
+      <c r="D192" s="3"/>
+      <c r="E192" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F191" s="58"/>
-      <c r="G191" s="58"/>
-      <c r="H191" s="58"/>
-    </row>
-    <row r="192" spans="1:8">
-      <c r="A192" s="11"/>
-      <c r="B192" s="11"/>
-      <c r="C192" s="11" t="s">
+      <c r="F192" s="57"/>
+      <c r="G192" s="57"/>
+      <c r="H192" s="57"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="11"/>
+      <c r="B193" s="11"/>
+      <c r="C193" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D192" s="11"/>
-      <c r="E192" s="55" t="s">
+      <c r="D193" s="11"/>
+      <c r="E193" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F192" s="55"/>
-      <c r="G192" s="55"/>
-      <c r="H192" s="55"/>
-    </row>
-    <row r="193" spans="1:7" ht="18" customHeight="1">
-      <c r="A193" s="1"/>
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
-      <c r="E193" s="1"/>
-      <c r="F193" s="1"/>
-      <c r="G193" s="1"/>
-    </row>
-    <row r="196" spans="1:7">
-      <c r="C196" s="3" t="s">
+      <c r="F193" s="54"/>
+      <c r="G193" s="54"/>
+      <c r="H193" s="54"/>
+    </row>
+    <row r="194" spans="1:8" ht="18" customHeight="1">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="C197" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="30.6" customHeight="1">
-      <c r="C197" s="2" t="s">
+    <row r="198" spans="1:8" ht="30.6" customHeight="1">
+      <c r="C198" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
-      <c r="C198" s="2" t="s">
+    <row r="199" spans="1:8">
+      <c r="C199" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
-      <c r="C199" s="2" t="s">
+    <row r="200" spans="1:8">
+      <c r="C200" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
-      <c r="C200" s="2" t="s">
+    <row r="201" spans="1:8">
+      <c r="C201" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
-      <c r="C201" s="2" t="s">
+    <row r="202" spans="1:8">
+      <c r="C202" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
-      <c r="C202" s="2" t="s">
+    <row r="203" spans="1:8">
+      <c r="C203" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
-      <c r="C206" s="3"/>
+    <row r="207" spans="1:8">
+      <c r="C207" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="E191:H191"/>
     <mergeCell ref="E192:H192"/>
+    <mergeCell ref="E193:H193"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
-    <mergeCell ref="E190:H190"/>
+    <mergeCell ref="E191:H191"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E4:H4"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\IMS_REPORTS\IMS_REPORTS\web\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cap nhat CN\IMS_REPORT KHNV2023\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="224">
   <si>
     <t>CỘNG HOÀ XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -646,9 +646,6 @@
     <t>XD00046</t>
   </si>
   <si>
-    <t>XD00047</t>
-  </si>
-  <si>
     <t>XD00111</t>
   </si>
   <si>
@@ -694,9 +691,6 @@
     <t>XD00061</t>
   </si>
   <si>
-    <t>XD00062</t>
-  </si>
-  <si>
     <t>XD00063</t>
   </si>
   <si>
@@ -706,15 +700,6 @@
     <t>XD00065</t>
   </si>
   <si>
-    <t>XD00066</t>
-  </si>
-  <si>
-    <t>XD00067</t>
-  </si>
-  <si>
-    <t>XD00068</t>
-  </si>
-  <si>
     <t>XD00069</t>
   </si>
   <si>
@@ -727,9 +712,6 @@
     <t>XD00072</t>
   </si>
   <si>
-    <t>XD00073</t>
-  </si>
-  <si>
     <t>XD00112</t>
   </si>
   <si>
@@ -751,18 +733,6 @@
     <t>XD00078</t>
   </si>
   <si>
-    <t>XD00079</t>
-  </si>
-  <si>
-    <t>XD00080</t>
-  </si>
-  <si>
-    <t>XD00081</t>
-  </si>
-  <si>
-    <t>XD00082</t>
-  </si>
-  <si>
     <t>XD00083</t>
   </si>
   <si>
@@ -794,6 +764,33 @@
   </si>
   <si>
     <t>XD00115</t>
+  </si>
+  <si>
+    <t>XD00002</t>
+  </si>
+  <si>
+    <t>XD00092</t>
+  </si>
+  <si>
+    <t>XD00093</t>
+  </si>
+  <si>
+    <t>XD00094</t>
+  </si>
+  <si>
+    <t>XD00095</t>
+  </si>
+  <si>
+    <t>XD00096</t>
+  </si>
+  <si>
+    <t>XD00097</t>
+  </si>
+  <si>
+    <t>XD00098</t>
+  </si>
+  <si>
+    <t>XD00099</t>
   </si>
 </sst>
 </file>
@@ -1826,10 +1823,43 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1849,39 +1879,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2267,12 +2264,12 @@
         <v>39</v>
       </c>
       <c r="B2" s="12"/>
-      <c r="E2" s="116" t="s">
+      <c r="E2" s="117" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:52">
       <c r="A3" s="12" t="s">
@@ -2280,87 +2277,87 @@
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
-      <c r="D3" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
+      <c r="D3" s="122" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
     </row>
     <row r="4" spans="1:52">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
-      <c r="E4" s="125" t="s">
+      <c r="E4" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
     </row>
     <row r="5" spans="1:52" ht="21.9" customHeight="1">
-      <c r="A5" s="126" t="s">
+      <c r="A5" s="124" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
     </row>
     <row r="6" spans="1:52" ht="23.25" customHeight="1">
-      <c r="F6" s="133" t="s">
+      <c r="F6" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
     </row>
     <row r="7" spans="1:52" s="9" customFormat="1" ht="27" customHeight="1">
-      <c r="A7" s="123" t="s">
+      <c r="A7" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="117"/>
-      <c r="C7" s="123" t="s">
+      <c r="B7" s="128"/>
+      <c r="C7" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="123" t="s">
+      <c r="D7" s="126" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="123" t="s">
+      <c r="E7" s="126" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="124" t="s">
+      <c r="F7" s="127" t="s">
         <v>100</v>
       </c>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
     </row>
     <row r="8" spans="1:52" s="9" customFormat="1" ht="32.25" customHeight="1">
-      <c r="A8" s="123"/>
-      <c r="B8" s="118"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="117" t="s">
+      <c r="A8" s="126"/>
+      <c r="B8" s="129"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="120" t="s">
+      <c r="G8" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="121"/>
+      <c r="H8" s="132"/>
     </row>
     <row r="9" spans="1:52" s="9" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A9" s="123"/>
-      <c r="B9" s="118"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="123"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="122" t="s">
+      <c r="A9" s="126"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="133" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="134" t="s">
@@ -2368,13 +2365,13 @@
       </c>
     </row>
     <row r="10" spans="1:52" s="9" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="123"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="122"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="133"/>
       <c r="H10" s="134"/>
     </row>
     <row r="11" spans="1:52" s="9" customFormat="1" ht="18.75" customHeight="1">
@@ -2856,7 +2853,7 @@
       </c>
     </row>
     <row r="19" spans="1:52" ht="22.5" customHeight="1">
-      <c r="A19" s="130" t="s">
+      <c r="A19" s="120" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="36" t="s">
@@ -2878,7 +2875,7 @@
       </c>
     </row>
     <row r="20" spans="1:52" ht="22.5" customHeight="1">
-      <c r="A20" s="131"/>
+      <c r="A20" s="121"/>
       <c r="B20" s="34" t="s">
         <v>128</v>
       </c>
@@ -3052,7 +3049,7 @@
         <v>108</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>131</v>
+        <v>215</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>113</v>
@@ -3127,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" s="26" t="s">
         <v>72</v>
@@ -3149,7 +3146,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="76" t="s">
         <v>73</v>
@@ -3171,7 +3168,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="77" t="s">
         <v>74</v>
@@ -3193,7 +3190,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C27" s="77" t="s">
         <v>75</v>
@@ -3215,7 +3212,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C28" s="78" t="s">
         <v>114</v>
@@ -3237,7 +3234,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C29" s="78" t="s">
         <v>115</v>
@@ -3259,7 +3256,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C30" s="77" t="s">
         <v>78</v>
@@ -3281,7 +3278,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C31" s="80" t="s">
         <v>61</v>
@@ -3303,7 +3300,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C32" s="77" t="s">
         <v>76</v>
@@ -3369,7 +3366,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C33" s="77" t="s">
         <v>60</v>
@@ -3391,7 +3388,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" s="77" t="s">
         <v>62</v>
@@ -3413,7 +3410,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C35" s="77" t="s">
         <v>6</v>
@@ -3479,7 +3476,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C36" s="77" t="s">
         <v>95</v>
@@ -3545,7 +3542,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C37" s="77" t="s">
         <v>66</v>
@@ -3611,7 +3608,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C38" s="77" t="s">
         <v>67</v>
@@ -3677,7 +3674,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C39" s="26" t="s">
         <v>65</v>
@@ -3743,7 +3740,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C40" s="77" t="s">
         <v>71</v>
@@ -3809,7 +3806,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" s="77" t="s">
         <v>70</v>
@@ -3875,7 +3872,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C42" s="77" t="s">
         <v>22</v>
@@ -3897,7 +3894,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C43" s="77" t="s">
         <v>105</v>
@@ -3963,7 +3960,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C44" s="81" t="s">
         <v>59</v>
@@ -4029,7 +4026,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C45" s="77" t="s">
         <v>111</v>
@@ -4049,7 +4046,7 @@
     <row r="46" spans="1:52" ht="22.5" customHeight="1">
       <c r="A46" s="25"/>
       <c r="B46" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C46" s="82" t="s">
         <v>106</v>
@@ -4071,7 +4068,7 @@
         <v>22</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C47" s="78" t="s">
         <v>118</v>
@@ -4093,7 +4090,7 @@
         <v>23</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C48" s="78" t="s">
         <v>91</v>
@@ -4159,7 +4156,7 @@
         <v>24</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C49" s="81" t="s">
         <v>79</v>
@@ -4225,7 +4222,7 @@
         <v>25</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C50" s="81" t="s">
         <v>77</v>
@@ -4291,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C51" s="26" t="s">
         <v>58</v>
@@ -4366,7 +4363,7 @@
         <v>4</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C52" s="84" t="s">
         <v>13</v>
@@ -4430,7 +4427,7 @@
     <row r="53" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A53" s="85"/>
       <c r="B53" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C53" s="84" t="s">
         <v>14</v>
@@ -4494,7 +4491,7 @@
     <row r="54" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="85"/>
       <c r="B54" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C54" s="82" t="s">
         <v>56</v>
@@ -4558,7 +4555,7 @@
     <row r="55" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="85"/>
       <c r="B55" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C55" s="82" t="s">
         <v>57</v>
@@ -4622,7 +4619,7 @@
     <row r="56" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A56" s="85"/>
       <c r="B56" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C56" s="84" t="s">
         <v>55</v>
@@ -4686,7 +4683,7 @@
     <row r="57" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A57" s="85"/>
       <c r="B57" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C57" s="84" t="s">
         <v>63</v>
@@ -4750,7 +4747,7 @@
     <row r="58" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A58" s="86"/>
       <c r="B58" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C58" s="84" t="s">
         <v>86</v>
@@ -4816,7 +4813,7 @@
         <v>27</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C59" s="26" t="s">
         <v>48</v>
@@ -4882,7 +4879,7 @@
         <v>109</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C60" s="29" t="s">
         <v>110</v>
@@ -4957,7 +4954,7 @@
         <v>1</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C61" s="78" t="s">
         <v>90</v>
@@ -5023,7 +5020,7 @@
         <v>2</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C62" s="26" t="s">
         <v>69</v>
@@ -5087,7 +5084,7 @@
     <row r="63" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A63" s="25"/>
       <c r="B63" s="25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C63" s="82" t="s">
         <v>116</v>
@@ -5151,7 +5148,7 @@
     <row r="64" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A64" s="25"/>
       <c r="B64" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C64" s="82" t="s">
         <v>117</v>
@@ -5217,7 +5214,7 @@
         <v>3</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C65" s="78" t="s">
         <v>92</v>
@@ -5283,7 +5280,7 @@
         <v>4</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C66" s="78" t="s">
         <v>93</v>
@@ -5349,7 +5346,7 @@
         <v>5</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="78" t="s">
         <v>94</v>
@@ -5415,7 +5412,7 @@
         <v>5</v>
       </c>
       <c r="B68" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C68" s="22" t="s">
         <v>43</v>
@@ -5490,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C69" s="26" t="s">
         <v>72</v>
@@ -5556,7 +5553,7 @@
         <v>2</v>
       </c>
       <c r="B70" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C70" s="76" t="s">
         <v>73</v>
@@ -5622,7 +5619,7 @@
         <v>3</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C71" s="77" t="s">
         <v>74</v>
@@ -5688,7 +5685,7 @@
         <v>4</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C72" s="77" t="s">
         <v>75</v>
@@ -5754,7 +5751,7 @@
         <v>5</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C73" s="26" t="s">
         <v>68</v>
@@ -5820,7 +5817,7 @@
         <v>23</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C74" s="87" t="s">
         <v>103</v>
@@ -5886,7 +5883,7 @@
         <v>6</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C75" s="77" t="s">
         <v>78</v>
@@ -5952,7 +5949,7 @@
         <v>23</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C76" s="80" t="s">
         <v>61</v>
@@ -6018,7 +6015,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C77" s="77" t="s">
         <v>76</v>
@@ -6040,7 +6037,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C78" s="77" t="s">
         <v>60</v>
@@ -6106,7 +6103,7 @@
         <v>9</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C79" s="77" t="s">
         <v>62</v>
@@ -6172,7 +6169,7 @@
         <v>10</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C80" s="77" t="s">
         <v>6</v>
@@ -6238,7 +6235,7 @@
         <v>11</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C81" s="77" t="s">
         <v>95</v>
@@ -6260,7 +6257,7 @@
         <v>12</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C82" s="77" t="s">
         <v>66</v>
@@ -6282,7 +6279,7 @@
         <v>13</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C83" s="77" t="s">
         <v>65</v>
@@ -6304,7 +6301,7 @@
         <v>14</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C84" s="77" t="s">
         <v>71</v>
@@ -6326,7 +6323,7 @@
         <v>15</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C85" s="77" t="s">
         <v>70</v>
@@ -6348,7 +6345,7 @@
         <v>16</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C86" s="26" t="s">
         <v>69</v>
@@ -6370,7 +6367,7 @@
         <v>23</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C87" s="88" t="s">
         <v>104</v>
@@ -6390,7 +6387,7 @@
     <row r="88" spans="1:52" ht="21" customHeight="1">
       <c r="A88" s="25"/>
       <c r="B88" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C88" s="82" t="s">
         <v>112</v>
@@ -6410,7 +6407,7 @@
     <row r="89" spans="1:52" ht="21.75" customHeight="1">
       <c r="A89" s="25"/>
       <c r="B89" s="25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C89" s="82" t="s">
         <v>107</v>
@@ -6432,7 +6429,7 @@
         <v>17</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C90" s="78" t="s">
         <v>92</v>
@@ -6454,7 +6451,7 @@
         <v>18</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" s="78" t="s">
         <v>93</v>
@@ -6476,7 +6473,7 @@
         <v>19</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C92" s="78" t="s">
         <v>94</v>
@@ -6498,7 +6495,7 @@
         <v>20</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C93" s="81" t="s">
         <v>77</v>
@@ -6520,7 +6517,7 @@
         <v>21</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C94" s="26" t="s">
         <v>48</v>
@@ -6542,7 +6539,7 @@
         <v>7</v>
       </c>
       <c r="B95" s="34" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C95" s="22" t="s">
         <v>15</v>
@@ -6608,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="B96" s="34" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C96" s="22" t="s">
         <v>53</v>
@@ -6674,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C97" s="90" t="s">
         <v>96</v>
@@ -6740,7 +6737,7 @@
         <v>27</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C98" s="92" t="s">
         <v>33</v>
@@ -6806,7 +6803,7 @@
         <v>27</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C99" s="92" t="s">
         <v>49</v>
@@ -6872,7 +6869,7 @@
         <v>2</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C100" s="77" t="s">
         <v>97</v>
@@ -6938,7 +6935,7 @@
         <v>27</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C101" s="92" t="s">
         <v>32</v>
@@ -7004,7 +7001,7 @@
         <v>27</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C102" s="93" t="s">
         <v>50</v>
@@ -7070,7 +7067,7 @@
         <v>3</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C103" s="95" t="s">
         <v>98</v>
@@ -7136,7 +7133,7 @@
         <v>4</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C104" s="71" t="s">
         <v>31</v>
@@ -7202,7 +7199,7 @@
         <v>27</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C105" s="92" t="s">
         <v>30</v>
@@ -7268,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C106" s="93" t="s">
         <v>51</v>
@@ -7334,7 +7331,7 @@
         <v>5</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C107" s="77" t="s">
         <v>29</v>
@@ -7400,7 +7397,7 @@
         <v>6</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C108" s="71" t="s">
         <v>28</v>
@@ -7466,7 +7463,7 @@
         <v>27</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C109" s="92" t="s">
         <v>34</v>
@@ -7532,7 +7529,7 @@
         <v>7</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C110" s="26" t="s">
         <v>36</v>
@@ -7596,7 +7593,7 @@
     <row r="111" spans="1:52" s="3" customFormat="1" ht="27" customHeight="1">
       <c r="A111" s="91"/>
       <c r="B111" s="25" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C111" s="82" t="s">
         <v>35</v>
@@ -7660,7 +7657,7 @@
     <row r="112" spans="1:52" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A112" s="91"/>
       <c r="B112" s="25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C112" s="26" t="s">
         <v>44</v>
@@ -7726,7 +7723,7 @@
         <v>8</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C113" s="77" t="s">
         <v>80</v>
@@ -7748,7 +7745,7 @@
         <v>9</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>222</v>
+        <v>120</v>
       </c>
       <c r="C114" s="77" t="s">
         <v>40</v>
@@ -7770,7 +7767,7 @@
         <v>10</v>
       </c>
       <c r="B115" s="34" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C115" s="71" t="s">
         <v>52</v>
@@ -7792,7 +7789,7 @@
         <v>18</v>
       </c>
       <c r="B116" s="34" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C116" s="97" t="s">
         <v>64</v>
@@ -7836,12 +7833,12 @@
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
       <c r="D119" s="15"/>
-      <c r="E119" s="116" t="s">
+      <c r="E119" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="F119" s="116"/>
-      <c r="G119" s="116"/>
-      <c r="H119" s="116"/>
+      <c r="F119" s="117"/>
+      <c r="G119" s="117"/>
+      <c r="H119" s="117"/>
     </row>
     <row r="120" spans="1:8" ht="19.5" customHeight="1">
       <c r="A120" s="16"/>
@@ -7850,12 +7847,12 @@
         <v>37</v>
       </c>
       <c r="D120" s="16"/>
-      <c r="E120" s="115" t="s">
+      <c r="E120" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="F120" s="115"/>
-      <c r="G120" s="115"/>
-      <c r="H120" s="115"/>
+      <c r="F120" s="118"/>
+      <c r="G120" s="118"/>
+      <c r="H120" s="118"/>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="17"/>
@@ -7864,12 +7861,12 @@
         <v>38</v>
       </c>
       <c r="D121" s="17"/>
-      <c r="E121" s="116" t="s">
+      <c r="E121" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="F121" s="116"/>
-      <c r="G121" s="116"/>
-      <c r="H121" s="116"/>
+      <c r="F121" s="117"/>
+      <c r="G121" s="117"/>
+      <c r="H121" s="117"/>
     </row>
     <row r="122" spans="1:8" ht="18" customHeight="1">
       <c r="A122" s="9"/>
@@ -7881,52 +7878,52 @@
       <c r="G122" s="2"/>
     </row>
     <row r="123" spans="1:8" ht="321.75" customHeight="1">
-      <c r="C123" s="129" t="s">
+      <c r="C123" s="119" t="s">
         <v>119</v>
       </c>
-      <c r="D123" s="129"/>
-      <c r="E123" s="129"/>
-      <c r="F123" s="129"/>
-      <c r="G123" s="129"/>
-      <c r="H123" s="129"/>
+      <c r="D123" s="119"/>
+      <c r="E123" s="119"/>
+      <c r="F123" s="119"/>
+      <c r="G123" s="119"/>
+      <c r="H123" s="119"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="C124" s="127"/>
-      <c r="D124" s="128"/>
-      <c r="E124" s="128"/>
-      <c r="F124" s="128"/>
-      <c r="G124" s="128"/>
-      <c r="H124" s="128"/>
+      <c r="C124" s="115"/>
+      <c r="D124" s="116"/>
+      <c r="E124" s="116"/>
+      <c r="F124" s="116"/>
+      <c r="G124" s="116"/>
+      <c r="H124" s="116"/>
     </row>
     <row r="125" spans="1:8" ht="32.25" customHeight="1">
-      <c r="C125" s="127"/>
-      <c r="D125" s="128"/>
-      <c r="E125" s="128"/>
-      <c r="F125" s="128"/>
-      <c r="G125" s="128"/>
-      <c r="H125" s="128"/>
+      <c r="C125" s="115"/>
+      <c r="D125" s="116"/>
+      <c r="E125" s="116"/>
+      <c r="F125" s="116"/>
+      <c r="G125" s="116"/>
+      <c r="H125" s="116"/>
     </row>
     <row r="126" spans="1:8" ht="18.75" customHeight="1">
-      <c r="C126" s="127"/>
-      <c r="D126" s="128"/>
-      <c r="E126" s="128"/>
-      <c r="F126" s="128"/>
-      <c r="G126" s="128"/>
-      <c r="H126" s="128"/>
+      <c r="C126" s="115"/>
+      <c r="D126" s="116"/>
+      <c r="E126" s="116"/>
+      <c r="F126" s="116"/>
+      <c r="G126" s="116"/>
+      <c r="H126" s="116"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="C128" s="127"/>
-      <c r="D128" s="128"/>
-      <c r="E128" s="128"/>
-      <c r="F128" s="128"/>
-      <c r="G128" s="128"/>
-      <c r="H128" s="128"/>
+      <c r="C128" s="115"/>
+      <c r="D128" s="116"/>
+      <c r="E128" s="116"/>
+      <c r="F128" s="116"/>
+      <c r="G128" s="116"/>
+      <c r="H128" s="116"/>
     </row>
     <row r="135" spans="3:3">
       <c r="C135" s="16"/>
     </row>
   </sheetData>
-  <sheetProtection password="CF7A" sheet="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="97M6TSPPDPi+FjPZiLy3JMvI5W0N9KJ8ghGITomDVeyEDAPbJ0CZQPnap0mQBr0qhZVPYROUaBQyscokyZcQVQ==" saltValue="hOw94LP2fQxpn5SrHmj/wg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="24">
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="E2:H2"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source_tree\IMS_REPORTS\build\web\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -348,9 +348,6 @@
     <t>Nguồn vốn nhận ủy thác của các chủ đầu tư khác</t>
   </si>
   <si>
-    <t>Biểu số 02/NHCS-KH</t>
-  </si>
-  <si>
     <t>- Cho vay dự án CWPD</t>
   </si>
   <si>
@@ -360,9 +357,6 @@
     <t>(PGD lập gửi tỉnh, tỉnh tổng hợp gửi HSC)</t>
   </si>
   <si>
-    <t>Tăng, giảm so với 31/12/2022</t>
-  </si>
-  <si>
     <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm từ nguồn vốn NHCSXH huy động (NĐ số 61/2015/NĐ-CP; NĐ 74/2019/NĐ-CP)</t>
   </si>
   <si>
@@ -379,18 +373,6 @@
   </si>
   <si>
     <t>Cho vay xây dựng cụm tuyến dân cư và nhà ở vùng ngập lũ ĐBSCL giai đoạn 2018-2020 (QĐ 714/QĐ-TTg)</t>
-  </si>
-  <si>
-    <t>KẾ HOẠCH TÍN DỤNG NĂM 2023</t>
-  </si>
-  <si>
-    <t>Kế hoạch tín dụng năm 2023</t>
-  </si>
-  <si>
-    <t>Thực hiện đến 31/12/2021</t>
-  </si>
-  <si>
-    <t>Ước thực hiện đến 31/12/2022</t>
   </si>
   <si>
     <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm theo Nghị quyết 11/NQ-CP</t>
@@ -818,6 +800,24 @@
   </si>
   <si>
     <t>Số hộ mới thoát nghèo (giai đoạn 2021-2023)</t>
+  </si>
+  <si>
+    <t>KẾ HOẠCH TÍN DỤNG NĂM 2024</t>
+  </si>
+  <si>
+    <t>Thực hiện đến 31/12/2022</t>
+  </si>
+  <si>
+    <t>Ước thực hiện đến 31/12/2023</t>
+  </si>
+  <si>
+    <t>Kế hoạch tín dụng năm 2024</t>
+  </si>
+  <si>
+    <t>Tăng, giảm so với 31/12/2023</t>
+  </si>
+  <si>
+    <t>Biểu số 02A/NHCS-KH</t>
   </si>
 </sst>
 </file>
@@ -2256,7 +2256,7 @@
       <c r="B1" s="2"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6" t="s">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="H1" s="6"/>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B2" s="8"/>
       <c r="E2" s="105" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F2" s="105"/>
       <c r="G2" s="105"/>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="5" spans="1:52" ht="21.9" customHeight="1">
       <c r="A5" s="108" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="B5" s="108"/>
       <c r="C5" s="108"/>
@@ -2326,13 +2326,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="110" t="s">
-        <v>98</v>
+        <v>213</v>
       </c>
       <c r="E7" s="110" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>97</v>
+        <v>215</v>
       </c>
       <c r="G7" s="111"/>
       <c r="H7" s="111"/>
@@ -2347,7 +2347,7 @@
         <v>26</v>
       </c>
       <c r="G8" s="115" t="s">
-        <v>89</v>
+        <v>216</v>
       </c>
       <c r="H8" s="116"/>
     </row>
@@ -2404,7 +2404,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>10</v>
@@ -2479,7 +2479,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="62" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>24</v>
@@ -2554,7 +2554,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C14" s="27" t="s">
         <v>25</v>
@@ -2629,7 +2629,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>17</v>
@@ -2704,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C16" s="27" t="s">
         <v>81</v>
@@ -2726,7 +2726,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>82</v>
@@ -2748,7 +2748,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C18" s="64" t="s">
         <v>47</v>
@@ -2770,7 +2770,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C19" s="65" t="s">
         <v>83</v>
@@ -2790,7 +2790,7 @@
     <row r="20" spans="1:52" ht="22.5" customHeight="1">
       <c r="A20" s="104"/>
       <c r="B20" s="26" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C20" s="66" t="s">
         <v>84</v>
@@ -2812,7 +2812,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>12</v>
@@ -2887,7 +2887,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>42</v>
@@ -2959,28 +2959,28 @@
     </row>
     <row r="23" spans="1:52" s="15" customFormat="1" ht="31.5" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D23" s="29">
-        <f>SUM(D24:D52)+D60-D46-D31</f>
+        <f>SUM(D24:D52)+D60-D46-D31-D47</f>
         <v>0</v>
       </c>
       <c r="E23" s="29">
-        <f>SUM(E24:E52)+E60-E46-E31</f>
+        <f t="shared" ref="E23:G23" si="1">SUM(E24:E52)+E60-E46-E31-E47</f>
         <v>0</v>
       </c>
       <c r="F23" s="29">
-        <f>SUM(F24:F52)+F60-F46-F31</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G23" s="29">
-        <f>SUM(G24:G52)+G60-G46-G31</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H23" s="49">
@@ -3037,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>72</v>
@@ -3046,7 +3046,7 @@
       <c r="E24" s="88"/>
       <c r="F24" s="88"/>
       <c r="G24" s="58">
-        <f t="shared" ref="G24:G50" si="1">F24-E24</f>
+        <f t="shared" ref="G24:G50" si="2">F24-E24</f>
         <v>0</v>
       </c>
       <c r="H24" s="55">
@@ -3059,7 +3059,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C25" s="67" t="s">
         <v>73</v>
@@ -3068,7 +3068,7 @@
       <c r="E25" s="93"/>
       <c r="F25" s="93"/>
       <c r="G25" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H25" s="55">
@@ -3081,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C26" s="68" t="s">
         <v>74</v>
@@ -3090,7 +3090,7 @@
       <c r="E26" s="93"/>
       <c r="F26" s="93"/>
       <c r="G26" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H26" s="55">
@@ -3103,7 +3103,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C27" s="68" t="s">
         <v>75</v>
@@ -3112,7 +3112,7 @@
       <c r="E27" s="88"/>
       <c r="F27" s="88"/>
       <c r="G27" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H27" s="55">
@@ -3125,16 +3125,16 @@
         <v>5</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C28" s="69" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D28" s="88"/>
       <c r="E28" s="88"/>
       <c r="F28" s="88"/>
       <c r="G28" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H28" s="55">
@@ -3147,16 +3147,16 @@
         <v>6</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C29" s="69" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D29" s="88"/>
       <c r="E29" s="88"/>
       <c r="F29" s="88"/>
       <c r="G29" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H29" s="55">
@@ -3169,7 +3169,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C30" s="68" t="s">
         <v>78</v>
@@ -3178,7 +3178,7 @@
       <c r="E30" s="88"/>
       <c r="F30" s="88"/>
       <c r="G30" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H30" s="55">
@@ -3191,7 +3191,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C31" s="71" t="s">
         <v>61</v>
@@ -3200,7 +3200,7 @@
       <c r="E31" s="88"/>
       <c r="F31" s="88"/>
       <c r="G31" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H31" s="55">
@@ -3213,7 +3213,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C32" s="68" t="s">
         <v>76</v>
@@ -3222,7 +3222,7 @@
       <c r="E32" s="88"/>
       <c r="F32" s="88"/>
       <c r="G32" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H32" s="55">
@@ -3279,7 +3279,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C33" s="68" t="s">
         <v>60</v>
@@ -3288,7 +3288,7 @@
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
       <c r="G33" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H33" s="55">
@@ -3301,7 +3301,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C34" s="68" t="s">
         <v>62</v>
@@ -3310,7 +3310,7 @@
       <c r="E34" s="88"/>
       <c r="F34" s="88"/>
       <c r="G34" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H34" s="55">
@@ -3323,7 +3323,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C35" s="68" t="s">
         <v>6</v>
@@ -3332,7 +3332,7 @@
       <c r="E35" s="88"/>
       <c r="F35" s="88"/>
       <c r="G35" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H35" s="55">
@@ -3389,16 +3389,16 @@
         <v>12</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D36" s="88"/>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
       <c r="G36" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H36" s="55">
@@ -3455,7 +3455,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C37" s="68" t="s">
         <v>66</v>
@@ -3464,7 +3464,7 @@
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
       <c r="G37" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H37" s="55">
@@ -3521,7 +3521,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C38" s="68" t="s">
         <v>67</v>
@@ -3530,7 +3530,7 @@
       <c r="E38" s="88"/>
       <c r="F38" s="88"/>
       <c r="G38" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H38" s="55">
@@ -3587,7 +3587,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C39" s="18" t="s">
         <v>65</v>
@@ -3596,7 +3596,7 @@
       <c r="E39" s="88"/>
       <c r="F39" s="88"/>
       <c r="G39" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H39" s="55">
@@ -3653,7 +3653,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C40" s="68" t="s">
         <v>71</v>
@@ -3662,7 +3662,7 @@
       <c r="E40" s="88"/>
       <c r="F40" s="88"/>
       <c r="G40" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H40" s="55">
@@ -3719,7 +3719,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C41" s="68" t="s">
         <v>70</v>
@@ -3728,7 +3728,7 @@
       <c r="E41" s="88"/>
       <c r="F41" s="88"/>
       <c r="G41" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H41" s="55">
@@ -3785,7 +3785,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C42" s="68" t="s">
         <v>22</v>
@@ -3794,7 +3794,7 @@
       <c r="E42" s="88"/>
       <c r="F42" s="88"/>
       <c r="G42" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H42" s="55">
@@ -3807,16 +3807,16 @@
         <v>19</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C43" s="68" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D43" s="88"/>
       <c r="E43" s="88"/>
       <c r="F43" s="88"/>
       <c r="G43" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H43" s="55">
@@ -3873,7 +3873,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C44" s="72" t="s">
         <v>59</v>
@@ -3882,7 +3882,7 @@
       <c r="E44" s="88"/>
       <c r="F44" s="88"/>
       <c r="G44" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H44" s="55">
@@ -3939,16 +3939,16 @@
         <v>21</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C45" s="68" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D45" s="88"/>
       <c r="E45" s="88"/>
       <c r="F45" s="88"/>
       <c r="G45" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H45" s="55">
@@ -3959,16 +3959,16 @@
     <row r="46" spans="1:52" ht="22.5" customHeight="1">
       <c r="A46" s="17"/>
       <c r="B46" s="17" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C46" s="73" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D46" s="88"/>
       <c r="E46" s="88"/>
       <c r="F46" s="88"/>
       <c r="G46" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H46" s="55">
@@ -3980,7 +3980,7 @@
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="98" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D47" s="88"/>
       <c r="E47" s="88"/>
@@ -3990,19 +3990,19 @@
     </row>
     <row r="48" spans="1:52" s="11" customFormat="1" ht="32.25" customHeight="1">
       <c r="A48" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C48" s="69" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D48" s="88"/>
       <c r="E48" s="88"/>
       <c r="F48" s="88"/>
       <c r="G48" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H48" s="55">
@@ -4056,10 +4056,10 @@
     </row>
     <row r="49" spans="1:52" s="11" customFormat="1" ht="27.75" customHeight="1">
       <c r="A49" s="17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C49" s="72" t="s">
         <v>79</v>
@@ -4068,7 +4068,7 @@
       <c r="E49" s="88"/>
       <c r="F49" s="88"/>
       <c r="G49" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H49" s="55">
@@ -4122,10 +4122,10 @@
     </row>
     <row r="50" spans="1:52" s="11" customFormat="1" ht="31.2">
       <c r="A50" s="17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C50" s="72" t="s">
         <v>77</v>
@@ -4134,7 +4134,7 @@
       <c r="E50" s="88"/>
       <c r="F50" s="88"/>
       <c r="G50" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H50" s="55">
@@ -4187,10 +4187,12 @@
       <c r="AZ50" s="2"/>
     </row>
     <row r="51" spans="1:52" s="11" customFormat="1" ht="31.2">
-      <c r="A51" s="17"/>
+      <c r="A51" s="17">
+        <v>25</v>
+      </c>
       <c r="B51" s="17"/>
       <c r="C51" s="102" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D51" s="88"/>
       <c r="E51" s="88"/>
@@ -4247,7 +4249,7 @@
         <v>26</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C52" s="18" t="s">
         <v>58</v>
@@ -4322,7 +4324,7 @@
         <v>4</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C53" s="75" t="s">
         <v>13</v>
@@ -4331,7 +4333,7 @@
       <c r="E53" s="93"/>
       <c r="F53" s="93"/>
       <c r="G53" s="58">
-        <f t="shared" ref="G53:G60" si="2">F53-E53</f>
+        <f t="shared" ref="G53:G60" si="3">F53-E53</f>
         <v>0</v>
       </c>
       <c r="H53" s="55">
@@ -4342,7 +4344,7 @@
     <row r="54" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="76"/>
       <c r="B54" s="17" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C54" s="75" t="s">
         <v>14</v>
@@ -4351,7 +4353,7 @@
       <c r="E54" s="93"/>
       <c r="F54" s="93"/>
       <c r="G54" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H54" s="55">
@@ -4362,7 +4364,7 @@
     <row r="55" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="76"/>
       <c r="B55" s="17" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C55" s="73" t="s">
         <v>56</v>
@@ -4371,7 +4373,7 @@
       <c r="E55" s="93"/>
       <c r="F55" s="93"/>
       <c r="G55" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H55" s="55">
@@ -4382,7 +4384,7 @@
     <row r="56" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A56" s="76"/>
       <c r="B56" s="17" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C56" s="73" t="s">
         <v>57</v>
@@ -4391,7 +4393,7 @@
       <c r="E56" s="93"/>
       <c r="F56" s="93"/>
       <c r="G56" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H56" s="55">
@@ -4402,7 +4404,7 @@
     <row r="57" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A57" s="76"/>
       <c r="B57" s="17" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C57" s="75" t="s">
         <v>55</v>
@@ -4411,7 +4413,7 @@
       <c r="E57" s="93"/>
       <c r="F57" s="93"/>
       <c r="G57" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H57" s="55">
@@ -4422,7 +4424,7 @@
     <row r="58" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A58" s="76"/>
       <c r="B58" s="17" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C58" s="75" t="s">
         <v>63</v>
@@ -4431,7 +4433,7 @@
       <c r="E58" s="93"/>
       <c r="F58" s="93"/>
       <c r="G58" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H58" s="55">
@@ -4442,16 +4444,16 @@
     <row r="59" spans="1:52" s="4" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A59" s="77"/>
       <c r="B59" s="17" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C59" s="75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" s="88"/>
       <c r="E59" s="93"/>
       <c r="F59" s="93"/>
       <c r="G59" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H59" s="55">
@@ -4464,7 +4466,7 @@
         <v>27</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C60" s="18" t="s">
         <v>48</v>
@@ -4473,7 +4475,7 @@
       <c r="E60" s="93"/>
       <c r="F60" s="93"/>
       <c r="G60" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H60" s="55">
@@ -4483,13 +4485,13 @@
     </row>
     <row r="61" spans="1:52" s="23" customFormat="1" ht="25.5" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D61" s="22">
         <f>D62+D63+D64+D65+D66</f>
@@ -4561,16 +4563,16 @@
         <v>1</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C62" s="69" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D62" s="88"/>
       <c r="E62" s="93"/>
       <c r="F62" s="93"/>
       <c r="G62" s="58">
-        <f t="shared" ref="G62:G66" si="3">F62-E62</f>
+        <f t="shared" ref="G62:G66" si="4">F62-E62</f>
         <v>0</v>
       </c>
       <c r="H62" s="57">
@@ -4583,7 +4585,7 @@
         <v>2</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C63" s="18" t="s">
         <v>69</v>
@@ -4592,7 +4594,7 @@
       <c r="E63" s="93"/>
       <c r="F63" s="93"/>
       <c r="G63" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H63" s="57">
@@ -4605,16 +4607,16 @@
         <v>3</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C64" s="69" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D64" s="88"/>
       <c r="E64" s="93"/>
       <c r="F64" s="93"/>
       <c r="G64" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H64" s="57">
@@ -4627,16 +4629,16 @@
         <v>4</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C65" s="69" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D65" s="88"/>
       <c r="E65" s="93"/>
       <c r="F65" s="93"/>
       <c r="G65" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H65" s="57">
@@ -4649,16 +4651,16 @@
         <v>5</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C66" s="69" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D66" s="88"/>
       <c r="E66" s="93"/>
       <c r="F66" s="93"/>
       <c r="G66" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H66" s="57">
@@ -4671,7 +4673,7 @@
         <v>5</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>43</v>
@@ -4746,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>72</v>
@@ -4755,7 +4757,7 @@
       <c r="E68" s="88"/>
       <c r="F68" s="88"/>
       <c r="G68" s="58">
-        <f t="shared" ref="G68:G94" si="4">F68-E68</f>
+        <f t="shared" ref="G68:G94" si="5">F68-E68</f>
         <v>0</v>
       </c>
       <c r="H68" s="54">
@@ -4768,7 +4770,7 @@
         <v>2</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C69" s="67" t="s">
         <v>73</v>
@@ -4777,7 +4779,7 @@
       <c r="E69" s="88"/>
       <c r="F69" s="88"/>
       <c r="G69" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H69" s="54">
@@ -4790,7 +4792,7 @@
         <v>3</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C70" s="68" t="s">
         <v>74</v>
@@ -4799,7 +4801,7 @@
       <c r="E70" s="88"/>
       <c r="F70" s="88"/>
       <c r="G70" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H70" s="54">
@@ -4812,7 +4814,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C71" s="68" t="s">
         <v>75</v>
@@ -4821,7 +4823,7 @@
       <c r="E71" s="88"/>
       <c r="F71" s="88"/>
       <c r="G71" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H71" s="54">
@@ -4834,7 +4836,7 @@
         <v>5</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C72" s="18" t="s">
         <v>68</v>
@@ -4843,7 +4845,7 @@
       <c r="E72" s="88"/>
       <c r="F72" s="88"/>
       <c r="G72" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H72" s="54">
@@ -4856,16 +4858,16 @@
         <v>23</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C73" s="78" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D73" s="88"/>
       <c r="E73" s="88"/>
       <c r="F73" s="88"/>
       <c r="G73" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H73" s="54">
@@ -4878,7 +4880,7 @@
         <v>6</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C74" s="68" t="s">
         <v>78</v>
@@ -4887,7 +4889,7 @@
       <c r="E74" s="88"/>
       <c r="F74" s="88"/>
       <c r="G74" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H74" s="54">
@@ -4900,7 +4902,7 @@
         <v>23</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C75" s="71" t="s">
         <v>61</v>
@@ -4909,7 +4911,7 @@
       <c r="E75" s="88"/>
       <c r="F75" s="88"/>
       <c r="G75" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H75" s="54">
@@ -4922,7 +4924,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C76" s="68" t="s">
         <v>76</v>
@@ -4931,7 +4933,7 @@
       <c r="E76" s="88"/>
       <c r="F76" s="88"/>
       <c r="G76" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H76" s="54">
@@ -4944,7 +4946,7 @@
         <v>8</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C77" s="68" t="s">
         <v>60</v>
@@ -4953,7 +4955,7 @@
       <c r="E77" s="88"/>
       <c r="F77" s="88"/>
       <c r="G77" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H77" s="54">
@@ -4966,7 +4968,7 @@
         <v>9</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C78" s="68" t="s">
         <v>62</v>
@@ -4975,7 +4977,7 @@
       <c r="E78" s="88"/>
       <c r="F78" s="88"/>
       <c r="G78" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H78" s="54">
@@ -4988,7 +4990,7 @@
         <v>10</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C79" s="68" t="s">
         <v>6</v>
@@ -4997,7 +4999,7 @@
       <c r="E79" s="88"/>
       <c r="F79" s="88"/>
       <c r="G79" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H79" s="54">
@@ -5010,20 +5012,20 @@
         <v>11</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C80" s="68" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D80" s="88"/>
       <c r="E80" s="88"/>
       <c r="F80" s="88"/>
       <c r="G80" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H80" s="54">
-        <f t="shared" ref="H80:H94" si="5">IF(AND(F80=G80,F80&lt;&gt;0),1,IFERROR(G80/E80,0))</f>
+        <f t="shared" ref="H80:H94" si="6">IF(AND(F80=G80,F80&lt;&gt;0),1,IFERROR(G80/E80,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -5032,7 +5034,7 @@
         <v>12</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C81" s="68" t="s">
         <v>66</v>
@@ -5041,11 +5043,11 @@
       <c r="E81" s="88"/>
       <c r="F81" s="88"/>
       <c r="G81" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H81" s="54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5054,7 +5056,7 @@
         <v>13</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C82" s="68" t="s">
         <v>65</v>
@@ -5063,11 +5065,11 @@
       <c r="E82" s="88"/>
       <c r="F82" s="88"/>
       <c r="G82" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H82" s="54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5076,7 +5078,7 @@
         <v>14</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C83" s="68" t="s">
         <v>71</v>
@@ -5085,11 +5087,11 @@
       <c r="E83" s="88"/>
       <c r="F83" s="88"/>
       <c r="G83" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H83" s="54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5098,7 +5100,7 @@
         <v>15</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C84" s="68" t="s">
         <v>70</v>
@@ -5107,11 +5109,11 @@
       <c r="E84" s="88"/>
       <c r="F84" s="88"/>
       <c r="G84" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H84" s="54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5120,7 +5122,7 @@
         <v>16</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C85" s="18" t="s">
         <v>69</v>
@@ -5129,11 +5131,11 @@
       <c r="E85" s="88"/>
       <c r="F85" s="88"/>
       <c r="G85" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H85" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5142,60 +5144,60 @@
         <v>23</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C86" s="79" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D86" s="88"/>
       <c r="E86" s="88"/>
       <c r="F86" s="88"/>
       <c r="G86" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H86" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="21" customHeight="1">
       <c r="A87" s="17"/>
       <c r="B87" s="17" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C87" s="73" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D87" s="88"/>
       <c r="E87" s="88"/>
       <c r="F87" s="88"/>
       <c r="G87" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H87" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="21.75" customHeight="1">
       <c r="A88" s="17"/>
       <c r="B88" s="17" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C88" s="73" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D88" s="88"/>
       <c r="E88" s="88"/>
       <c r="F88" s="88"/>
       <c r="G88" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H88" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5204,20 +5206,20 @@
         <v>17</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C89" s="69" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D89" s="88"/>
       <c r="E89" s="88"/>
       <c r="F89" s="88"/>
       <c r="G89" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H89" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5226,20 +5228,20 @@
         <v>18</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C90" s="69" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D90" s="88"/>
       <c r="E90" s="88"/>
       <c r="F90" s="88"/>
       <c r="G90" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H90" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5248,20 +5250,20 @@
         <v>19</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C91" s="69" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D91" s="88"/>
       <c r="E91" s="88"/>
       <c r="F91" s="88"/>
       <c r="G91" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H91" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5270,7 +5272,7 @@
         <v>20</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C92" s="72" t="s">
         <v>77</v>
@@ -5279,11 +5281,11 @@
       <c r="E92" s="88"/>
       <c r="F92" s="88"/>
       <c r="G92" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H92" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5292,7 +5294,7 @@
         <v>21</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C93" s="18" t="s">
         <v>48</v>
@@ -5301,11 +5303,11 @@
       <c r="E93" s="88"/>
       <c r="F93" s="88"/>
       <c r="G93" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H93" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5314,7 +5316,7 @@
         <v>7</v>
       </c>
       <c r="B94" s="26" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C94" s="14" t="s">
         <v>15</v>
@@ -5323,11 +5325,11 @@
       <c r="E94" s="88"/>
       <c r="F94" s="88"/>
       <c r="G94" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H94" s="54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5336,7 +5338,7 @@
         <v>16</v>
       </c>
       <c r="B95" s="26" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>53</v>
@@ -5345,11 +5347,11 @@
       <c r="E95" s="88"/>
       <c r="F95" s="88"/>
       <c r="G95" s="41">
-        <f t="shared" ref="G95:G115" si="6">F95-E95</f>
+        <f t="shared" ref="G95:G115" si="7">F95-E95</f>
         <v>0</v>
       </c>
       <c r="H95" s="54">
-        <f t="shared" ref="H95:H115" si="7">IF(AND(F95=G95,F95&lt;&gt;0),1,IFERROR(G95/E95,0))</f>
+        <f t="shared" ref="H95:H115" si="8">IF(AND(F95=G95,F95&lt;&gt;0),1,IFERROR(G95/E95,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -5358,20 +5360,20 @@
         <v>1</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C96" s="100" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D96" s="88"/>
       <c r="E96" s="88"/>
       <c r="F96" s="88"/>
       <c r="G96" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H96" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5380,7 +5382,7 @@
         <v>27</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C97" s="73" t="s">
         <v>33</v>
@@ -5389,11 +5391,11 @@
       <c r="E97" s="93"/>
       <c r="F97" s="93"/>
       <c r="G97" s="43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H97" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5402,7 +5404,7 @@
         <v>27</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C98" s="73" t="s">
         <v>49</v>
@@ -5411,11 +5413,11 @@
       <c r="E98" s="93"/>
       <c r="F98" s="93"/>
       <c r="G98" s="43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H98" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5424,20 +5426,20 @@
         <v>2</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C99" s="101" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D99" s="88"/>
       <c r="E99" s="88"/>
       <c r="F99" s="88"/>
       <c r="G99" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H99" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5446,7 +5448,7 @@
         <v>27</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C100" s="73" t="s">
         <v>32</v>
@@ -5455,11 +5457,11 @@
       <c r="E100" s="88"/>
       <c r="F100" s="88"/>
       <c r="G100" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H100" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5468,7 +5470,7 @@
         <v>27</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C101" s="71" t="s">
         <v>50</v>
@@ -5477,11 +5479,11 @@
       <c r="E101" s="88"/>
       <c r="F101" s="88"/>
       <c r="G101" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H101" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5490,20 +5492,20 @@
         <v>3</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C102" s="99" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D102" s="88"/>
       <c r="E102" s="88"/>
       <c r="F102" s="88"/>
       <c r="G102" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H102" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5512,7 +5514,7 @@
         <v>4</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C103" s="18" t="s">
         <v>31</v>
@@ -5521,11 +5523,11 @@
       <c r="E103" s="88"/>
       <c r="F103" s="88"/>
       <c r="G103" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H103" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5534,7 +5536,7 @@
         <v>27</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C104" s="73" t="s">
         <v>30</v>
@@ -5543,11 +5545,11 @@
       <c r="E104" s="93"/>
       <c r="F104" s="93"/>
       <c r="G104" s="43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H104" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5556,7 +5558,7 @@
         <v>27</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C105" s="71" t="s">
         <v>51</v>
@@ -5565,11 +5567,11 @@
       <c r="E105" s="93"/>
       <c r="F105" s="93"/>
       <c r="G105" s="43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H105" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5578,7 +5580,7 @@
         <v>5</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C106" s="68" t="s">
         <v>29</v>
@@ -5587,11 +5589,11 @@
       <c r="E106" s="88"/>
       <c r="F106" s="88"/>
       <c r="G106" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H106" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5600,7 +5602,7 @@
         <v>6</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C107" s="18" t="s">
         <v>28</v>
@@ -5609,11 +5611,11 @@
       <c r="E107" s="93"/>
       <c r="F107" s="93"/>
       <c r="G107" s="43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H107" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5622,7 +5624,7 @@
         <v>27</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C108" s="73" t="s">
         <v>34</v>
@@ -5631,11 +5633,11 @@
       <c r="E108" s="88"/>
       <c r="F108" s="88"/>
       <c r="G108" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H108" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5644,7 +5646,7 @@
         <v>7</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C109" s="18" t="s">
         <v>36</v>
@@ -5653,18 +5655,18 @@
       <c r="E109" s="93"/>
       <c r="F109" s="93"/>
       <c r="G109" s="43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H109" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:8" s="3" customFormat="1" ht="27" customHeight="1">
       <c r="A110" s="81"/>
       <c r="B110" s="17" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C110" s="73" t="s">
         <v>35</v>
@@ -5673,18 +5675,18 @@
       <c r="E110" s="88"/>
       <c r="F110" s="88"/>
       <c r="G110" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H110" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:8" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A111" s="81"/>
       <c r="B111" s="17" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C111" s="18" t="s">
         <v>44</v>
@@ -5693,11 +5695,11 @@
       <c r="E111" s="88"/>
       <c r="F111" s="88"/>
       <c r="G111" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H111" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5706,7 +5708,7 @@
         <v>8</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C112" s="68" t="s">
         <v>80</v>
@@ -5715,11 +5717,11 @@
       <c r="E112" s="88"/>
       <c r="F112" s="88"/>
       <c r="G112" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H112" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5728,7 +5730,7 @@
         <v>9</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C113" s="68" t="s">
         <v>40</v>
@@ -5737,11 +5739,11 @@
       <c r="E113" s="88"/>
       <c r="F113" s="88"/>
       <c r="G113" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H113" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5750,7 +5752,7 @@
         <v>10</v>
       </c>
       <c r="B114" s="26" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C114" s="18" t="s">
         <v>52</v>
@@ -5759,11 +5761,11 @@
       <c r="E114" s="88"/>
       <c r="F114" s="88"/>
       <c r="G114" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H114" s="54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5772,7 +5774,7 @@
         <v>18</v>
       </c>
       <c r="B115" s="26" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C115" s="84" t="s">
         <v>64</v>
@@ -5781,11 +5783,11 @@
       <c r="E115" s="97"/>
       <c r="F115" s="97"/>
       <c r="G115" s="59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H115" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -5810,7 +5812,7 @@
       <c r="C118" s="10"/>
       <c r="D118" s="10"/>
       <c r="E118" s="105" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F118" s="105"/>
       <c r="G118" s="105"/>
@@ -5855,7 +5857,7 @@
     </row>
     <row r="122" spans="1:8" ht="321.75" customHeight="1">
       <c r="C122" s="122" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D122" s="122"/>
       <c r="E122" s="122"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source_tree\IMS_REPORTS\build\web\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\Cap nhat\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="221">
   <si>
     <t>CỘNG HOÀ XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -818,6 +818,15 @@
   </si>
   <si>
     <t>Biểu số 02A/NHCS-KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cho vay hộ gia đình SXKD tại VKK theo QĐ 31/2007/QĐ-TTg </t>
+  </si>
+  <si>
+    <t>XD000291</t>
+  </si>
+  <si>
+    <t>XD000251</t>
   </si>
 </sst>
 </file>
@@ -3046,7 +3055,7 @@
       <c r="E24" s="88"/>
       <c r="F24" s="88"/>
       <c r="G24" s="58">
-        <f t="shared" ref="G24:G50" si="2">F24-E24</f>
+        <f t="shared" ref="G24:G51" si="2">F24-E24</f>
         <v>0</v>
       </c>
       <c r="H24" s="55">
@@ -3978,15 +3987,23 @@
     </row>
     <row r="47" spans="1:52" ht="22.5" customHeight="1">
       <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
+      <c r="B47" s="17" t="s">
+        <v>220</v>
+      </c>
       <c r="C47" s="98" t="s">
         <v>98</v>
       </c>
       <c r="D47" s="88"/>
       <c r="E47" s="88"/>
       <c r="F47" s="88"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="55"/>
+      <c r="G47" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:52" s="11" customFormat="1" ht="32.25" customHeight="1">
       <c r="A48" s="17">
@@ -4190,15 +4207,23 @@
       <c r="A51" s="17">
         <v>25</v>
       </c>
-      <c r="B51" s="17"/>
+      <c r="B51" s="17" t="s">
+        <v>219</v>
+      </c>
       <c r="C51" s="102" t="s">
         <v>92</v>
       </c>
       <c r="D51" s="88"/>
       <c r="E51" s="88"/>
       <c r="F51" s="88"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="55"/>
+      <c r="G51" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -4971,7 +4996,7 @@
         <v>171</v>
       </c>
       <c r="C78" s="68" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
       <c r="D78" s="88"/>
       <c r="E78" s="88"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK02.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\update TTBC\2024_T7_KHNV\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSHOP\CV NAM 2024\TTBC\KHNV\Chỉnh sửa Kế hoạch tín dụng 2025\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52754B8C-C6C4-4DAF-AF11-671317229357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BIEU 02 -2023" sheetId="12" r:id="rId1"/>
@@ -18,12 +19,12 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'BIEU 02 -2023'!$A$1:$H$93</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BIEU 02 -2023'!$7:$11</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="168">
   <si>
     <t>CỘNG HOÀ XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -467,9 +468,6 @@
     <t>Cho vay các chương trình khác</t>
   </si>
   <si>
-    <t>NHU CẦU VAY VỐN TỪ NGUỒN VỐN ĐỊA PHƯƠNG</t>
-  </si>
-  <si>
     <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm (theo NĐ số 61/2015/NĐ-CP; NĐ 74/2019/NĐ-CP)</t>
   </si>
   <si>
@@ -618,13 +616,23 @@
   </si>
   <si>
     <t>Số hộ nghèo theo chuẩn hộ nghèo</t>
+  </si>
+  <si>
+    <t>DƯ NỢ NGUỒN VỐN ĐỊA PHƯƠNG</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="34">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0;\-#,##0;;@"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="36">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -827,12 +835,27 @@
       <family val="1"/>
     </font>
     <font>
+      <i/>
       <sz val="12"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-0.14999847407452621"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -965,6 +988,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor rgb="FFB7B7B7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1219,7 +1248,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1269,20 +1298,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="10" xfId="39" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="10" xfId="39" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1296,102 +1313,101 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="25" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="25" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="25" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="10" xfId="39" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="10" xfId="39" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="27" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="3" fontId="21" fillId="25" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="21" fillId="25" borderId="10" xfId="42" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="21" fillId="25" borderId="10" xfId="42" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="25" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="25" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1412,6 +1428,42 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="46">
@@ -1452,9 +1504,9 @@
     <cellStyle name="Linked Cell" xfId="35" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="36" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="37"/>
-    <cellStyle name="Normal 5" xfId="38"/>
-    <cellStyle name="Normal_1a. Mau bieu Ke hoach hoa  949 ngay 08-6-2004" xfId="39"/>
+    <cellStyle name="Normal 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 5" xfId="38" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal_1a. Mau bieu Ke hoach hoa  949 ngay 08-6-2004" xfId="39" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="Note" xfId="40" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="41" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Percent" xfId="42" builtinId="5"/>
@@ -1761,7 +1813,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1774,195 +1826,195 @@
     <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:52">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="55" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:52">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="56" t="s">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
     </row>
     <row r="4" spans="1:52">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="57" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
     </row>
     <row r="5" spans="1:52">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+    </row>
+    <row r="6" spans="1:52">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+    </row>
+    <row r="7" spans="1:52">
+      <c r="A7" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="61"/>
+      <c r="C7" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-    </row>
-    <row r="6" spans="1:52">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-    </row>
-    <row r="7" spans="1:52">
-      <c r="A7" s="48" t="s">
+      <c r="E7" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+    </row>
+    <row r="8" spans="1:52">
+      <c r="A8" s="59"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="65"/>
+    </row>
+    <row r="9" spans="1:52" ht="12.75">
+      <c r="A9" s="59"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" ht="8.25" customHeight="1">
+      <c r="A10" s="59"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="56"/>
+    </row>
+    <row r="11" spans="1:52" ht="18.75" customHeight="1">
+      <c r="A11" s="21">
         <v>1</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="48" t="s">
+      <c r="B11" s="21"/>
+      <c r="C11" s="21">
         <v>2</v>
       </c>
-      <c r="D7" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-    </row>
-    <row r="8" spans="1:52">
-      <c r="A8" s="48"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="H8" s="54"/>
-    </row>
-    <row r="9" spans="1:52" ht="12.75">
-      <c r="A9" s="48"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:52" ht="8.25" customHeight="1">
-      <c r="A10" s="48"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="44"/>
-    </row>
-    <row r="11" spans="1:52" ht="18.75" customHeight="1">
-      <c r="A11" s="25">
-        <v>1</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25">
-        <v>2</v>
-      </c>
-      <c r="D11" s="26">
+      <c r="D11" s="22">
         <v>3</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="22">
         <v>4</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="22">
         <v>5</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="22">
         <v>6</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="23">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:52" s="14" customFormat="1">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="29" t="s">
+      <c r="B12" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="33">
         <f>D19</f>
         <v>0</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="33">
         <f t="shared" ref="E12:F12" si="0">E19</f>
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="30">
-        <f>F12-E12</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="31" t="str">
-        <f>IF(E12=0, "", ROUND((G12/E12)*100, 2))</f>
+      <c r="G12" s="40" t="str">
+        <f>IF(OR(E12&lt;&gt;0,F12&lt;&gt;0),F12-E12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="41" t="str">
+        <f>IF(OR(ISBLANK(G12), G12="",AND(E12=0,G12=0)), "", IF(AND(E12=0, G12&gt;0), 100, IF(AND(E12&gt;0, G12=0), 0, ROUND((G12/E12)*100, 3))))</f>
         <v/>
       </c>
       <c r="I12" s="1"/>
@@ -2011,33 +2063,33 @@
       <c r="AZ12" s="1"/>
     </row>
     <row r="13" spans="1:52" s="14" customFormat="1">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="29" t="s">
+      <c r="B13" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="33">
         <f>D12-D18</f>
         <v>0</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="33">
         <f t="shared" ref="E13:F13" si="1">E12-E18</f>
         <v>0</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="30">
-        <f t="shared" ref="G13:G76" si="2">F13-E13</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="31" t="str">
-        <f t="shared" ref="H13:H76" si="3">IF(E13=0, "", ROUND((G13/E13)*100, 2))</f>
+      <c r="G13" s="40" t="str">
+        <f t="shared" ref="G13:G76" si="2">IF(OR(E13&lt;&gt;0,F13&lt;&gt;0),F13-E13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="41" t="str">
+        <f t="shared" ref="H13:H76" si="3">IF(OR(ISBLANK(G13), G13="",AND(E13=0,G13=0)), "", IF(AND(E13=0, G13&gt;0), 100, IF(AND(E13&gt;0, G13=0), 0, ROUND((G13/E13)*100, 3))))</f>
         <v/>
       </c>
       <c r="I13" s="1"/>
@@ -2086,13 +2138,13 @@
       <c r="AZ13" s="1"/>
     </row>
     <row r="14" spans="1:52" s="11" customFormat="1">
-      <c r="A14" s="27">
+      <c r="A14" s="23">
         <v>1</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="33" t="s">
+      <c r="B14" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="27" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="34">
@@ -2107,11 +2159,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G14" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="31" t="str">
+      <c r="G14" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H14" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2161,13 +2213,13 @@
       <c r="AZ14" s="3"/>
     </row>
     <row r="15" spans="1:52" s="11" customFormat="1">
-      <c r="A15" s="27">
+      <c r="A15" s="23">
         <v>2</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="C15" s="33" t="s">
+      <c r="B15" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="34">
@@ -2182,11 +2234,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G15" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="31" t="str">
+      <c r="G15" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H15" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2236,151 +2288,151 @@
       <c r="AZ15" s="3"/>
     </row>
     <row r="16" spans="1:52" s="5" customFormat="1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H16" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:52" s="5" customFormat="1">
+      <c r="A17" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B17" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:52" s="5" customFormat="1">
-      <c r="A17" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" s="32" t="s">
+      <c r="C17" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H17" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:52">
+      <c r="A18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:52">
-      <c r="A18" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="36" t="s">
+      <c r="C18" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H18" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:52" s="17" customFormat="1">
+      <c r="A19" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:52" s="19" customFormat="1">
-      <c r="A19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="33">
         <f>D20+D50+D66</f>
         <v>0</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="33">
         <f t="shared" ref="E19:F19" si="6">E20+E50+E66</f>
         <v>0</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G19" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:52" s="19" customFormat="1">
-      <c r="A20" s="28" t="s">
+      <c r="G19" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H19" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:52" s="17" customFormat="1">
+      <c r="A20" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="29" t="s">
+      <c r="B20" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="33">
         <f>SUM(D21:D33)+SUM(D36:D43)+D49</f>
         <v>0</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="33">
         <f t="shared" ref="E20:F20" si="7">SUM(E21:E33)+SUM(E36:E43)+E49</f>
         <v>0</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="33">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G20" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="31" t="str">
+      <c r="G20" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H20" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:52" s="14" customFormat="1">
-      <c r="A21" s="27">
+      <c r="A21" s="23">
         <v>1</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="31" t="str">
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H21" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2430,23 +2482,23 @@
       <c r="AZ21" s="1"/>
     </row>
     <row r="22" spans="1:52" s="11" customFormat="1">
-      <c r="A22" s="27">
+      <c r="A22" s="23">
         <v>2</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="31" t="str">
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H22" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2496,23 +2548,23 @@
       <c r="AZ22" s="3"/>
     </row>
     <row r="23" spans="1:52" s="11" customFormat="1">
-      <c r="A23" s="27">
+      <c r="A23" s="23">
         <v>3</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="31" t="str">
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H23" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2561,200 +2613,200 @@
       <c r="AY23" s="3"/>
       <c r="AZ23" s="3"/>
     </row>
-    <row r="24" spans="1:52">
-      <c r="A24" s="27">
+    <row r="24" spans="1:52" ht="31.5">
+      <c r="A24" s="23">
         <v>4</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="31" t="str">
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H24" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:52" ht="31.5">
-      <c r="A25" s="27">
+      <c r="A25" s="23">
         <v>5</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="31" t="str">
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H25" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:52" ht="31.5">
-      <c r="A26" s="27">
+      <c r="A26" s="23">
         <v>6</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="31" t="str">
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H26" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:52" ht="31.5">
-      <c r="A27" s="27">
+      <c r="A27" s="23">
         <v>7</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="31" t="str">
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H27" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:52">
-      <c r="A28" s="27">
+      <c r="A28" s="23">
         <v>8</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="31" t="str">
+      <c r="C28" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H28" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:52">
-      <c r="A29" s="27">
+      <c r="A29" s="23">
         <v>9</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="31" t="str">
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H29" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:52">
-      <c r="A30" s="27">
+      <c r="A30" s="23">
         <v>10</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="31" t="str">
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H30" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:52">
-      <c r="A31" s="27">
+      <c r="A31" s="23">
         <v>11</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="31" t="str">
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H31" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:52" s="9" customFormat="1">
-      <c r="A32" s="27">
+      <c r="A32" s="23">
         <v>12</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="31" t="str">
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H32" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2804,72 +2856,72 @@
       <c r="AZ32" s="2"/>
     </row>
     <row r="33" spans="1:52">
-      <c r="A33" s="27">
+      <c r="A33" s="23">
         <v>13</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="43">
-        <f>D34+D35</f>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H33" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:52" ht="16.5" customHeight="1">
+      <c r="A34" s="48"/>
+      <c r="B34" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H34" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:52" s="9" customFormat="1">
+      <c r="A35" s="49"/>
+      <c r="B35" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="67">
+        <f>D33-D34</f>
         <v>0</v>
       </c>
-      <c r="E33" s="43">
-        <f t="shared" ref="E33:F33" si="8">E34+E35</f>
+      <c r="E35" s="67">
+        <f>E33-E34</f>
         <v>0</v>
       </c>
-      <c r="F33" s="43">
-        <f t="shared" si="8"/>
+      <c r="F35" s="67">
+        <f>F33-F34</f>
         <v>0</v>
       </c>
-      <c r="G33" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:52" ht="16.5" customHeight="1">
-      <c r="A34" s="47"/>
-      <c r="B34" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:52" s="9" customFormat="1">
-      <c r="A35" s="47"/>
-      <c r="B35" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="31" t="str">
+      <c r="G35" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H35" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2919,23 +2971,23 @@
       <c r="AZ35" s="2"/>
     </row>
     <row r="36" spans="1:52" s="9" customFormat="1" ht="31.5">
-      <c r="A36" s="27">
+      <c r="A36" s="23">
         <v>14</v>
       </c>
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="33" t="s">
+      <c r="C36" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="31" t="str">
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H36" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2985,23 +3037,23 @@
       <c r="AZ36" s="2"/>
     </row>
     <row r="37" spans="1:52" s="9" customFormat="1" ht="31.5">
-      <c r="A37" s="27">
+      <c r="A37" s="23">
         <v>15</v>
       </c>
-      <c r="B37" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="33" t="s">
+      <c r="B37" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="31" t="str">
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H37" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3051,23 +3103,23 @@
       <c r="AZ37" s="2"/>
     </row>
     <row r="38" spans="1:52" s="9" customFormat="1" ht="31.5">
-      <c r="A38" s="27">
+      <c r="A38" s="23">
         <v>16</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="31" t="str">
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H38" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3117,23 +3169,23 @@
       <c r="AZ38" s="2"/>
     </row>
     <row r="39" spans="1:52" s="9" customFormat="1" ht="31.5">
-      <c r="A39" s="27">
+      <c r="A39" s="23">
         <v>17</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C39" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="31" t="str">
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H39" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3183,23 +3235,23 @@
       <c r="AZ39" s="2"/>
     </row>
     <row r="40" spans="1:52" s="9" customFormat="1" ht="47.25">
-      <c r="A40" s="27">
+      <c r="A40" s="23">
         <v>18</v>
       </c>
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="33" t="s">
+      <c r="C40" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="31" t="str">
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H40" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3249,23 +3301,23 @@
       <c r="AZ40" s="2"/>
     </row>
     <row r="41" spans="1:52" s="9" customFormat="1">
-      <c r="A41" s="27">
+      <c r="A41" s="23">
         <v>19</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="31" t="str">
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H41" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3315,54 +3367,45 @@
       <c r="AZ41" s="2"/>
     </row>
     <row r="42" spans="1:52" ht="31.5">
-      <c r="A42" s="27">
+      <c r="A42" s="23">
         <v>20</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="33" t="s">
+      <c r="C42" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="31" t="str">
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H42" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="1:52" s="9" customFormat="1">
-      <c r="A43" s="27">
+      <c r="A43" s="23">
         <v>21</v>
       </c>
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C43" s="33" t="s">
+      <c r="C43" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="D43" s="24">
-        <f>SUM(D44:D48)</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="24">
-        <f t="shared" ref="E43:F43" si="9">SUM(E44:E48)</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="24">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="31" t="str">
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H43" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3412,21 +3455,23 @@
       <c r="AZ43" s="2"/>
     </row>
     <row r="44" spans="1:52" s="9" customFormat="1">
-      <c r="A44" s="38"/>
-      <c r="B44" s="32" t="s">
+      <c r="A44" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="37" t="s">
+      <c r="C44" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="31" t="str">
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H44" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3476,81 +3521,89 @@
       <c r="AZ44" s="2"/>
     </row>
     <row r="45" spans="1:52">
-      <c r="A45" s="38"/>
-      <c r="B45" s="32" t="s">
+      <c r="A45" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="37" t="s">
+      <c r="C45" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="31" t="str">
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H45" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:52">
-      <c r="A46" s="38"/>
-      <c r="B46" s="32" t="s">
+      <c r="A46" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="37" t="s">
+      <c r="C46" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="31" t="str">
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H46" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="1:52">
-      <c r="A47" s="38"/>
-      <c r="B47" s="32" t="s">
+      <c r="A47" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="37" t="s">
+      <c r="C47" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H47" s="31" t="str">
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H47" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:52" s="9" customFormat="1">
-      <c r="A48" s="38"/>
-      <c r="B48" s="32" t="s">
+      <c r="A48" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="37" t="s">
+      <c r="C48" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="31" t="str">
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H48" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3600,23 +3653,23 @@
       <c r="AZ48" s="2"/>
     </row>
     <row r="49" spans="1:52" s="9" customFormat="1">
-      <c r="A49" s="27">
+      <c r="A49" s="23">
         <v>22</v>
       </c>
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C49" s="33" t="s">
+      <c r="C49" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="31" t="str">
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H49" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3666,32 +3719,32 @@
       <c r="AZ49" s="2"/>
     </row>
     <row r="50" spans="1:52" s="9" customFormat="1">
-      <c r="A50" s="28" t="s">
+      <c r="A50" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="36" t="s">
+      <c r="B50" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="C50" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D50" s="24">
+      <c r="C50" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" s="34">
         <f>SUM(D51:D61)+D64+D65</f>
         <v>0</v>
       </c>
-      <c r="E50" s="24">
-        <f t="shared" ref="E50:F50" si="10">SUM(E51:E61)+E64+E65</f>
+      <c r="E50" s="34">
+        <f t="shared" ref="E50:F50" si="8">SUM(E51:E61)+E64+E65</f>
         <v>0</v>
       </c>
-      <c r="F50" s="24">
-        <f t="shared" si="10"/>
+      <c r="F50" s="34">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G50" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="31" t="str">
+      <c r="G50" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H50" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3741,23 +3794,23 @@
       <c r="AZ50" s="2"/>
     </row>
     <row r="51" spans="1:52" s="9" customFormat="1">
-      <c r="A51" s="27">
+      <c r="A51" s="23">
         <v>1</v>
       </c>
-      <c r="B51" s="32" t="s">
+      <c r="B51" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="33" t="s">
+      <c r="C51" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="31" t="str">
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H51" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3807,23 +3860,23 @@
       <c r="AZ51" s="2"/>
     </row>
     <row r="52" spans="1:52" s="12" customFormat="1">
-      <c r="A52" s="27">
+      <c r="A52" s="23">
         <v>2</v>
       </c>
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="33" t="s">
+      <c r="C52" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="31" t="str">
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H52" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3873,208 +3926,199 @@
       <c r="AZ52" s="2"/>
     </row>
     <row r="53" spans="1:52" s="4" customFormat="1">
-      <c r="A53" s="27">
+      <c r="A53" s="23">
         <v>3</v>
       </c>
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="37"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H53" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:52" s="4" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A54" s="23">
+        <v>4</v>
+      </c>
+      <c r="B54" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C53" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:52" s="4" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A54" s="27">
-        <v>4</v>
-      </c>
-      <c r="B54" s="32" t="s">
+      <c r="C54" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="37"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H54" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:52" s="4" customFormat="1" ht="31.5">
+      <c r="A55" s="23">
+        <v>5</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H55" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:52" s="4" customFormat="1" ht="31.5">
+      <c r="A56" s="23">
+        <v>6</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H56" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:52" s="4" customFormat="1">
+      <c r="A57" s="23">
+        <v>7</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H57" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:52" s="4" customFormat="1">
+      <c r="A58" s="23">
+        <v>8</v>
+      </c>
+      <c r="B58" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="C54" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:52" s="4" customFormat="1" ht="31.5">
-      <c r="A55" s="27">
-        <v>5</v>
-      </c>
-      <c r="B55" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:52" s="4" customFormat="1" ht="31.5">
-      <c r="A56" s="27">
-        <v>6</v>
-      </c>
-      <c r="B56" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:52" s="4" customFormat="1">
-      <c r="A57" s="27">
-        <v>7</v>
-      </c>
-      <c r="B57" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:52" s="4" customFormat="1">
-      <c r="A58" s="27">
-        <v>8</v>
-      </c>
-      <c r="B58" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="C58" s="33" t="s">
+      <c r="C58" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="31" t="str">
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H58" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="59" spans="1:52" s="4" customFormat="1">
-      <c r="A59" s="27">
+      <c r="A59" s="23">
         <v>9</v>
       </c>
-      <c r="B59" s="32" t="s">
+      <c r="B59" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="33" t="s">
+      <c r="C59" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="31" t="str">
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H59" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="60" spans="1:52" s="4" customFormat="1">
-      <c r="A60" s="27">
+      <c r="A60" s="23">
         <v>10</v>
       </c>
-      <c r="B60" s="32" t="s">
+      <c r="B60" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C60" s="33" t="s">
+      <c r="C60" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H60" s="31" t="str">
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H60" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="61" spans="1:52" s="13" customFormat="1">
-      <c r="A61" s="27">
+      <c r="A61" s="45">
         <v>11</v>
       </c>
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C61" s="33" t="s">
+      <c r="C61" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="43">
-        <f>SUM(D62:D63)</f>
-        <v>0</v>
-      </c>
-      <c r="E61" s="43">
-        <f t="shared" ref="E61:F61" si="11">SUM(E62:E63)</f>
-        <v>0</v>
-      </c>
-      <c r="F61" s="43">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G61" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="31" t="str">
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H61" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4124,129 +4168,139 @@
       <c r="AZ61" s="4"/>
     </row>
     <row r="62" spans="1:52" s="4" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A62" s="47"/>
-      <c r="B62" s="32" t="s">
+      <c r="A62" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="B62" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="C62" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="34">
-        <f t="shared" si="2"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H62" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:52" s="4" customFormat="1">
+      <c r="A63" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D63" s="67">
+        <f>D61-D62</f>
         <v>0</v>
       </c>
-      <c r="H62" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:52" s="4" customFormat="1">
-      <c r="A63" s="47"/>
-      <c r="B63" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C63" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="34">
-        <f t="shared" si="2"/>
+      <c r="E63" s="67">
+        <f>E61-E62</f>
         <v>0</v>
       </c>
-      <c r="H63" s="31" t="str">
+      <c r="F63" s="67">
+        <f>F61-F62</f>
+        <v>0</v>
+      </c>
+      <c r="G63" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H63" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="1:52" s="4" customFormat="1" ht="31.5">
-      <c r="A64" s="27">
+      <c r="A64" s="23">
         <v>12</v>
       </c>
-      <c r="B64" s="32" t="s">
+      <c r="B64" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="C64" s="33" t="s">
+      <c r="C64" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="31" t="str">
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H64" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="65" spans="1:52" s="4" customFormat="1">
-      <c r="A65" s="27">
+      <c r="A65" s="23">
         <v>13</v>
       </c>
-      <c r="B65" s="32" t="s">
+      <c r="B65" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C65" s="33" t="s">
+      <c r="C65" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="31" t="str">
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H65" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="1:52" s="4" customFormat="1">
-      <c r="A66" s="28" t="s">
+      <c r="A66" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="36" t="s">
+      <c r="B66" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H66" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:52" s="11" customFormat="1">
+      <c r="A67" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:52" s="11" customFormat="1">
-      <c r="A67" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B67" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D67" s="39"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H67" s="31" t="str">
+      <c r="D67" s="50"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4296,410 +4350,420 @@
       <c r="AZ67" s="3"/>
     </row>
     <row r="68" spans="1:52" s="3" customFormat="1">
-      <c r="A68" s="27">
+      <c r="A68" s="23">
         <v>1</v>
       </c>
-      <c r="B68" s="32" t="s">
+      <c r="B68" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="C68" s="33" t="s">
+      <c r="C68" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H68" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:52" s="3" customFormat="1">
+      <c r="A69" s="23">
+        <v>2</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="D68" s="40"/>
-      <c r="E68" s="40"/>
-      <c r="F68" s="40"/>
-      <c r="G68" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H68" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:52" s="3" customFormat="1">
-      <c r="A69" s="27">
-        <v>2</v>
-      </c>
-      <c r="B69" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C69" s="33" t="s">
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H69" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:52" s="3" customFormat="1">
+      <c r="A70" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H69" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:52" s="3" customFormat="1">
-      <c r="A70" s="26"/>
-      <c r="B70" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C70" s="37" t="s">
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H70" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:52" s="3" customFormat="1">
+      <c r="A71" s="23">
+        <v>3</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H71" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:52" s="3" customFormat="1">
+      <c r="A72" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:52" s="3" customFormat="1">
-      <c r="A71" s="27">
-        <v>3</v>
-      </c>
-      <c r="B71" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="C71" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="D71" s="41"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H71" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:52" s="3" customFormat="1">
-      <c r="A72" s="26"/>
-      <c r="B72" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" s="37" t="s">
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H72" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:52" s="3" customFormat="1">
+      <c r="A73" s="23">
+        <v>4</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H73" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:52" s="3" customFormat="1">
+      <c r="A74" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
-      <c r="F72" s="40"/>
-      <c r="G72" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H72" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:52" s="3" customFormat="1">
-      <c r="A73" s="27">
-        <v>4</v>
-      </c>
-      <c r="B73" s="32" t="s">
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H74" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:52" s="3" customFormat="1">
+      <c r="A75" s="23">
+        <v>5</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H75" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:52" s="3" customFormat="1" ht="31.5">
+      <c r="A76" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="40" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H76" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:52" s="3" customFormat="1" ht="31.5">
+      <c r="A77" s="23">
+        <v>6</v>
+      </c>
+      <c r="B77" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:52" s="3" customFormat="1">
-      <c r="A74" s="26"/>
-      <c r="B74" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="D74" s="40"/>
-      <c r="E74" s="40"/>
-      <c r="F74" s="40"/>
-      <c r="G74" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:52" s="3" customFormat="1">
-      <c r="A75" s="27">
-        <v>5</v>
-      </c>
-      <c r="B75" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C75" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="D75" s="41"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:52" s="3" customFormat="1" ht="31.5">
-      <c r="A76" s="26"/>
-      <c r="B76" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" s="37" t="s">
+      <c r="C77" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D76" s="40"/>
-      <c r="E76" s="40"/>
-      <c r="F76" s="40"/>
-      <c r="G76" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:52" s="3" customFormat="1">
-      <c r="A77" s="27">
-        <v>6</v>
-      </c>
-      <c r="B77" s="32" t="s">
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="40" t="str">
+        <f t="shared" ref="G77:G86" si="9">IF(OR(E77&lt;&gt;0,F77&lt;&gt;0),F77-E77,"")</f>
+        <v/>
+      </c>
+      <c r="H77" s="41" t="str">
+        <f t="shared" ref="H77:H86" si="10">IF(OR(ISBLANK(G77), G77="",AND(E77=0,G77=0)), "", IF(AND(E77=0, G77&gt;0), 100, IF(AND(E77&gt;0, G77=0), 0, ROUND((G77/E77)*100, 3))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:52" s="3" customFormat="1">
+      <c r="A78" s="23">
+        <v>7</v>
+      </c>
+      <c r="B78" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C77" s="33" t="s">
+      <c r="C78" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D77" s="40"/>
-      <c r="E77" s="40"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="30">
-        <f t="shared" ref="G77:G86" si="12">F77-E77</f>
-        <v>0</v>
-      </c>
-      <c r="H77" s="31" t="str">
-        <f t="shared" ref="H77:H86" si="13">IF(E77=0, "", ROUND((G77/E77)*100, 2))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:52" s="3" customFormat="1">
-      <c r="A78" s="27">
-        <v>7</v>
-      </c>
-      <c r="B78" s="32" t="s">
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H78" s="41" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:52" s="3" customFormat="1">
+      <c r="A79" s="23">
+        <v>8</v>
+      </c>
+      <c r="B79" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="C78" s="33" t="s">
+      <c r="C79" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="D78" s="40"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
-      <c r="G78" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H78" s="31" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:52" s="3" customFormat="1">
-      <c r="A79" s="27">
-        <v>8</v>
-      </c>
-      <c r="B79" s="32" t="s">
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H79" s="41" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:52" s="3" customFormat="1">
+      <c r="A80" s="23">
+        <v>9</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H80" s="41" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:8" s="3" customFormat="1">
+      <c r="A81" s="23">
+        <v>10</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D81" s="37"/>
+      <c r="E81" s="37"/>
+      <c r="F81" s="37"/>
+      <c r="G81" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H81" s="41" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:8" s="3" customFormat="1" ht="31.5">
+      <c r="A82" s="23">
+        <v>11</v>
+      </c>
+      <c r="B82" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="C79" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="D79" s="40"/>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
-      <c r="G79" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="31" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:52" s="3" customFormat="1">
-      <c r="A80" s="27">
-        <v>9</v>
-      </c>
-      <c r="B80" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C80" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D80" s="40"/>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
-      <c r="G80" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="31" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:8" s="3" customFormat="1">
-      <c r="A81" s="27">
-        <v>10</v>
-      </c>
-      <c r="B81" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C81" s="33" t="s">
+      <c r="C82" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H82" s="41" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:8" s="3" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A83" s="23">
+        <v>12</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C83" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="D83" s="37"/>
+      <c r="E83" s="37"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H83" s="41" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:8" s="3" customFormat="1">
+      <c r="A84" s="23">
+        <v>13</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C84" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" s="39"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H84" s="41" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C85" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="D81" s="40"/>
-      <c r="E81" s="40"/>
-      <c r="F81" s="40"/>
-      <c r="G81" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="31" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A82" s="27">
-        <v>11</v>
-      </c>
-      <c r="B82" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="C82" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" s="40"/>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H82" s="31" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:8" s="3" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A83" s="27">
-        <v>12</v>
-      </c>
-      <c r="B83" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C83" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="D83" s="40"/>
-      <c r="E83" s="40"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H83" s="31" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:8" s="3" customFormat="1">
-      <c r="A84" s="27">
-        <v>13</v>
-      </c>
-      <c r="B84" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="C84" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="D84" s="41"/>
-      <c r="E84" s="41"/>
-      <c r="F84" s="41"/>
-      <c r="G84" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H84" s="31" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="26"/>
-      <c r="B85" s="32" t="s">
+      <c r="D85" s="37"/>
+      <c r="E85" s="37"/>
+      <c r="F85" s="37"/>
+      <c r="G85" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H85" s="41" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="31.5">
+      <c r="A86" s="23">
+        <v>14</v>
+      </c>
+      <c r="B86" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="C85" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="31" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="31.5">
-      <c r="A86" s="27">
-        <v>14</v>
-      </c>
-      <c r="B86" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="C86" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="D86" s="40"/>
-      <c r="E86" s="40"/>
-      <c r="F86" s="40"/>
-      <c r="G86" s="30">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H86" s="31" t="str">
-        <f t="shared" si="13"/>
+      <c r="C86" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="D86" s="37"/>
+      <c r="E86" s="37"/>
+      <c r="F86" s="37"/>
+      <c r="G86" s="40" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="H86" s="41" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4723,12 +4787,12 @@
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
-      <c r="E89" s="45" t="s">
+      <c r="E89" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="F89" s="45"/>
-      <c r="G89" s="45"/>
-      <c r="H89" s="45"/>
+      <c r="F89" s="57"/>
+      <c r="G89" s="57"/>
+      <c r="H89" s="57"/>
     </row>
     <row r="90" spans="1:8" ht="33" customHeight="1">
       <c r="A90" s="6"/>
@@ -4737,12 +4801,12 @@
         <v>19</v>
       </c>
       <c r="D90" s="6"/>
-      <c r="E90" s="46" t="s">
+      <c r="E90" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
+      <c r="F90" s="58"/>
+      <c r="G90" s="58"/>
+      <c r="H90" s="58"/>
     </row>
     <row r="91" spans="1:8" ht="37.5" customHeight="1">
       <c r="A91" s="7"/>
@@ -4751,12 +4815,12 @@
         <v>20</v>
       </c>
       <c r="D91" s="7"/>
-      <c r="E91" s="45" t="s">
+      <c r="E91" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="F91" s="45"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
+      <c r="F91" s="57"/>
+      <c r="G91" s="57"/>
+      <c r="H91" s="57"/>
     </row>
     <row r="92" spans="1:8" ht="34.5" customHeight="1">
       <c r="A92" s="2"/>
@@ -4768,299 +4832,292 @@
       <c r="G92" s="2"/>
     </row>
     <row r="93" spans="1:8" ht="15.75" customHeight="1">
-      <c r="C93" s="35" t="s">
+      <c r="C93" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D93" s="35"/>
-      <c r="E93" s="35"/>
-      <c r="F93" s="35"/>
-      <c r="G93" s="35"/>
-      <c r="H93" s="35"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
     </row>
     <row r="94" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
-      <c r="C94" s="35"/>
-      <c r="D94" s="35"/>
-      <c r="E94" s="35"/>
-      <c r="F94" s="35"/>
-      <c r="G94" s="35"/>
-      <c r="H94" s="35"/>
+      <c r="C94" s="28"/>
+      <c r="D94" s="28"/>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
     </row>
     <row r="95" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
-      <c r="C95" s="35"/>
-      <c r="D95" s="35"/>
-      <c r="E95" s="35"/>
-      <c r="F95" s="35"/>
-      <c r="G95" s="35"/>
-      <c r="H95" s="35"/>
+      <c r="C95" s="28"/>
+      <c r="D95" s="28"/>
+      <c r="E95" s="28"/>
+      <c r="F95" s="28"/>
+      <c r="G95" s="28"/>
+      <c r="H95" s="28"/>
     </row>
     <row r="96" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
-      <c r="C96" s="35"/>
-      <c r="D96" s="35"/>
-      <c r="E96" s="35"/>
-      <c r="F96" s="35"/>
-      <c r="G96" s="35"/>
-      <c r="H96" s="35"/>
+      <c r="C96" s="28"/>
+      <c r="D96" s="28"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="28"/>
+      <c r="G96" s="28"/>
+      <c r="H96" s="28"/>
     </row>
     <row r="97" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
-      <c r="C97" s="35"/>
-      <c r="D97" s="35"/>
-      <c r="E97" s="35"/>
-      <c r="F97" s="35"/>
-      <c r="G97" s="35"/>
-      <c r="H97" s="35"/>
+      <c r="C97" s="28"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
     </row>
     <row r="98" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
-      <c r="C98" s="35"/>
-      <c r="D98" s="35"/>
-      <c r="E98" s="35"/>
-      <c r="F98" s="35"/>
-      <c r="G98" s="35"/>
-      <c r="H98" s="35"/>
+      <c r="C98" s="28"/>
+      <c r="D98" s="28"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
     </row>
     <row r="99" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
-      <c r="C99" s="35"/>
-      <c r="D99" s="35"/>
-      <c r="E99" s="35"/>
-      <c r="F99" s="35"/>
-      <c r="G99" s="35"/>
-      <c r="H99" s="35"/>
+      <c r="C99" s="28"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="28"/>
+      <c r="H99" s="28"/>
     </row>
     <row r="100" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
-      <c r="C100" s="35"/>
-      <c r="D100" s="35"/>
-      <c r="E100" s="35"/>
-      <c r="F100" s="35"/>
-      <c r="G100" s="35"/>
-      <c r="H100" s="35"/>
+      <c r="C100" s="28"/>
+      <c r="D100" s="28"/>
+      <c r="E100" s="28"/>
+      <c r="F100" s="28"/>
+      <c r="G100" s="28"/>
+      <c r="H100" s="28"/>
     </row>
     <row r="101" spans="1:8" s="3" customFormat="1" ht="24" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
-      <c r="C101" s="35"/>
-      <c r="D101" s="35"/>
-      <c r="E101" s="35"/>
-      <c r="F101" s="35"/>
-      <c r="G101" s="35"/>
-      <c r="H101" s="35"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
     </row>
     <row r="102" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
-      <c r="C102" s="35"/>
-      <c r="D102" s="35"/>
-      <c r="E102" s="35"/>
-      <c r="F102" s="35"/>
-      <c r="G102" s="35"/>
-      <c r="H102" s="35"/>
+      <c r="C102" s="28"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="28"/>
     </row>
     <row r="103" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
-      <c r="C103" s="35"/>
-      <c r="D103" s="35"/>
-      <c r="E103" s="35"/>
-      <c r="F103" s="35"/>
-      <c r="G103" s="35"/>
-      <c r="H103" s="35"/>
+      <c r="C103" s="28"/>
+      <c r="D103" s="28"/>
+      <c r="E103" s="28"/>
+      <c r="F103" s="28"/>
+      <c r="G103" s="28"/>
+      <c r="H103" s="28"/>
     </row>
     <row r="104" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="35"/>
-      <c r="E104" s="35"/>
-      <c r="F104" s="35"/>
-      <c r="G104" s="35"/>
-      <c r="H104" s="35"/>
+      <c r="C104" s="28"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="28"/>
+      <c r="F104" s="28"/>
+      <c r="G104" s="28"/>
+      <c r="H104" s="28"/>
     </row>
     <row r="105" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
-      <c r="C105" s="35"/>
-      <c r="D105" s="35"/>
-      <c r="E105" s="35"/>
-      <c r="F105" s="35"/>
-      <c r="G105" s="35"/>
-      <c r="H105" s="35"/>
+      <c r="C105" s="28"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="28"/>
+      <c r="F105" s="28"/>
+      <c r="G105" s="28"/>
+      <c r="H105" s="28"/>
     </row>
     <row r="106" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
-      <c r="C106" s="35"/>
-      <c r="D106" s="35"/>
-      <c r="E106" s="35"/>
-      <c r="F106" s="35"/>
-      <c r="G106" s="35"/>
-      <c r="H106" s="35"/>
+      <c r="C106" s="28"/>
+      <c r="D106" s="28"/>
+      <c r="E106" s="28"/>
+      <c r="F106" s="28"/>
+      <c r="G106" s="28"/>
+      <c r="H106" s="28"/>
     </row>
     <row r="107" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
-      <c r="C107" s="35"/>
-      <c r="D107" s="35"/>
-      <c r="E107" s="35"/>
-      <c r="F107" s="35"/>
-      <c r="G107" s="35"/>
-      <c r="H107" s="35"/>
+      <c r="C107" s="28"/>
+      <c r="D107" s="28"/>
+      <c r="E107" s="28"/>
+      <c r="F107" s="28"/>
+      <c r="G107" s="28"/>
+      <c r="H107" s="28"/>
     </row>
     <row r="108" spans="1:8" s="3" customFormat="1" ht="19.5" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
-      <c r="C108" s="35"/>
-      <c r="D108" s="35"/>
-      <c r="E108" s="35"/>
-      <c r="F108" s="35"/>
-      <c r="G108" s="35"/>
-      <c r="H108" s="35"/>
+      <c r="C108" s="28"/>
+      <c r="D108" s="28"/>
+      <c r="E108" s="28"/>
+      <c r="F108" s="28"/>
+      <c r="G108" s="28"/>
+      <c r="H108" s="28"/>
     </row>
     <row r="109" spans="1:8" s="3" customFormat="1" ht="23.25" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
-      <c r="C109" s="35"/>
-      <c r="D109" s="35"/>
-      <c r="E109" s="35"/>
-      <c r="F109" s="35"/>
-      <c r="G109" s="35"/>
-      <c r="H109" s="35"/>
+      <c r="C109" s="28"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="28"/>
+      <c r="F109" s="28"/>
+      <c r="G109" s="28"/>
+      <c r="H109" s="28"/>
     </row>
     <row r="110" spans="1:8" s="3" customFormat="1" ht="27" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
-      <c r="C110" s="35"/>
-      <c r="D110" s="35"/>
-      <c r="E110" s="35"/>
-      <c r="F110" s="35"/>
-      <c r="G110" s="35"/>
-      <c r="H110" s="35"/>
+      <c r="C110" s="28"/>
+      <c r="D110" s="28"/>
+      <c r="E110" s="28"/>
+      <c r="F110" s="28"/>
+      <c r="G110" s="28"/>
+      <c r="H110" s="28"/>
     </row>
     <row r="111" spans="1:8" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
-      <c r="C111" s="35"/>
-      <c r="D111" s="35"/>
-      <c r="E111" s="35"/>
-      <c r="F111" s="35"/>
-      <c r="G111" s="35"/>
-      <c r="H111" s="35"/>
+      <c r="C111" s="28"/>
+      <c r="D111" s="28"/>
+      <c r="E111" s="28"/>
+      <c r="F111" s="28"/>
+      <c r="G111" s="28"/>
+      <c r="H111" s="28"/>
     </row>
     <row r="112" spans="1:8" ht="25.5" customHeight="1">
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
+      <c r="C112" s="28"/>
+      <c r="D112" s="28"/>
+      <c r="E112" s="28"/>
+      <c r="F112" s="28"/>
+      <c r="G112" s="28"/>
+      <c r="H112" s="28"/>
     </row>
     <row r="113" spans="3:8">
-      <c r="C113" s="35"/>
-      <c r="D113" s="35"/>
-      <c r="E113" s="35"/>
-      <c r="F113" s="35"/>
-      <c r="G113" s="35"/>
-      <c r="H113" s="35"/>
+      <c r="C113" s="28"/>
+      <c r="D113" s="28"/>
+      <c r="E113" s="28"/>
+      <c r="F113" s="28"/>
+      <c r="G113" s="28"/>
+      <c r="H113" s="28"/>
     </row>
     <row r="114" spans="3:8" ht="23.25" customHeight="1">
-      <c r="C114" s="35"/>
-      <c r="D114" s="35"/>
-      <c r="E114" s="35"/>
-      <c r="F114" s="35"/>
-      <c r="G114" s="35"/>
-      <c r="H114" s="35"/>
+      <c r="C114" s="28"/>
+      <c r="D114" s="28"/>
+      <c r="E114" s="28"/>
+      <c r="F114" s="28"/>
+      <c r="G114" s="28"/>
+      <c r="H114" s="28"/>
     </row>
     <row r="115" spans="3:8" ht="23.25" customHeight="1">
-      <c r="C115" s="35"/>
-      <c r="D115" s="35"/>
-      <c r="E115" s="35"/>
-      <c r="F115" s="35"/>
-      <c r="G115" s="35"/>
-      <c r="H115" s="35"/>
+      <c r="C115" s="28"/>
+      <c r="D115" s="28"/>
+      <c r="E115" s="28"/>
+      <c r="F115" s="28"/>
+      <c r="G115" s="28"/>
+      <c r="H115" s="28"/>
     </row>
     <row r="116" spans="3:8" ht="12" customHeight="1">
-      <c r="C116" s="35"/>
-      <c r="D116" s="35"/>
-      <c r="E116" s="35"/>
-      <c r="F116" s="35"/>
-      <c r="G116" s="35"/>
-      <c r="H116" s="35"/>
+      <c r="C116" s="28"/>
+      <c r="D116" s="28"/>
+      <c r="E116" s="28"/>
+      <c r="F116" s="28"/>
+      <c r="G116" s="28"/>
+      <c r="H116" s="28"/>
     </row>
     <row r="117" spans="3:8" ht="12" customHeight="1">
-      <c r="C117" s="35"/>
-      <c r="D117" s="35"/>
-      <c r="E117" s="35"/>
-      <c r="F117" s="35"/>
-      <c r="G117" s="35"/>
-      <c r="H117" s="35"/>
+      <c r="C117" s="28"/>
+      <c r="D117" s="28"/>
+      <c r="E117" s="28"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="28"/>
+      <c r="H117" s="28"/>
     </row>
     <row r="118" spans="3:8">
-      <c r="C118" s="35"/>
-      <c r="D118" s="35"/>
-      <c r="E118" s="35"/>
-      <c r="F118" s="35"/>
-      <c r="G118" s="35"/>
-      <c r="H118" s="35"/>
+      <c r="C118" s="28"/>
+      <c r="D118" s="28"/>
+      <c r="E118" s="28"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="28"/>
+      <c r="H118" s="28"/>
     </row>
     <row r="119" spans="3:8" ht="19.5" customHeight="1">
-      <c r="C119" s="35"/>
-      <c r="D119" s="35"/>
-      <c r="E119" s="35"/>
-      <c r="F119" s="35"/>
-      <c r="G119" s="35"/>
-      <c r="H119" s="35"/>
+      <c r="C119" s="28"/>
+      <c r="D119" s="28"/>
+      <c r="E119" s="28"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="28"/>
+      <c r="H119" s="28"/>
     </row>
     <row r="120" spans="3:8">
-      <c r="C120" s="35"/>
-      <c r="D120" s="35"/>
-      <c r="E120" s="35"/>
-      <c r="F120" s="35"/>
-      <c r="G120" s="35"/>
-      <c r="H120" s="35"/>
+      <c r="C120" s="28"/>
+      <c r="D120" s="28"/>
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="28"/>
+      <c r="H120" s="28"/>
     </row>
     <row r="121" spans="3:8" ht="18" customHeight="1">
-      <c r="C121" s="35"/>
-      <c r="D121" s="35"/>
-      <c r="E121" s="35"/>
-      <c r="F121" s="35"/>
-      <c r="G121" s="35"/>
-      <c r="H121" s="35"/>
+      <c r="C121" s="28"/>
+      <c r="D121" s="28"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
     </row>
     <row r="122" spans="3:8" ht="321.75" customHeight="1">
-      <c r="C122" s="35"/>
-      <c r="D122" s="35"/>
-      <c r="E122" s="35"/>
-      <c r="F122" s="35"/>
-      <c r="G122" s="35"/>
-      <c r="H122" s="35"/>
+      <c r="C122" s="28"/>
+      <c r="D122" s="28"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="28"/>
+      <c r="G122" s="28"/>
+      <c r="H122" s="28"/>
     </row>
     <row r="124" spans="3:8" ht="32.25" customHeight="1"/>
     <row r="125" spans="3:8" ht="18.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="c/Fz4SftqXzTAe7x2cbHFUdk5Fjb5QRB8+DtF7v709Oh+w0YtS4QlksUY4kuI9EWK5Pkp4uyjoeWpW3SQ7jk8g==" saltValue="q4mwtKBnPfzKAOqa1Gi/1Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="20">
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="F6:H6"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EPAwu64rbxIfeACAAZrkWT/CIzapqa5Awel6An6ZGUhhKy28Tegja3aXySbqNjp7WOain7MuhZW/sHUp5JweNA==" saltValue="RnOYwu3DqwLiK9n59AFLiw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="18">
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="E89:H89"/>
     <mergeCell ref="E90:H90"/>
     <mergeCell ref="E91:H91"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A62:A63"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="D7:D10"/>
@@ -5070,6 +5127,11 @@
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:G10"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="F6:H6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.38" bottom="0.38" header="3.937007874015748E-2" footer="0.3"/>
